--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4EE3926-4AE3-4D56-BDDA-E4EB58F4F360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133998B3-4922-42DF-85AE-15F9301564D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22020" yWindow="3420" windowWidth="21600" windowHeight="11385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.NF" sheetId="1" r:id="rId1"/>
     <sheet name="Bäckereikette" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>

--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133998B3-4922-42DF-85AE-15F9301564D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC9D123-35EB-4D62-99C3-D9FCD167D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.NF" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="101">
   <si>
     <t>Filiale</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Zahlart</t>
-  </si>
-  <si>
-    <t>durchschnittl. Umsatz</t>
   </si>
   <si>
     <t>Geschlecht</t>
@@ -920,7 +917,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>21</v>
@@ -939,21 +936,19 @@
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -962,78 +957,78 @@
         <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1041,17 +1036,17 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1059,17 +1054,17 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1092,7 +1087,7 @@
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="4"/>
@@ -1181,7 +1176,7 @@
         <v>11</v>
       </c>
       <c r="L20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -1207,7 +1202,7 @@
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
@@ -1219,31 +1214,29 @@
         <v>13</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
@@ -1252,87 +1245,87 @@
         <v>15</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="J23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="L23" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1340,17 +1333,17 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="8"/>
       <c r="G26" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
@@ -1358,17 +1351,17 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1378,7 +1371,7 @@
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1391,7 +1384,7 @@
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E29" s="4"/>
       <c r="G29" s="4"/>
@@ -1425,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.140625" style="4" customWidth="1"/>
@@ -1512,7 +1505,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -1538,7 +1531,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>21</v>
@@ -1550,31 +1543,28 @@
         <v>13</v>
       </c>
       <c r="L3" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -1583,115 +1573,115 @@
         <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="L5" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10"/>
       <c r="D10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="4"/>
       <c r="J10" s="4"/>
@@ -1699,7 +1689,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11"/>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1710,46 +1700,46 @@
     </row>
     <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="H17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="I17" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="J17" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="K17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="L17" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="M17" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="M17" s="13" t="s">
+      <c r="N17" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="N17" s="13" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -1760,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" s="19">
         <v>4</v>
@@ -1791,7 +1781,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="22">
         <v>50</v>
@@ -1818,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="19">
@@ -1846,10 +1836,10 @@
         <v>0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="22">
         <v>7.2</v>
@@ -1874,10 +1864,10 @@
         <v>0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="22">
         <v>7.2</v>
@@ -1902,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="22">
         <v>7.2</v>
@@ -1929,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D24" s="22">
         <v>7.2</v>
@@ -1957,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="4">
         <v>7.2</v>
@@ -1988,13 +1978,13 @@
         <v>12</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E26" s="19">
         <v>8</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
@@ -2015,7 +2005,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E27" s="24">
         <v>4</v>
@@ -2046,7 +2036,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
@@ -2074,7 +2064,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" s="25">
         <v>4</v>
@@ -2102,7 +2092,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="24">
         <v>4</v>
@@ -2133,7 +2123,7 @@
         <v>14</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E31" s="25">
         <v>4</v>
@@ -2154,55 +2144,58 @@
     </row>
     <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="4">
-        <v>7.2</v>
-      </c>
-      <c r="E32" s="19">
-        <v>5</v>
-      </c>
-      <c r="F32" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="E32" s="24">
+        <v>4</v>
+      </c>
+      <c r="F32" s="20">
+        <v>1</v>
+      </c>
       <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
+      <c r="H32" s="20">
+        <v>1</v>
+      </c>
       <c r="I32" s="21"/>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
-      <c r="M32" s="20"/>
+      <c r="L32" s="9">
+        <v>1</v>
+      </c>
+      <c r="M32" s="20">
+        <v>1</v>
+      </c>
       <c r="N32" s="21"/>
     </row>
     <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>14</v>
+      <c r="B33" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C33" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E33" s="24">
-        <v>4</v>
-      </c>
-      <c r="F33" s="20">
-        <v>1</v>
-      </c>
+      <c r="D33" s="22">
+        <v>50</v>
+      </c>
+      <c r="E33" s="19">
+        <f>2*D33+2</f>
+        <v>102</v>
+      </c>
+      <c r="F33" s="20"/>
       <c r="G33" s="20"/>
-      <c r="H33" s="20">
-        <v>1</v>
-      </c>
+      <c r="H33" s="20"/>
       <c r="I33" s="21"/>
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
-      <c r="L33" s="9">
-        <v>1</v>
-      </c>
       <c r="M33" s="20">
         <v>1</v>
       </c>
@@ -2213,17 +2206,16 @@
         <v>3</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D34" s="22">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E34" s="19">
-        <f>2*D34+2</f>
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="20"/>
@@ -2231,9 +2223,7 @@
       <c r="I34" s="21"/>
       <c r="J34" s="21"/>
       <c r="K34" s="21"/>
-      <c r="M34" s="20">
-        <v>1</v>
-      </c>
+      <c r="M34" s="20"/>
       <c r="N34" s="21"/>
     </row>
     <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2241,16 +2231,16 @@
         <v>3</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="22">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="D35" s="4">
+        <v>4.2</v>
       </c>
       <c r="E35" s="19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
@@ -2258,7 +2248,9 @@
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
-      <c r="M35" s="20"/>
+      <c r="M35" s="20">
+        <v>1</v>
+      </c>
       <c r="N35" s="21"/>
     </row>
     <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2266,16 +2258,13 @@
         <v>3</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="4">
-        <v>4.2</v>
+        <v>77</v>
       </c>
       <c r="E36" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F36" s="20"/>
       <c r="G36" s="20"/>
@@ -2283,9 +2272,7 @@
       <c r="I36" s="21"/>
       <c r="J36" s="21"/>
       <c r="K36" s="21"/>
-      <c r="M36" s="20">
-        <v>1</v>
-      </c>
+      <c r="M36" s="20"/>
       <c r="N36" s="21"/>
     </row>
     <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2293,13 +2280,16 @@
         <v>3</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="D37" s="4">
+        <v>4.2</v>
       </c>
       <c r="E37" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
@@ -2307,7 +2297,9 @@
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
-      <c r="M37" s="20"/>
+      <c r="M37" s="20">
+        <v>1</v>
+      </c>
       <c r="N37" s="21"/>
     </row>
     <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2315,16 +2307,13 @@
         <v>3</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="4">
-        <v>4.2</v>
+        <v>77</v>
       </c>
       <c r="E38" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="20"/>
@@ -2342,13 +2331,17 @@
         <v>3</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>78</v>
+        <v>75</v>
+      </c>
+      <c r="D39" s="4">
+        <v>12</v>
       </c>
       <c r="E39" s="19">
-        <v>8</v>
+        <f>2*D39+2</f>
+        <v>26</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="20"/>
@@ -2365,22 +2358,23 @@
       <c r="A40" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>49</v>
+      <c r="B40" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="4">
-        <v>12</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D40" s="22"/>
       <c r="E40" s="19">
-        <f>2*D40+2</f>
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
+      <c r="G40" s="20">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20">
+        <v>1</v>
+      </c>
       <c r="I40" s="21"/>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
@@ -2393,23 +2387,22 @@
       <c r="A41" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>52</v>
+      <c r="B41" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="C41" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="22"/>
+      <c r="D41" s="22">
+        <v>20</v>
+      </c>
       <c r="E41" s="19">
-        <v>4</v>
+        <f>2*D41+2</f>
+        <v>42</v>
       </c>
       <c r="F41" s="20"/>
-      <c r="G41" s="20">
-        <v>1</v>
-      </c>
-      <c r="H41" s="20">
-        <v>1</v>
-      </c>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
       <c r="I41" s="21"/>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
@@ -2420,59 +2413,58 @@
     </row>
     <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>51</v>
+        <v>4</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" s="22">
-        <v>20</v>
-      </c>
-      <c r="E42" s="19">
-        <f>2*D42+2</f>
-        <v>42</v>
-      </c>
-      <c r="F42" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="E42" s="24">
+        <v>4</v>
+      </c>
+      <c r="F42" s="20">
+        <v>1</v>
+      </c>
       <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
+      <c r="H42" s="20">
+        <v>1</v>
+      </c>
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
-      <c r="M42" s="20">
-        <v>1</v>
-      </c>
+      <c r="L42" s="9">
+        <v>1</v>
+      </c>
+      <c r="M42" s="20"/>
       <c r="N42" s="21"/>
     </row>
     <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>15</v>
+      <c r="B43" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="24">
-        <v>4</v>
-      </c>
-      <c r="F43" s="20">
-        <v>1</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D43" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="E43" s="19">
+        <v>5</v>
+      </c>
+      <c r="F43" s="20"/>
       <c r="G43" s="20"/>
-      <c r="H43" s="20">
-        <v>1</v>
-      </c>
+      <c r="H43" s="20"/>
       <c r="I43" s="21"/>
       <c r="J43" s="21"/>
       <c r="K43" s="21"/>
-      <c r="L43" s="9">
-        <v>1</v>
-      </c>
-      <c r="M43" s="20"/>
+      <c r="M43" s="20">
+        <v>1</v>
+      </c>
       <c r="N43" s="21"/>
     </row>
     <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2480,12 +2472,12 @@
         <v>4</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44" s="4">
+        <v>79</v>
+      </c>
+      <c r="D44" s="22">
         <v>4.2</v>
       </c>
       <c r="E44" s="19">
@@ -2497,6 +2489,7 @@
       <c r="I44" s="21"/>
       <c r="J44" s="21"/>
       <c r="K44" s="21"/>
+      <c r="L44" s="20"/>
       <c r="M44" s="20">
         <v>1</v>
       </c>
@@ -2507,16 +2500,17 @@
         <v>4</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D45" s="22">
-        <v>4.2</v>
+        <v>50</v>
       </c>
       <c r="E45" s="19">
-        <v>5</v>
+        <f>2*D45+2</f>
+        <v>102</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="20"/>
@@ -2524,7 +2518,9 @@
       <c r="I45" s="21"/>
       <c r="J45" s="21"/>
       <c r="K45" s="21"/>
-      <c r="L45" s="20"/>
+      <c r="L45" s="20">
+        <v>1</v>
+      </c>
       <c r="M45" s="20">
         <v>1</v>
       </c>
@@ -2534,28 +2530,26 @@
       <c r="A46" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>32</v>
+      <c r="B46" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="22">
-        <v>50</v>
-      </c>
-      <c r="E46" s="19">
-        <f>2*D46+2</f>
-        <v>102</v>
+        <v>74</v>
+      </c>
+      <c r="E46" s="25">
+        <v>4</v>
       </c>
       <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
+      <c r="G46" s="20">
+        <v>1</v>
+      </c>
+      <c r="H46" s="20">
+        <v>1</v>
+      </c>
       <c r="I46" s="21"/>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
-      <c r="L46" s="20">
-        <v>1</v>
-      </c>
+      <c r="L46" s="20"/>
       <c r="M46" s="20">
         <v>1</v>
       </c>
@@ -2563,28 +2557,30 @@
     </row>
     <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E47" s="25">
         <v>4</v>
       </c>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20">
-        <v>1</v>
-      </c>
+      <c r="F47" s="20">
+        <v>1</v>
+      </c>
+      <c r="G47" s="20"/>
       <c r="H47" s="20">
         <v>1</v>
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
-      <c r="L47" s="20"/>
+      <c r="L47" s="20">
+        <v>1</v>
+      </c>
       <c r="M47" s="20">
         <v>1</v>
       </c>
@@ -2594,22 +2590,22 @@
       <c r="A48" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>16</v>
+      <c r="B48" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E48" s="25">
-        <v>4</v>
-      </c>
-      <c r="F48" s="20">
-        <v>1</v>
-      </c>
+      <c r="D48" s="22">
+        <v>50</v>
+      </c>
+      <c r="E48" s="19">
+        <f>2*D48+2</f>
+        <v>102</v>
+      </c>
+      <c r="F48" s="20"/>
       <c r="G48" s="20"/>
-      <c r="H48" s="20">
-        <v>1</v>
-      </c>
+      <c r="H48" s="20"/>
       <c r="I48" s="21"/>
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
@@ -2623,30 +2619,30 @@
     </row>
     <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D49" s="22">
-        <v>50</v>
-      </c>
-      <c r="E49" s="19">
-        <f>2*D49+2</f>
-        <v>102</v>
-      </c>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="E49" s="25">
+        <v>4</v>
+      </c>
+      <c r="F49" s="20">
+        <v>1</v>
+      </c>
+      <c r="G49" s="20">
+        <v>1</v>
+      </c>
+      <c r="H49" s="20">
+        <v>1</v>
+      </c>
       <c r="I49" s="21"/>
       <c r="J49" s="21"/>
       <c r="K49" s="21"/>
-      <c r="L49" s="20">
-        <v>1</v>
-      </c>
+      <c r="L49" s="20"/>
       <c r="M49" s="20">
         <v>1</v>
       </c>
@@ -2657,20 +2653,19 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E50" s="25">
-        <v>4</v>
+        <v>81</v>
+      </c>
+      <c r="D50" s="22"/>
+      <c r="E50" s="19">
+        <v>2</v>
       </c>
       <c r="F50" s="20">
         <v>1</v>
       </c>
-      <c r="G50" s="20">
-        <v>1</v>
-      </c>
+      <c r="G50" s="20"/>
       <c r="H50" s="20">
         <v>1</v>
       </c>
@@ -2687,23 +2682,21 @@
       <c r="A51" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>21</v>
+      <c r="B51" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D51" s="22"/>
+        <v>79</v>
+      </c>
+      <c r="D51" s="22">
+        <v>4.2</v>
+      </c>
       <c r="E51" s="19">
-        <v>2</v>
-      </c>
-      <c r="F51" s="20">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F51" s="20"/>
       <c r="G51" s="20"/>
-      <c r="H51" s="20">
-        <v>1</v>
-      </c>
+      <c r="H51" s="20"/>
       <c r="I51" s="21"/>
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
@@ -2718,16 +2711,14 @@
         <v>6</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52" s="22">
-        <v>4.2</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="D52" s="22"/>
       <c r="E52" s="19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="20"/>
@@ -2736,9 +2727,7 @@
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
       <c r="L52" s="20"/>
-      <c r="M52" s="20">
-        <v>1</v>
-      </c>
+      <c r="M52" s="20"/>
       <c r="N52" s="21"/>
     </row>
     <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2746,10 +2735,10 @@
         <v>6</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="19">
@@ -2770,14 +2759,16 @@
         <v>6</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D54" s="22"/>
+        <v>79</v>
+      </c>
+      <c r="D54" s="22">
+        <v>4.2</v>
+      </c>
       <c r="E54" s="19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="20"/>
@@ -2786,7 +2777,9 @@
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
       <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
+      <c r="M54" s="20">
+        <v>1</v>
+      </c>
       <c r="N54" s="21"/>
     </row>
     <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2794,16 +2787,17 @@
         <v>6</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D55" s="22">
-        <v>4.2</v>
+        <v>50</v>
       </c>
       <c r="E55" s="19">
-        <v>5</v>
+        <f>2*D55+2</f>
+        <v>102</v>
       </c>
       <c r="F55" s="20"/>
       <c r="G55" s="20"/>
@@ -2822,17 +2816,14 @@
         <v>6</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D56" s="22">
-        <v>50</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D56" s="22"/>
       <c r="E56" s="19">
-        <f>2*D56+2</f>
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="F56" s="20"/>
       <c r="G56" s="20"/>
@@ -2841,61 +2832,63 @@
       <c r="J56" s="21"/>
       <c r="K56" s="21"/>
       <c r="L56" s="20"/>
-      <c r="M56" s="20">
-        <v>1</v>
-      </c>
+      <c r="M56" s="20"/>
       <c r="N56" s="21"/>
     </row>
     <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>50</v>
+        <v>7</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" s="22"/>
-      <c r="E57" s="19">
-        <v>1</v>
-      </c>
-      <c r="F57" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="E57" s="25">
+        <v>4</v>
+      </c>
+      <c r="F57" s="20">
+        <v>1</v>
+      </c>
       <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
+      <c r="H57" s="20">
+        <v>1</v>
+      </c>
       <c r="I57" s="21"/>
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
+      <c r="L57" s="20">
+        <v>1</v>
+      </c>
+      <c r="M57" s="20">
+        <v>1</v>
+      </c>
       <c r="N57" s="21"/>
     </row>
     <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>17</v>
+      <c r="B58" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E58" s="25">
-        <v>4</v>
-      </c>
-      <c r="F58" s="20">
-        <v>1</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="D58" s="22">
+        <v>4.2</v>
+      </c>
+      <c r="E58" s="19">
+        <v>5</v>
+      </c>
+      <c r="F58" s="20"/>
       <c r="G58" s="20"/>
-      <c r="H58" s="20">
-        <v>1</v>
-      </c>
+      <c r="H58" s="20"/>
       <c r="I58" s="21"/>
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
-      <c r="L58" s="20">
-        <v>1</v>
-      </c>
+      <c r="L58" s="20"/>
       <c r="M58" s="20">
         <v>1</v>
       </c>
@@ -2906,17 +2899,13 @@
         <v>7</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D59" s="22">
-        <v>4.2</v>
-      </c>
-      <c r="E59" s="19">
-        <v>5</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="D59" s="22"/>
+      <c r="E59" s="19"/>
       <c r="F59" s="20"/>
       <c r="G59" s="20"/>
       <c r="H59" s="20"/>
@@ -2924,9 +2913,7 @@
       <c r="J59" s="21"/>
       <c r="K59" s="21"/>
       <c r="L59" s="20"/>
-      <c r="M59" s="20">
-        <v>1</v>
-      </c>
+      <c r="M59" s="20"/>
       <c r="N59" s="21"/>
     </row>
     <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2934,13 +2921,17 @@
         <v>7</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D60" s="22"/>
-      <c r="E60" s="19"/>
+        <v>76</v>
+      </c>
+      <c r="D60" s="22">
+        <v>7.2</v>
+      </c>
+      <c r="E60" s="19">
+        <v>5</v>
+      </c>
       <c r="F60" s="20"/>
       <c r="G60" s="20"/>
       <c r="H60" s="20"/>
@@ -2948,7 +2939,9 @@
       <c r="J60" s="21"/>
       <c r="K60" s="21"/>
       <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
+      <c r="M60" s="20">
+        <v>1</v>
+      </c>
       <c r="N60" s="21"/>
     </row>
     <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.25">
@@ -2956,16 +2949,17 @@
         <v>7</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D61" s="22">
-        <v>7.2</v>
+        <v>50</v>
       </c>
       <c r="E61" s="19">
-        <v>5</v>
+        <f>2*D642+2</f>
+        <v>2</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="20"/>
@@ -2973,7 +2967,9 @@
       <c r="I61" s="21"/>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
-      <c r="L61" s="20"/>
+      <c r="L61" s="20">
+        <v>1</v>
+      </c>
       <c r="M61" s="20">
         <v>1</v>
       </c>
@@ -2981,30 +2977,30 @@
     </row>
     <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>40</v>
+        <v>8</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D62" s="22">
-        <v>50</v>
-      </c>
-      <c r="E62" s="19">
-        <f>2*D643+2</f>
-        <v>2</v>
-      </c>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
+        <v>74</v>
+      </c>
+      <c r="E62" s="25">
+        <v>4</v>
+      </c>
+      <c r="F62" s="20">
+        <v>1</v>
+      </c>
+      <c r="G62" s="20">
+        <v>1</v>
+      </c>
+      <c r="H62" s="20">
+        <v>1</v>
+      </c>
       <c r="I62" s="21"/>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
-      <c r="L62" s="20">
-        <v>1</v>
-      </c>
+      <c r="L62" s="20"/>
       <c r="M62" s="20">
         <v>1</v>
       </c>
@@ -3015,13 +3011,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E63" s="25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F63" s="20">
         <v>1</v>
@@ -3046,13 +3042,13 @@
         <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E64" s="25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F64" s="20">
         <v>1</v>
@@ -3076,24 +3072,18 @@
       <c r="A65" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>15</v>
+      <c r="B65" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E65" s="25">
-        <v>4</v>
-      </c>
-      <c r="F65" s="20">
-        <v>1</v>
-      </c>
-      <c r="G65" s="20">
-        <v>1</v>
-      </c>
-      <c r="H65" s="20">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
       <c r="I65" s="21"/>
       <c r="J65" s="21"/>
       <c r="K65" s="21"/>
@@ -3105,20 +3095,26 @@
     </row>
     <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>35</v>
+        <v>9</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E66" s="25">
-        <v>2</v>
-      </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="F66" s="20">
+        <v>1</v>
+      </c>
+      <c r="G66" s="20">
+        <v>1</v>
+      </c>
+      <c r="H66" s="20">
+        <v>1</v>
+      </c>
       <c r="I66" s="21"/>
       <c r="J66" s="21"/>
       <c r="K66" s="21"/>
@@ -3133,13 +3129,14 @@
         <v>9</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67" s="25">
-        <v>4</v>
+        <v>77</v>
+      </c>
+      <c r="D67" s="22"/>
+      <c r="E67" s="19">
+        <v>8</v>
       </c>
       <c r="F67" s="20">
         <v>1</v>
@@ -3164,14 +3161,14 @@
         <v>9</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D68" s="22"/>
       <c r="E68" s="19">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F68" s="20">
         <v>1</v>
@@ -3195,25 +3192,21 @@
       <c r="A69" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>15</v>
+      <c r="B69" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" s="22"/>
+        <v>83</v>
+      </c>
+      <c r="D69" s="22">
+        <v>5.2</v>
+      </c>
       <c r="E69" s="19">
-        <v>4</v>
-      </c>
-      <c r="F69" s="20">
-        <v>1</v>
-      </c>
-      <c r="G69" s="20">
-        <v>1</v>
-      </c>
-      <c r="H69" s="20">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
       <c r="I69" s="21"/>
       <c r="J69" s="21"/>
       <c r="K69" s="21"/>
@@ -3225,23 +3218,27 @@
     </row>
     <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>35</v>
+        <v>10</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" s="22">
-        <v>5.2</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D70" s="22"/>
       <c r="E70" s="19">
-        <v>5</v>
-      </c>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
+        <v>4</v>
+      </c>
+      <c r="F70" s="20">
+        <v>1</v>
+      </c>
+      <c r="G70" s="20">
+        <v>1</v>
+      </c>
+      <c r="H70" s="20">
+        <v>1</v>
+      </c>
       <c r="I70" s="21"/>
       <c r="J70" s="21"/>
       <c r="K70" s="21"/>
@@ -3256,10 +3253,10 @@
         <v>10</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D71" s="22"/>
       <c r="E71" s="19">
@@ -3287,25 +3284,19 @@
       <c r="A72" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>13</v>
+      <c r="B72" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="19">
-        <v>4</v>
-      </c>
-      <c r="F72" s="20">
-        <v>1</v>
-      </c>
-      <c r="G72" s="20">
-        <v>1</v>
-      </c>
-      <c r="H72" s="20">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
       <c r="I72" s="21"/>
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
@@ -3320,14 +3311,14 @@
         <v>10</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C73" s="18" t="s">
         <v>85</v>
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F73" s="20"/>
       <c r="G73" s="20"/>
@@ -3346,10 +3337,10 @@
         <v>10</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="19">
@@ -3369,25 +3360,31 @@
     </row>
     <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D75" s="22"/>
-      <c r="E75" s="19">
-        <v>5</v>
-      </c>
-      <c r="F75" s="20"/>
+        <v>22</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C75" t="s">
+        <v>74</v>
+      </c>
+      <c r="D75"/>
+      <c r="E75" s="26">
+        <v>4</v>
+      </c>
+      <c r="F75" s="20">
+        <v>1</v>
+      </c>
       <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
+      <c r="H75" s="20">
+        <v>1</v>
+      </c>
       <c r="I75" s="21"/>
       <c r="J75" s="21"/>
       <c r="K75" s="21"/>
-      <c r="L75" s="20"/>
+      <c r="L75" s="20">
+        <v>1</v>
+      </c>
       <c r="M75" s="20">
         <v>1</v>
       </c>
@@ -3397,29 +3394,26 @@
       <c r="A76" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D76"/>
-      <c r="E76" s="26">
-        <v>4</v>
-      </c>
-      <c r="F76" s="20">
-        <v>1</v>
-      </c>
+      <c r="D76" s="22">
+        <v>50</v>
+      </c>
+      <c r="E76" s="19">
+        <f>2*D76+2</f>
+        <v>102</v>
+      </c>
+      <c r="F76" s="20"/>
       <c r="G76" s="20"/>
-      <c r="H76" s="20">
-        <v>1</v>
-      </c>
+      <c r="H76" s="20"/>
       <c r="I76" s="21"/>
       <c r="J76" s="21"/>
       <c r="K76" s="21"/>
-      <c r="L76" s="20">
-        <v>1</v>
-      </c>
+      <c r="L76" s="20"/>
       <c r="M76" s="20">
         <v>1</v>
       </c>
@@ -3433,14 +3427,13 @@
         <v>53</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D77" s="22">
-        <v>50</v>
+        <v>86</v>
+      </c>
+      <c r="D77" s="4">
+        <v>5</v>
       </c>
       <c r="E77" s="19">
-        <f>2*D77+2</f>
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
@@ -3462,13 +3455,14 @@
         <v>54</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D78" s="4">
-        <v>5</v>
+        <v>75</v>
+      </c>
+      <c r="D78" s="22">
+        <v>2</v>
       </c>
       <c r="E78" s="19">
-        <v>7</v>
+        <f>2*D78+2</f>
+        <v>6</v>
       </c>
       <c r="F78" s="20"/>
       <c r="G78" s="20"/>
@@ -3490,14 +3484,14 @@
         <v>55</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" s="22">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="D79" s="4">
+        <v>7</v>
       </c>
       <c r="E79" s="19">
         <f>2*D79+2</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F79" s="20"/>
       <c r="G79" s="20"/>
@@ -3511,47 +3505,36 @@
       </c>
       <c r="N79" s="21"/>
     </row>
-    <row r="80" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D80" s="4">
-        <v>7</v>
-      </c>
-      <c r="E80" s="19">
-        <f>2*D80+2</f>
-        <v>16</v>
-      </c>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
+    <row r="80" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+      <c r="A80" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="42"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21"/>
+      <c r="H80" s="21"/>
       <c r="I80" s="21"/>
       <c r="J80" s="21"/>
       <c r="K80" s="21"/>
       <c r="L80" s="20"/>
-      <c r="M80" s="20">
-        <v>1</v>
-      </c>
+      <c r="M80" s="20"/>
       <c r="N80" s="21"/>
     </row>
-    <row r="81" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A81" s="42" t="s">
+    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A81" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="B81" s="42"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
+      <c r="B81" s="43"/>
+      <c r="C81" s="43"/>
+      <c r="D81" s="43"/>
+      <c r="E81" s="43"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="28"/>
+      <c r="H81" s="28"/>
+      <c r="I81" s="28"/>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
       <c r="L81" s="20"/>
@@ -3559,68 +3542,90 @@
       <c r="N81" s="21"/>
     </row>
     <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="43" t="s">
+      <c r="A82" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="B82" s="43"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="28"/>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="21"/>
+      <c r="H82" s="21"/>
+      <c r="I82" s="21"/>
       <c r="J82" s="21"/>
       <c r="K82" s="21"/>
       <c r="L82" s="20"/>
       <c r="M82" s="20"/>
       <c r="N82" s="21"/>
     </row>
-    <row r="83" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A83" s="44" t="s">
+    <row r="83" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A83" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="44"/>
-      <c r="C83" s="29"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
+      <c r="C83" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D83" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="F83" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="G83" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H83" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>97</v>
+      </c>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
       <c r="L83" s="20"/>
       <c r="M83" s="20"/>
       <c r="N83" s="21"/>
     </row>
-    <row r="84" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A84" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="B84" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D84" s="32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E84" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F84" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="G84" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="H84" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="I84" s="32" t="s">
-        <v>98</v>
+    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A84" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" s="4">
+        <v>50</v>
+      </c>
+      <c r="C84" s="4">
+        <v>5</v>
+      </c>
+      <c r="D84" s="19">
+        <f t="shared" ref="D84:D95" si="0">B84+10*C84</f>
+        <v>100</v>
+      </c>
+      <c r="E84" s="19">
+        <f>SUM(E18:E25)</f>
+        <v>135</v>
+      </c>
+      <c r="F84" s="19">
+        <f t="shared" ref="F84:F95" si="1">D84*E84</f>
+        <v>13500</v>
+      </c>
+      <c r="G84" s="34">
+        <f t="shared" ref="G84:I95" si="2">F84/1024</f>
+        <v>13.18359375</v>
+      </c>
+      <c r="H84" s="34">
+        <f t="shared" si="2"/>
+        <v>1.2874603271484375E-2</v>
+      </c>
+      <c r="I84" s="19">
+        <f t="shared" si="2"/>
+        <v>1.257285475730896E-5</v>
       </c>
       <c r="J84" s="21"/>
       <c r="K84" s="21"/>
@@ -3629,38 +3634,38 @@
       <c r="N84" s="21"/>
     </row>
     <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A85" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B85" s="4">
-        <v>50</v>
-      </c>
-      <c r="C85" s="4">
-        <v>5</v>
+      <c r="A85" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="36">
+        <v>10000000</v>
+      </c>
+      <c r="C85" s="36">
+        <v>11000000</v>
       </c>
       <c r="D85" s="19">
-        <f t="shared" ref="D85:D96" si="0">B85+10*C85</f>
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>120000000</v>
       </c>
       <c r="E85" s="19">
-        <f>SUM(E18:E25)</f>
-        <v>135</v>
+        <f>SUM(E26:E29)</f>
+        <v>17</v>
       </c>
       <c r="F85" s="19">
-        <f t="shared" ref="F85:F96" si="1">D85*E85</f>
-        <v>13500</v>
+        <f t="shared" si="1"/>
+        <v>2040000000</v>
       </c>
       <c r="G85" s="34">
-        <f t="shared" ref="G85:I96" si="2">F85/1024</f>
-        <v>13.18359375</v>
+        <f t="shared" si="2"/>
+        <v>1992187.5</v>
       </c>
       <c r="H85" s="34">
         <f t="shared" si="2"/>
-        <v>1.2874603271484375E-2</v>
+        <v>1945.49560546875</v>
       </c>
       <c r="I85" s="19">
         <f t="shared" si="2"/>
-        <v>1.257285475730896E-5</v>
+        <v>1.8998980522155762</v>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -3670,37 +3675,37 @@
     </row>
     <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" s="36">
-        <v>10000000</v>
-      </c>
-      <c r="C86" s="36">
-        <v>11000000</v>
+        <v>2</v>
+      </c>
+      <c r="B86" s="4">
+        <v>150</v>
+      </c>
+      <c r="C86" s="4">
+        <v>30</v>
       </c>
       <c r="D86" s="19">
         <f t="shared" si="0"/>
-        <v>120000000</v>
+        <v>450</v>
       </c>
       <c r="E86" s="19">
-        <f>SUM(E26:E29)</f>
-        <v>17</v>
+        <f>SUM(E30:E31)</f>
+        <v>8</v>
       </c>
       <c r="F86" s="19">
         <f t="shared" si="1"/>
-        <v>2040000000</v>
+        <v>3600</v>
       </c>
       <c r="G86" s="34">
         <f t="shared" si="2"/>
-        <v>1992187.5</v>
+        <v>3.515625</v>
       </c>
       <c r="H86" s="34">
         <f t="shared" si="2"/>
-        <v>1945.49560546875</v>
+        <v>3.4332275390625E-3</v>
       </c>
       <c r="I86" s="19">
         <f t="shared" si="2"/>
-        <v>1.8998980522155762</v>
+        <v>3.3527612686157227E-6</v>
       </c>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
@@ -3710,37 +3715,37 @@
     </row>
     <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="35" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B87" s="4">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C87" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D87" s="19">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="E87" s="19">
-        <f>SUM(E30:E32)</f>
-        <v>13</v>
+        <f>SUM(E32:E41)</f>
+        <v>205</v>
       </c>
       <c r="F87" s="19">
         <f t="shared" si="1"/>
-        <v>5850</v>
+        <v>110700</v>
       </c>
       <c r="G87" s="34">
         <f t="shared" si="2"/>
-        <v>5.712890625</v>
+        <v>108.10546875</v>
       </c>
       <c r="H87" s="34">
         <f t="shared" si="2"/>
-        <v>5.5789947509765625E-3</v>
+        <v>0.10557174682617188</v>
       </c>
       <c r="I87" s="19">
         <f t="shared" si="2"/>
-        <v>5.4482370615005493E-6</v>
+        <v>1.0309740900993347E-4</v>
       </c>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
@@ -3750,37 +3755,37 @@
     </row>
     <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B88" s="4">
-        <v>200</v>
-      </c>
-      <c r="C88" s="4">
-        <v>34</v>
+        <v>4</v>
+      </c>
+      <c r="B88" s="21">
+        <v>50</v>
+      </c>
+      <c r="C88" s="21">
+        <v>5</v>
       </c>
       <c r="D88" s="19">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>100</v>
       </c>
       <c r="E88" s="19">
-        <f>SUM(E33:E42)</f>
-        <v>205</v>
+        <f>SUM(E42:E46)</f>
+        <v>120</v>
       </c>
       <c r="F88" s="19">
         <f t="shared" si="1"/>
-        <v>110700</v>
+        <v>12000</v>
       </c>
       <c r="G88" s="34">
         <f t="shared" si="2"/>
-        <v>108.10546875</v>
+        <v>11.71875</v>
       </c>
       <c r="H88" s="34">
         <f t="shared" si="2"/>
-        <v>0.10557174682617188</v>
+        <v>1.1444091796875E-2</v>
       </c>
       <c r="I88" s="19">
         <f t="shared" si="2"/>
-        <v>1.0309740900993347E-4</v>
+        <v>1.1175870895385742E-5</v>
       </c>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
@@ -3789,38 +3794,38 @@
       <c r="N88" s="21"/>
     </row>
     <row r="89" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A89" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="B89" s="21">
-        <v>50</v>
-      </c>
-      <c r="C89" s="21">
+      <c r="A89" s="37" t="s">
         <v>5</v>
+      </c>
+      <c r="B89" s="4">
+        <v>6</v>
+      </c>
+      <c r="C89" s="4">
+        <v>0</v>
       </c>
       <c r="D89" s="19">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E89" s="19">
-        <f>SUM(E43:E47)</f>
-        <v>120</v>
+        <f>SUM(E47:E48)</f>
+        <v>106</v>
       </c>
       <c r="F89" s="19">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>636</v>
       </c>
       <c r="G89" s="34">
         <f t="shared" si="2"/>
-        <v>11.71875</v>
+        <v>0.62109375</v>
       </c>
       <c r="H89" s="34">
         <f t="shared" si="2"/>
-        <v>1.1444091796875E-2</v>
+        <v>6.06536865234375E-4</v>
       </c>
       <c r="I89" s="19">
         <f t="shared" si="2"/>
-        <v>1.1175870895385742E-5</v>
+        <v>5.9232115745544434E-7</v>
       </c>
       <c r="J89" s="21"/>
       <c r="K89" s="21"/>
@@ -3830,37 +3835,37 @@
     </row>
     <row r="90" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90" s="4">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="C90" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D90" s="19">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="E90" s="19">
-        <f>SUM(E48:E49)</f>
-        <v>106</v>
+        <f>SUM(E49:E55)</f>
+        <v>134</v>
       </c>
       <c r="F90" s="19">
         <f t="shared" si="1"/>
-        <v>636</v>
+        <v>29480</v>
       </c>
       <c r="G90" s="34">
         <f t="shared" si="2"/>
-        <v>0.62109375</v>
+        <v>28.7890625</v>
       </c>
       <c r="H90" s="34">
         <f t="shared" si="2"/>
-        <v>6.06536865234375E-4</v>
+        <v>2.811431884765625E-2</v>
       </c>
       <c r="I90" s="19">
         <f t="shared" si="2"/>
-        <v>5.9232115745544434E-7</v>
+        <v>2.7455389499664307E-5</v>
       </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
@@ -3868,39 +3873,39 @@
       <c r="M90" s="20"/>
       <c r="N90" s="21"/>
     </row>
-    <row r="91" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B91" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="C91" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D91" s="19">
         <f t="shared" si="0"/>
-        <v>220</v>
+        <v>70</v>
       </c>
       <c r="E91" s="19">
-        <f>SUM(E50:E56)</f>
-        <v>134</v>
+        <f>SUM(E57:E61)</f>
+        <v>16</v>
       </c>
       <c r="F91" s="19">
         <f t="shared" si="1"/>
-        <v>29480</v>
+        <v>1120</v>
       </c>
       <c r="G91" s="34">
         <f t="shared" si="2"/>
-        <v>28.7890625</v>
+        <v>1.09375</v>
       </c>
       <c r="H91" s="34">
         <f t="shared" si="2"/>
-        <v>2.811431884765625E-2</v>
+        <v>1.068115234375E-3</v>
       </c>
       <c r="I91" s="19">
         <f t="shared" si="2"/>
-        <v>2.7455389499664307E-5</v>
+        <v>1.0430812835693359E-6</v>
       </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21"/>
@@ -3908,39 +3913,39 @@
       <c r="M91" s="20"/>
       <c r="N91" s="21"/>
     </row>
-    <row r="92" spans="1:14" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B92" s="4">
-        <v>50</v>
-      </c>
-      <c r="C92" s="4">
-        <v>2</v>
+    <row r="92" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A92" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="18">
+        <v>250</v>
+      </c>
+      <c r="C92" s="18">
+        <v>25</v>
       </c>
       <c r="D92" s="19">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="E92" s="19">
-        <f>SUM(E58:E62)</f>
-        <v>16</v>
+        <f>SUM(E62:E65)</f>
+        <v>12</v>
       </c>
       <c r="F92" s="19">
         <f t="shared" si="1"/>
-        <v>1120</v>
+        <v>6000</v>
       </c>
       <c r="G92" s="34">
         <f t="shared" si="2"/>
-        <v>1.09375</v>
+        <v>5.859375</v>
       </c>
       <c r="H92" s="34">
         <f t="shared" si="2"/>
-        <v>1.068115234375E-3</v>
+        <v>5.7220458984375E-3</v>
       </c>
       <c r="I92" s="19">
         <f t="shared" si="2"/>
-        <v>1.0430812835693359E-6</v>
+        <v>5.5879354476928711E-6</v>
       </c>
       <c r="J92" s="21"/>
       <c r="K92" s="21"/>
@@ -3950,37 +3955,37 @@
     </row>
     <row r="93" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B93" s="18">
-        <v>250</v>
-      </c>
-      <c r="C93" s="18">
-        <v>25</v>
+        <v>9</v>
+      </c>
+      <c r="B93" s="38">
+        <v>30000000</v>
+      </c>
+      <c r="C93" s="38">
+        <v>33000000</v>
       </c>
       <c r="D93" s="19">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>360000000</v>
       </c>
       <c r="E93" s="19">
-        <f>SUM(E63:E66)</f>
-        <v>12</v>
+        <f>SUM(E66:E69)</f>
+        <v>21</v>
       </c>
       <c r="F93" s="19">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>7560000000</v>
       </c>
       <c r="G93" s="34">
         <f t="shared" si="2"/>
-        <v>5.859375</v>
+        <v>7382812.5</v>
       </c>
       <c r="H93" s="34">
         <f t="shared" si="2"/>
-        <v>5.7220458984375E-3</v>
+        <v>7209.77783203125</v>
       </c>
       <c r="I93" s="19">
         <f t="shared" si="2"/>
-        <v>5.5879354476928711E-6</v>
+        <v>7.0407986640930176</v>
       </c>
       <c r="J93" s="21"/>
       <c r="K93" s="21"/>
@@ -3990,37 +3995,37 @@
     </row>
     <row r="94" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B94" s="38">
-        <v>30000000</v>
-      </c>
-      <c r="C94" s="38">
-        <v>33000000</v>
+        <v>10</v>
+      </c>
+      <c r="B94" s="18">
+        <v>30000</v>
+      </c>
+      <c r="C94" s="18">
+        <v>36000</v>
       </c>
       <c r="D94" s="19">
         <f t="shared" si="0"/>
-        <v>360000000</v>
+        <v>390000</v>
       </c>
       <c r="E94" s="19">
-        <f>SUM(E67:E70)</f>
+        <f>SUM(E70:E74)</f>
         <v>21</v>
       </c>
       <c r="F94" s="19">
         <f t="shared" si="1"/>
-        <v>7560000000</v>
+        <v>8190000</v>
       </c>
       <c r="G94" s="34">
         <f t="shared" si="2"/>
-        <v>7382812.5</v>
+        <v>7998.046875</v>
       </c>
       <c r="H94" s="34">
         <f t="shared" si="2"/>
-        <v>7209.77783203125</v>
+        <v>7.8105926513671875</v>
       </c>
       <c r="I94" s="19">
         <f t="shared" si="2"/>
-        <v>7.0407986640930176</v>
+        <v>7.627531886100769E-3</v>
       </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -4029,38 +4034,38 @@
       <c r="N94" s="21"/>
     </row>
     <row r="95" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A95" s="35" t="s">
-        <v>10</v>
+      <c r="A95" s="23" t="s">
+        <v>22</v>
       </c>
       <c r="B95" s="18">
-        <v>30000</v>
+        <v>250</v>
       </c>
       <c r="C95" s="18">
-        <v>36000</v>
+        <v>39</v>
       </c>
       <c r="D95" s="19">
         <f t="shared" si="0"/>
-        <v>390000</v>
+        <v>640</v>
       </c>
       <c r="E95" s="19">
-        <f>SUM(E71:E75)</f>
-        <v>21</v>
+        <f>SUM(E75:E79)</f>
+        <v>135</v>
       </c>
       <c r="F95" s="19">
         <f t="shared" si="1"/>
-        <v>8190000</v>
+        <v>86400</v>
       </c>
       <c r="G95" s="34">
         <f t="shared" si="2"/>
-        <v>7998.046875</v>
+        <v>84.375</v>
       </c>
       <c r="H95" s="34">
         <f t="shared" si="2"/>
-        <v>7.8105926513671875</v>
+        <v>8.23974609375E-2</v>
       </c>
       <c r="I95" s="19">
         <f t="shared" si="2"/>
-        <v>7.627531886100769E-3</v>
+        <v>8.0466270446777344E-5</v>
       </c>
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
@@ -4069,39 +4074,14 @@
       <c r="N95" s="21"/>
     </row>
     <row r="96" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A96" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="18">
-        <v>250</v>
-      </c>
-      <c r="C96" s="18">
-        <v>39</v>
-      </c>
-      <c r="D96" s="19">
-        <f t="shared" si="0"/>
-        <v>640</v>
-      </c>
-      <c r="E96" s="19">
-        <f>SUM(E76:E80)</f>
-        <v>135</v>
-      </c>
-      <c r="F96" s="19">
-        <f t="shared" si="1"/>
-        <v>86400</v>
-      </c>
-      <c r="G96" s="34">
-        <f t="shared" si="2"/>
-        <v>84.375</v>
-      </c>
-      <c r="H96" s="34">
-        <f t="shared" si="2"/>
-        <v>8.23974609375E-2</v>
-      </c>
-      <c r="I96" s="19">
-        <f t="shared" si="2"/>
-        <v>8.0466270446777344E-5</v>
-      </c>
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="I96"/>
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
       <c r="L96" s="20"/>
@@ -4109,44 +4089,45 @@
       <c r="N96" s="21"/>
     </row>
     <row r="97" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="G97"/>
-      <c r="H97"/>
-      <c r="I97"/>
+      <c r="A97" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="40"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="21"/>
+      <c r="F97" s="19">
+        <f>SUM(F84:F95)</f>
+        <v>9608453436</v>
+      </c>
+      <c r="G97" s="19">
+        <f>SUM(G84:G95)</f>
+        <v>9383255.30859375</v>
+      </c>
+      <c r="H97" s="19">
+        <f>SUM(H84:H95)</f>
+        <v>9163.335262298584</v>
+      </c>
+      <c r="I97" s="19">
+        <f>SUM(I84:I95)</f>
+        <v>8.9485695920884609</v>
+      </c>
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
       <c r="L97" s="20"/>
       <c r="M97" s="20"/>
       <c r="N97" s="21"/>
     </row>
-    <row r="98" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A98" s="39" t="s">
-        <v>99</v>
-      </c>
-      <c r="B98" s="40"/>
-      <c r="C98" s="40"/>
+    <row r="98" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="21"/>
+      <c r="B98" s="21"/>
+      <c r="C98" s="21"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
-      <c r="F98" s="19">
-        <f>SUM(F85:F96)</f>
-        <v>9608455686</v>
-      </c>
-      <c r="G98" s="19">
-        <f>SUM(G85:G96)</f>
-        <v>9383257.505859375</v>
-      </c>
-      <c r="H98" s="19">
-        <f>SUM(H85:H96)</f>
-        <v>9163.3374080657959</v>
-      </c>
-      <c r="I98" s="19">
-        <f>SUM(I85:I96)</f>
-        <v>8.9485716875642538</v>
-      </c>
+      <c r="F98" s="21"/>
+      <c r="G98" s="21"/>
+      <c r="H98" s="21"/>
+      <c r="I98" s="21"/>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
       <c r="L98" s="20"/>
@@ -4154,47 +4135,47 @@
       <c r="N98" s="21"/>
     </row>
     <row r="99" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="21"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="21"/>
-      <c r="D99" s="21"/>
+      <c r="A99" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="B99" s="45"/>
+      <c r="C99" s="45"/>
+      <c r="D99" s="41">
+        <v>0.4</v>
+      </c>
       <c r="E99" s="21"/>
-      <c r="F99" s="21"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="21"/>
+      <c r="F99" s="19">
+        <f>F97*1.4</f>
+        <v>13451834810.4</v>
+      </c>
+      <c r="G99" s="19">
+        <f>G97*1.4</f>
+        <v>13136557.43203125</v>
+      </c>
+      <c r="H99" s="19">
+        <f>H97*1.4</f>
+        <v>12828.669367218017</v>
+      </c>
+      <c r="I99" s="19">
+        <f>I97*1.4</f>
+        <v>12.527997428923845</v>
+      </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
       <c r="L99" s="20"/>
       <c r="M99" s="20"/>
       <c r="N99" s="21"/>
     </row>
-    <row r="100" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="41">
-        <v>0.4</v>
-      </c>
+    <row r="100" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A100" s="23"/>
+      <c r="B100" s="18"/>
+      <c r="C100" s="18"/>
+      <c r="D100" s="22"/>
       <c r="E100" s="21"/>
-      <c r="F100" s="19">
-        <f>F98*1.4</f>
-        <v>13451837960.4</v>
-      </c>
-      <c r="G100" s="19">
-        <f>G98*1.4</f>
-        <v>13136560.508203125</v>
-      </c>
-      <c r="H100" s="19">
-        <f>H98*1.4</f>
-        <v>12828.672371292114</v>
-      </c>
-      <c r="I100" s="19">
-        <f>I98*1.4</f>
-        <v>12.528000362589955</v>
-      </c>
+      <c r="F100" s="20"/>
+      <c r="G100" s="20"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="21"/>
       <c r="J100" s="21"/>
       <c r="K100" s="21"/>
       <c r="L100" s="20"/>
@@ -4234,15 +4215,6 @@
       <c r="N102" s="21"/>
     </row>
     <row r="103" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A103" s="23"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="22"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="21"/>
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
       <c r="L103" s="20"/>
@@ -4264,6 +4236,15 @@
       <c r="N105" s="21"/>
     </row>
     <row r="106" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="A106" s="23"/>
+      <c r="B106" s="18"/>
+      <c r="C106" s="18"/>
+      <c r="D106" s="22"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="20"/>
+      <c r="H106" s="20"/>
+      <c r="I106" s="21"/>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
       <c r="L106" s="20"/>
@@ -4366,119 +4347,103 @@
       <c r="M112" s="20"/>
       <c r="N112" s="21"/>
     </row>
-    <row r="113" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A113" s="23"/>
-      <c r="B113" s="18"/>
-      <c r="C113" s="18"/>
-      <c r="D113" s="22"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="21"/>
+    <row r="113" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
       <c r="L113" s="20"/>
       <c r="M113" s="20"/>
       <c r="N113" s="21"/>
     </row>
-    <row r="114" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J114" s="21"/>
       <c r="K114" s="21"/>
       <c r="L114" s="20"/>
       <c r="M114" s="20"/>
       <c r="N114" s="21"/>
     </row>
-    <row r="115" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J115" s="21"/>
       <c r="K115" s="21"/>
       <c r="L115" s="20"/>
       <c r="M115" s="20"/>
       <c r="N115" s="21"/>
     </row>
-    <row r="116" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
       <c r="L116" s="20"/>
       <c r="M116" s="20"/>
       <c r="N116" s="21"/>
     </row>
-    <row r="117" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
       <c r="L117" s="20"/>
       <c r="M117" s="20"/>
       <c r="N117" s="21"/>
     </row>
-    <row r="118" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
       <c r="L118" s="20"/>
       <c r="M118" s="20"/>
       <c r="N118" s="21"/>
     </row>
-    <row r="119" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
       <c r="L119" s="20"/>
       <c r="M119" s="20"/>
       <c r="N119" s="21"/>
     </row>
-    <row r="120" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J120" s="21"/>
       <c r="K120" s="21"/>
       <c r="L120" s="20"/>
       <c r="M120" s="20"/>
       <c r="N120" s="21"/>
     </row>
-    <row r="121" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J121" s="21"/>
       <c r="K121" s="21"/>
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
       <c r="N121" s="21"/>
     </row>
-    <row r="122" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J122" s="21"/>
       <c r="K122" s="21"/>
       <c r="L122" s="20"/>
       <c r="M122" s="20"/>
       <c r="N122" s="21"/>
     </row>
-    <row r="123" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J123" s="21"/>
       <c r="K123" s="21"/>
       <c r="L123" s="20"/>
       <c r="M123" s="20"/>
       <c r="N123" s="21"/>
     </row>
-    <row r="124" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J124" s="21"/>
       <c r="K124" s="21"/>
       <c r="L124" s="20"/>
       <c r="M124" s="20"/>
       <c r="N124" s="21"/>
     </row>
-    <row r="125" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="10:14" ht="15" x14ac:dyDescent="0.25">
       <c r="J125" s="21"/>
       <c r="K125" s="21"/>
       <c r="L125" s="20"/>
       <c r="M125" s="20"/>
       <c r="N125" s="21"/>
     </row>
-    <row r="126" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="J126" s="21"/>
-      <c r="K126" s="21"/>
-      <c r="L126" s="20"/>
-      <c r="M126" s="20"/>
-      <c r="N126" s="21"/>
-    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A99:C99"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -1,32 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfa\Documents\Data Engineer\Projekt\BackZeit\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC9D123-35EB-4D62-99C3-D9FCD167D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="3.NF" sheetId="1" r:id="rId1"/>
-    <sheet name="Bäckereikette" sheetId="2" r:id="rId2"/>
+    <sheet name="3.NF" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Bäckereikette" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -35,329 +21,334 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="101">
-  <si>
-    <t>Filiale</t>
-  </si>
-  <si>
-    <t>Verkauf</t>
-  </si>
-  <si>
-    <t>Verkäufer</t>
-  </si>
-  <si>
-    <t>Mitarbeiter</t>
-  </si>
-  <si>
-    <t>Produkt</t>
-  </si>
-  <si>
-    <t>Kategorie</t>
-  </si>
-  <si>
-    <t>Rezept</t>
-  </si>
-  <si>
-    <t>Zutaten</t>
-  </si>
-  <si>
-    <t>beinhaltet</t>
-  </si>
-  <si>
-    <t>wird verkauft</t>
-  </si>
-  <si>
-    <t>arbeitet in</t>
-  </si>
-  <si>
-    <t>FilialID</t>
-  </si>
-  <si>
-    <t>Zeitpunkt</t>
-  </si>
-  <si>
-    <t>VerkäuferID</t>
-  </si>
-  <si>
-    <t>MitarbeiterID</t>
-  </si>
-  <si>
-    <t>ProduktID</t>
-  </si>
-  <si>
-    <t>KategorieID</t>
-  </si>
-  <si>
-    <t>ZutatID</t>
-  </si>
-  <si>
-    <t>Filialname</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Bruttopreis</t>
-  </si>
-  <si>
-    <t>Version</t>
-  </si>
-  <si>
-    <t>Adresse</t>
-  </si>
-  <si>
-    <t>Zahlart</t>
-  </si>
-  <si>
-    <t>Geschlecht</t>
-  </si>
-  <si>
-    <t>Nettopreis</t>
-  </si>
-  <si>
-    <t>Zubereitungsdauer</t>
-  </si>
-  <si>
-    <t>Allergen</t>
-  </si>
-  <si>
-    <t>Datum</t>
-  </si>
-  <si>
-    <t>Stromkosten</t>
-  </si>
-  <si>
-    <t>Stunden/Woche</t>
-  </si>
-  <si>
-    <t>ProduktName</t>
-  </si>
-  <si>
-    <t>gültig_bis</t>
-  </si>
-  <si>
-    <t>PreisProkg</t>
-  </si>
-  <si>
-    <t>Menge</t>
-  </si>
-  <si>
-    <t>Schichtende</t>
-  </si>
-  <si>
-    <t>Heizkosten</t>
-  </si>
-  <si>
-    <t>Kündigungsdatum</t>
-  </si>
-  <si>
-    <t>gültig_ab</t>
-  </si>
-  <si>
-    <t>Bezeichnung</t>
-  </si>
-  <si>
-    <t>Schichtbeginn</t>
-  </si>
-  <si>
-    <t>Kaltmiete</t>
-  </si>
-  <si>
-    <t>Gehalt/Stunde</t>
-  </si>
-  <si>
-    <t>Backzeit</t>
-  </si>
-  <si>
-    <t>sonstNebenkosten</t>
-  </si>
-  <si>
-    <t>Einstellungsdatum</t>
-  </si>
-  <si>
-    <t>Autor</t>
-  </si>
-  <si>
-    <t>qm</t>
-  </si>
-  <si>
-    <t>Telefonnummer</t>
-  </si>
-  <si>
-    <t>Stückzahl</t>
-  </si>
-  <si>
-    <t>Arbeitsbereich</t>
-  </si>
-  <si>
-    <t>AdresseID</t>
-  </si>
-  <si>
-    <t>Straße</t>
-  </si>
-  <si>
-    <t>PLZ</t>
-  </si>
-  <si>
-    <t>Ort</t>
-  </si>
-  <si>
-    <t>Hausnummer</t>
-  </si>
-  <si>
-    <t>char</t>
-  </si>
-  <si>
-    <t>tinyint</t>
-  </si>
-  <si>
-    <t>PreisProKg</t>
-  </si>
-  <si>
-    <t>GrößeInQm</t>
-  </si>
-  <si>
-    <t>Relation</t>
-  </si>
-  <si>
-    <t>Feldname</t>
-  </si>
-  <si>
-    <t>Datentyp</t>
-  </si>
-  <si>
-    <t>Länge /
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="102">
+  <si>
+    <t xml:space="preserve">Filiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkauf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verkäufer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitarbeiter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kategorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zutaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beinhaltet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wird verkauft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arbeitet in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FilialID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeitpunkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VerkäuferID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MitarbeiterID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProduktID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KategorieID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZutatID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filialname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bruttopreis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LagerkostenProg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adresse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zahlart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geschlecht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nettopreis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zubereitungsdauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allergen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stromkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stunden/Woche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProduktName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gültig_bis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreisProkg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schichtende</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heizkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kündigungsdatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gültig_ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezeichnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schichtbeginn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltmiete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehalt/Stunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backzeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sonstNebenkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einstellungsdatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telefonnummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stückzahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeitsbereich</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AdresseID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straße</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hausnummer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreisProKg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GrößeInQm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feldname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datentyp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Länge /
 Genauigkeit</t>
   </si>
   <si>
-    <t>Storage Bytes
+    <t xml:space="preserve">Storage Bytes
 (je Datensatz)</t>
   </si>
   <si>
-    <t>PK</t>
-  </si>
-  <si>
-    <t>FK</t>
-  </si>
-  <si>
-    <t>IDENTITY</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Computed</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>Unique</t>
-  </si>
-  <si>
-    <t>NOT NULL</t>
-  </si>
-  <si>
-    <t>CHECK</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>nvarchar</t>
-  </si>
-  <si>
-    <t>Decimal(7,2)</t>
-  </si>
-  <si>
-    <t>datetime2</t>
-  </si>
-  <si>
-    <t>StundenProWoche</t>
-  </si>
-  <si>
-    <t>Decimal(4,2)</t>
-  </si>
-  <si>
-    <t>GehaltProStunde</t>
-  </si>
-  <si>
-    <t>smallint</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>Decimal(5,2)</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>varchar</t>
-  </si>
-  <si>
-    <t>Speicherbedarfshochrechnung (Relationen)</t>
-  </si>
-  <si>
-    <t>Bytes je Datensatz werden automatisch anhand des Relation-Namens aus Tabelle Speicherbedarfsermittlung summiert</t>
-  </si>
-  <si>
-    <t>Relationen-Übersicht (Anz. DS ist je Relation unterschiedlich)</t>
-  </si>
-  <si>
-    <t>Anz. DS 
+    <t xml:space="preserve">PK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDENTITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT NULL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nvarchar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decimal(7,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">datetime2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">char</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StundenProWoche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decimal(4,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GehaltProStunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smallint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tinyint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decimal(5,2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">varchar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speicherbedarfshochrechnung (Relationen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bytes je Datensatz werden automatisch anhand des Relation-Namens aus Tabelle Speicherbedarfsermittlung summiert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relationen-Übersicht (Anz. DS ist je Relation unterschiedlich)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anz. DS 
 Bestand</t>
   </si>
   <si>
-    <t>Anz. DS 
+    <t xml:space="preserve">Anz. DS 
 Zuwachs (1 J.)</t>
   </si>
   <si>
-    <t>Gesamt:
+    <t xml:space="preserve">Gesamt:
 DS</t>
   </si>
   <si>
-    <t>Bytes je 
+    <t xml:space="preserve">Bytes je 
 Datensatz (1 DS)</t>
   </si>
   <si>
-    <t>Speicherbedarf
+    <t xml:space="preserve">Speicherbedarf
 gesamt (Bytes)</t>
   </si>
   <si>
-    <t>KB (1 KB 
+    <t xml:space="preserve">KB (1 KB 
 = 1024 Byte)</t>
   </si>
   <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>GB</t>
-  </si>
-  <si>
-    <t>Gesamt (alle Relationen)</t>
-  </si>
-  <si>
-    <t>Aufschlag für Unvorhergesehenes
+    <t xml:space="preserve">MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamt (alle Relationen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufschlag für Unvorhergesehenes
 (ohnehin Reserve vorhanden, da der Füllgrad von varchar geschätzt nur etwa 40% betragen wird</t>
-  </si>
-  <si>
-    <t>LagerkostenProg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-    <numFmt numFmtId="165" formatCode="0.00\ %"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00E+00"/>
+    <numFmt numFmtId="167" formatCode="0.00\ %"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
@@ -365,14 +356,29 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -386,84 +392,96 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFBFBFBF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFF6600"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="14"/>
       <color rgb="FF2F5496"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF2F5496"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFBFBFBF"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFFF6600"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -500,14 +518,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="hair">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -523,108 +541,225 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="46">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -683,29 +818,13 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2F5496"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
@@ -747,14 +866,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="DejaVu Sans"/>
-        <a:cs typeface="DejaVu Sans"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -807,24 +926,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:L32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -894,7 +1014,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -917,7 +1037,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>21</v>
@@ -929,26 +1049,26 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -957,124 +1077,124 @@
         <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1083,18 +1203,18 @@
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1103,7 +1223,7 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1138,10 +1258,10 @@
         <v>10</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -1175,11 +1295,11 @@
       <c r="K20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
@@ -1202,7 +1322,7 @@
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>21</v>
@@ -1214,29 +1334,29 @@
         <v>13</v>
       </c>
       <c r="L21" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
@@ -1245,133 +1365,133 @@
         <v>15</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="8"/>
       <c r="G26" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1380,18 +1500,18 @@
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="9"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="10"/>
@@ -1400,16 +1520,17 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="10"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;12Page &amp;P</oddFooter>
   </headerFooter>
@@ -1417,22 +1538,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:N125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="4" customWidth="1"/>
-    <col min="7" max="7" width="20" style="4" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="20" style="4" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="18.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="17.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="6.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="6.1"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="12.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1467,10 +1592,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1505,10 +1630,10 @@
         <v>11</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1531,7 +1656,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>21</v>
@@ -1543,28 +1668,28 @@
         <v>13</v>
       </c>
       <c r="L3" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -1573,176 +1698,168 @@
         <v>15</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10"/>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="4"/>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11"/>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="D14"/>
-    </row>
-    <row r="17" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="C17" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="H17" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="I17" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="J17" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="K17" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="L17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="M17" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="M17" s="13" t="s">
+      <c r="N17" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="N17" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
         <v>0</v>
       </c>
@@ -1750,30 +1867,28 @@
         <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="19">
+        <v>73</v>
+      </c>
+      <c r="E18" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="20"/>
-      <c r="H18" s="20">
+      <c r="H18" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
-      <c r="L18" s="20">
-        <v>1</v>
-      </c>
-      <c r="M18" s="20">
+      <c r="L18" s="20"/>
+      <c r="M18" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="21"/>
     </row>
-    <row r="19" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="16" t="s">
         <v>0</v>
       </c>
@@ -1781,12 +1896,12 @@
         <v>18</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="22">
+        <v>74</v>
+      </c>
+      <c r="D19" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="19" t="n">
         <v>102</v>
       </c>
       <c r="F19" s="20"/>
@@ -1795,33 +1910,33 @@
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
-      <c r="L19" s="20">
-        <v>1</v>
-      </c>
-      <c r="M19" s="20">
+      <c r="L19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="21"/>
     </row>
-    <row r="20" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="22"/>
-      <c r="E20" s="19">
+      <c r="E20" s="19" t="n">
         <v>4</v>
       </c>
       <c r="F20" s="20"/>
-      <c r="G20" s="20">
-        <v>1</v>
-      </c>
-      <c r="H20" s="20">
+      <c r="G20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I20" s="21"/>
@@ -1831,20 +1946,20 @@
       <c r="M20" s="20"/>
       <c r="N20" s="21"/>
     </row>
-    <row r="21" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="22">
+        <v>75</v>
+      </c>
+      <c r="D21" s="22" t="n">
         <v>7.2</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F21" s="20"/>
@@ -1854,25 +1969,25 @@
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
       <c r="L21" s="20"/>
-      <c r="M21" s="20">
+      <c r="M21" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="21"/>
     </row>
-    <row r="22" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="22">
+        <v>75</v>
+      </c>
+      <c r="D22" s="22" t="n">
         <v>7.2</v>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="20"/>
@@ -1882,25 +1997,25 @@
       <c r="J22" s="21"/>
       <c r="K22" s="21"/>
       <c r="L22" s="20"/>
-      <c r="M22" s="20">
+      <c r="M22" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="21"/>
     </row>
-    <row r="23" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="22">
+        <v>75</v>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>7.2</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="19" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="20"/>
@@ -1909,25 +2024,25 @@
       <c r="J23" s="21"/>
       <c r="K23" s="21"/>
       <c r="L23" s="20"/>
-      <c r="M23" s="20">
+      <c r="M23" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="21"/>
     </row>
-    <row r="24" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="22">
+        <v>75</v>
+      </c>
+      <c r="D24" s="22" t="n">
         <v>7.2</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="20"/>
@@ -1937,25 +2052,25 @@
       <c r="J24" s="21"/>
       <c r="K24" s="21"/>
       <c r="L24" s="20"/>
-      <c r="M24" s="20">
+      <c r="M24" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="21"/>
     </row>
-    <row r="25" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="4">
+        <v>75</v>
+      </c>
+      <c r="D25" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F25" s="20"/>
@@ -1965,12 +2080,12 @@
       <c r="J25" s="21"/>
       <c r="K25" s="21"/>
       <c r="L25" s="20"/>
-      <c r="M25" s="20">
+      <c r="M25" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="21"/>
     </row>
-    <row r="26" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
         <v>1</v>
       </c>
@@ -1978,26 +2093,28 @@
         <v>12</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="19">
+        <v>76</v>
+      </c>
+      <c r="E26" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>49</v>
+      <c r="F26" s="20" t="n">
+        <v>1</v>
       </c>
       <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
+      <c r="H26" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="I26" s="21"/>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
       <c r="L26" s="20"/>
-      <c r="M26" s="20">
+      <c r="M26" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="21"/>
     </row>
-    <row r="27" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
         <v>1</v>
       </c>
@@ -2005,43 +2122,43 @@
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="24">
+        <v>73</v>
+      </c>
+      <c r="E27" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="20">
-        <v>1</v>
-      </c>
-      <c r="G27" s="20">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20">
+      <c r="F27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
       <c r="L27" s="20"/>
-      <c r="M27" s="20">
+      <c r="M27" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="21"/>
     </row>
-    <row r="28" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
         <v>1</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="E28" s="19">
+        <v>77</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="20"/>
@@ -2051,12 +2168,12 @@
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
       <c r="L28" s="20"/>
-      <c r="M28" s="20">
+      <c r="M28" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="21"/>
     </row>
-    <row r="29" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
         <v>1</v>
       </c>
@@ -2064,27 +2181,27 @@
         <v>13</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="25">
+        <v>73</v>
+      </c>
+      <c r="E29" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G29" s="20">
-        <v>1</v>
-      </c>
-      <c r="H29" s="9">
+      <c r="G29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="21"/>
       <c r="J29" s="21"/>
       <c r="K29" s="21"/>
       <c r="L29" s="20"/>
-      <c r="M29" s="20">
+      <c r="M29" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="21"/>
     </row>
-    <row r="30" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
         <v>2</v>
       </c>
@@ -2092,30 +2209,28 @@
         <v>13</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E30" s="24">
+        <v>73</v>
+      </c>
+      <c r="E30" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="20"/>
-      <c r="H30" s="20">
+      <c r="H30" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="21"/>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
-      <c r="L30" s="20">
-        <v>1</v>
-      </c>
-      <c r="M30" s="20">
+      <c r="L30" s="20"/>
+      <c r="M30" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="21"/>
     </row>
-    <row r="31" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
         <v>2</v>
       </c>
@@ -2123,26 +2238,26 @@
         <v>14</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="25">
+        <v>73</v>
+      </c>
+      <c r="E31" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="21"/>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
-      <c r="L31" s="20">
-        <v>1</v>
-      </c>
-      <c r="M31" s="20">
+      <c r="L31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="21"/>
     </row>
-    <row r="32" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
         <v>3</v>
       </c>
@@ -2150,30 +2265,27 @@
         <v>14</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="24">
+        <v>73</v>
+      </c>
+      <c r="E32" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="20"/>
-      <c r="H32" s="20">
+      <c r="H32" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="21"/>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
-      <c r="L32" s="9">
-        <v>1</v>
-      </c>
-      <c r="M32" s="20">
+      <c r="M32" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="21"/>
     </row>
-    <row r="33" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
         <v>3</v>
       </c>
@@ -2181,13 +2293,13 @@
         <v>19</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="22">
+        <v>74</v>
+      </c>
+      <c r="D33" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E33" s="19">
-        <f>2*D33+2</f>
+      <c r="E33" s="19" t="n">
+        <f aca="false">2*D33+2</f>
         <v>102</v>
       </c>
       <c r="F33" s="20"/>
@@ -2196,25 +2308,25 @@
       <c r="I33" s="21"/>
       <c r="J33" s="21"/>
       <c r="K33" s="21"/>
-      <c r="M33" s="20">
+      <c r="M33" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="21"/>
     </row>
-    <row r="34" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="22">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19">
+        <v>77</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="20"/>
@@ -2226,7 +2338,7 @@
       <c r="M34" s="20"/>
       <c r="N34" s="21"/>
     </row>
-    <row r="35" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="23" t="s">
         <v>3</v>
       </c>
@@ -2236,10 +2348,10 @@
       <c r="C35" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F35" s="20"/>
@@ -2248,22 +2360,22 @@
       <c r="I35" s="21"/>
       <c r="J35" s="21"/>
       <c r="K35" s="21"/>
-      <c r="M35" s="20">
+      <c r="M35" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="21"/>
     </row>
-    <row r="36" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" s="19">
+        <v>76</v>
+      </c>
+      <c r="E36" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F36" s="20"/>
@@ -2275,7 +2387,7 @@
       <c r="M36" s="20"/>
       <c r="N36" s="21"/>
     </row>
-    <row r="37" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
         <v>3</v>
       </c>
@@ -2285,10 +2397,10 @@
       <c r="C37" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="E37" s="19">
+      <c r="E37" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F37" s="20"/>
@@ -2297,22 +2409,22 @@
       <c r="I37" s="21"/>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
-      <c r="M37" s="20">
+      <c r="M37" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="21"/>
     </row>
-    <row r="38" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E38" s="19">
+        <v>76</v>
+      </c>
+      <c r="E38" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F38" s="20"/>
@@ -2321,26 +2433,26 @@
       <c r="I38" s="21"/>
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
-      <c r="M38" s="20">
+      <c r="M38" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="21"/>
     </row>
-    <row r="39" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="4">
+        <v>74</v>
+      </c>
+      <c r="D39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E39" s="19">
-        <f>2*D39+2</f>
+      <c r="E39" s="19" t="n">
+        <f aca="false">2*D39+2</f>
         <v>26</v>
       </c>
       <c r="F39" s="20"/>
@@ -2349,55 +2461,53 @@
       <c r="I39" s="21"/>
       <c r="J39" s="21"/>
       <c r="K39" s="21"/>
-      <c r="M39" s="20">
+      <c r="M39" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="21"/>
     </row>
-    <row r="40" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="22"/>
-      <c r="E40" s="19">
+      <c r="E40" s="19" t="n">
         <v>4</v>
       </c>
       <c r="F40" s="20"/>
-      <c r="G40" s="20">
-        <v>1</v>
-      </c>
-      <c r="H40" s="20">
-        <v>1</v>
-      </c>
+      <c r="G40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20"/>
       <c r="I40" s="21"/>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
-      <c r="M40" s="20">
+      <c r="M40" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="21"/>
     </row>
-    <row r="41" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="23" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D41" s="22">
+        <v>74</v>
+      </c>
+      <c r="D41" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="E41" s="19">
-        <f>2*D41+2</f>
+      <c r="E41" s="19" t="n">
+        <f aca="false">2*D41+2</f>
         <v>42</v>
       </c>
       <c r="F41" s="20"/>
@@ -2406,12 +2516,12 @@
       <c r="I41" s="21"/>
       <c r="J41" s="21"/>
       <c r="K41" s="21"/>
-      <c r="M41" s="20">
+      <c r="M41" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="21"/>
     </row>
-    <row r="42" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="23" t="s">
         <v>4</v>
       </c>
@@ -2419,28 +2529,25 @@
         <v>15</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E42" s="24">
+        <v>73</v>
+      </c>
+      <c r="E42" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="20"/>
-      <c r="H42" s="20">
+      <c r="H42" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
-      <c r="L42" s="9">
-        <v>1</v>
-      </c>
       <c r="M42" s="20"/>
       <c r="N42" s="21"/>
     </row>
-    <row r="43" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
         <v>4</v>
       </c>
@@ -2450,10 +2557,10 @@
       <c r="C43" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F43" s="20"/>
@@ -2462,25 +2569,25 @@
       <c r="I43" s="21"/>
       <c r="J43" s="21"/>
       <c r="K43" s="21"/>
-      <c r="M43" s="20">
+      <c r="M43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="21"/>
     </row>
-    <row r="44" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="22" t="n">
         <v>4.2</v>
       </c>
-      <c r="E44" s="19">
+      <c r="E44" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F44" s="20"/>
@@ -2490,26 +2597,26 @@
       <c r="J44" s="21"/>
       <c r="K44" s="21"/>
       <c r="L44" s="20"/>
-      <c r="M44" s="20">
+      <c r="M44" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N44" s="21"/>
     </row>
-    <row r="45" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="22">
+        <v>74</v>
+      </c>
+      <c r="D45" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E45" s="19">
-        <f>2*D45+2</f>
+      <c r="E45" s="19" t="n">
+        <f aca="false">2*D45+2</f>
         <v>102</v>
       </c>
       <c r="F45" s="20"/>
@@ -2518,15 +2625,15 @@
       <c r="I45" s="21"/>
       <c r="J45" s="21"/>
       <c r="K45" s="21"/>
-      <c r="L45" s="20">
-        <v>1</v>
-      </c>
-      <c r="M45" s="20">
+      <c r="L45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="21"/>
     </row>
-    <row r="46" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="s">
         <v>4</v>
       </c>
@@ -2534,28 +2641,28 @@
         <v>16</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E46" s="25">
+        <v>73</v>
+      </c>
+      <c r="E46" s="25" t="n">
         <v>4</v>
       </c>
       <c r="F46" s="20"/>
-      <c r="G46" s="20">
-        <v>1</v>
-      </c>
-      <c r="H46" s="20">
+      <c r="G46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I46" s="21"/>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
       <c r="L46" s="20"/>
-      <c r="M46" s="20">
+      <c r="M46" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N46" s="21"/>
     </row>
-    <row r="47" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="s">
         <v>5</v>
       </c>
@@ -2563,30 +2670,28 @@
         <v>16</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="25">
+        <v>73</v>
+      </c>
+      <c r="E47" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="20"/>
-      <c r="H47" s="20">
+      <c r="H47" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I47" s="21"/>
       <c r="J47" s="21"/>
       <c r="K47" s="21"/>
-      <c r="L47" s="20">
-        <v>1</v>
-      </c>
-      <c r="M47" s="20">
+      <c r="L47" s="20"/>
+      <c r="M47" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N47" s="21"/>
     </row>
-    <row r="48" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
         <v>5</v>
       </c>
@@ -2594,13 +2699,13 @@
         <v>19</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="22">
+        <v>74</v>
+      </c>
+      <c r="D48" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E48" s="19">
-        <f>2*D48+2</f>
+      <c r="E48" s="19" t="n">
+        <f aca="false">2*D48+2</f>
         <v>102</v>
       </c>
       <c r="F48" s="20"/>
@@ -2609,15 +2714,15 @@
       <c r="I48" s="21"/>
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
-      <c r="L48" s="20">
-        <v>1</v>
-      </c>
-      <c r="M48" s="20">
+      <c r="L48" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N48" s="21"/>
     </row>
-    <row r="49" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="23" t="s">
         <v>6</v>
       </c>
@@ -2625,30 +2730,30 @@
         <v>15</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E49" s="25">
+        <v>73</v>
+      </c>
+      <c r="E49" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="20">
-        <v>1</v>
-      </c>
-      <c r="G49" s="20">
-        <v>1</v>
-      </c>
-      <c r="H49" s="20">
+      <c r="F49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I49" s="21"/>
       <c r="J49" s="21"/>
       <c r="K49" s="21"/>
       <c r="L49" s="20"/>
-      <c r="M49" s="20">
+      <c r="M49" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N49" s="21"/>
     </row>
-    <row r="50" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="s">
         <v>6</v>
       </c>
@@ -2659,39 +2764,39 @@
         <v>81</v>
       </c>
       <c r="D50" s="22"/>
-      <c r="E50" s="19">
+      <c r="E50" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="20"/>
-      <c r="H50" s="20">
+      <c r="H50" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I50" s="21"/>
       <c r="J50" s="21"/>
       <c r="K50" s="21"/>
       <c r="L50" s="20"/>
-      <c r="M50" s="20">
+      <c r="M50" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N50" s="21"/>
     </row>
-    <row r="51" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="22" t="n">
         <v>4.2</v>
       </c>
-      <c r="E51" s="19">
+      <c r="E51" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F51" s="20"/>
@@ -2701,23 +2806,23 @@
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
       <c r="L51" s="20"/>
-      <c r="M51" s="20">
+      <c r="M51" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N51" s="21"/>
     </row>
-    <row r="52" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D52" s="22"/>
-      <c r="E52" s="19">
+      <c r="E52" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F52" s="20"/>
@@ -2730,18 +2835,18 @@
       <c r="M52" s="20"/>
       <c r="N52" s="21"/>
     </row>
-    <row r="53" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" s="22"/>
-      <c r="E53" s="19">
+      <c r="E53" s="19" t="n">
         <v>8</v>
       </c>
       <c r="F53" s="20"/>
@@ -2754,20 +2859,20 @@
       <c r="M53" s="20"/>
       <c r="N53" s="21"/>
     </row>
-    <row r="54" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="22" t="n">
         <v>4.2</v>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F54" s="20"/>
@@ -2777,26 +2882,26 @@
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
       <c r="L54" s="20"/>
-      <c r="M54" s="20">
+      <c r="M54" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N54" s="21"/>
     </row>
-    <row r="55" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D55" s="22">
+        <v>74</v>
+      </c>
+      <c r="D55" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E55" s="19">
-        <f>2*D55+2</f>
+      <c r="E55" s="19" t="n">
+        <f aca="false">2*D55+2</f>
         <v>102</v>
       </c>
       <c r="F55" s="20"/>
@@ -2806,23 +2911,23 @@
       <c r="J55" s="21"/>
       <c r="K55" s="21"/>
       <c r="L55" s="20"/>
-      <c r="M55" s="20">
+      <c r="M55" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N55" s="21"/>
     </row>
-    <row r="56" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="23" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="D56" s="22"/>
-      <c r="E56" s="19">
+      <c r="E56" s="19" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="20"/>
@@ -2835,7 +2940,7 @@
       <c r="M56" s="20"/>
       <c r="N56" s="21"/>
     </row>
-    <row r="57" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="23" t="s">
         <v>7</v>
       </c>
@@ -2843,43 +2948,41 @@
         <v>17</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E57" s="25">
+        <v>73</v>
+      </c>
+      <c r="E57" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="20"/>
-      <c r="H57" s="20">
+      <c r="H57" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="21"/>
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
-      <c r="L57" s="20">
-        <v>1</v>
-      </c>
-      <c r="M57" s="20">
+      <c r="L57" s="20"/>
+      <c r="M57" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N57" s="21"/>
     </row>
-    <row r="58" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="22">
+      <c r="D58" s="22" t="n">
         <v>4.2</v>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="20"/>
@@ -2889,20 +2992,20 @@
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
       <c r="L58" s="20"/>
-      <c r="M58" s="20">
+      <c r="M58" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N58" s="21"/>
     </row>
-    <row r="59" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D59" s="22"/>
       <c r="E59" s="19"/>
@@ -2916,20 +3019,20 @@
       <c r="M59" s="20"/>
       <c r="N59" s="21"/>
     </row>
-    <row r="60" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D60" s="22">
+        <v>75</v>
+      </c>
+      <c r="D60" s="22" t="n">
         <v>7.2</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F60" s="20"/>
@@ -2939,26 +3042,26 @@
       <c r="J60" s="21"/>
       <c r="K60" s="21"/>
       <c r="L60" s="20"/>
-      <c r="M60" s="20">
+      <c r="M60" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N60" s="21"/>
     </row>
-    <row r="61" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="23" t="s">
         <v>7</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D61" s="22">
+        <v>74</v>
+      </c>
+      <c r="D61" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E61" s="19">
-        <f>2*D642+2</f>
+      <c r="E61" s="19" t="n">
+        <f aca="false">2*D642+2</f>
         <v>2</v>
       </c>
       <c r="F61" s="20"/>
@@ -2967,15 +3070,15 @@
       <c r="I61" s="21"/>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
-      <c r="L61" s="20">
-        <v>1</v>
-      </c>
-      <c r="M61" s="20">
+      <c r="L61" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N61" s="21"/>
     </row>
-    <row r="62" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="s">
         <v>8</v>
       </c>
@@ -2983,30 +3086,30 @@
         <v>17</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="25">
+        <v>73</v>
+      </c>
+      <c r="E62" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F62" s="20">
-        <v>1</v>
-      </c>
-      <c r="G62" s="20">
-        <v>1</v>
-      </c>
-      <c r="H62" s="20">
+      <c r="F62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I62" s="21"/>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
       <c r="L62" s="20"/>
-      <c r="M62" s="20">
+      <c r="M62" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N62" s="21"/>
     </row>
-    <row r="63" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="23" t="s">
         <v>8</v>
       </c>
@@ -3016,28 +3119,28 @@
       <c r="C63" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="20">
-        <v>1</v>
-      </c>
-      <c r="G63" s="20">
-        <v>1</v>
-      </c>
-      <c r="H63" s="20">
+      <c r="F63" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I63" s="21"/>
       <c r="J63" s="21"/>
       <c r="K63" s="21"/>
       <c r="L63" s="20"/>
-      <c r="M63" s="20">
+      <c r="M63" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N63" s="21"/>
     </row>
-    <row r="64" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="23" t="s">
         <v>8</v>
       </c>
@@ -3045,40 +3148,40 @@
         <v>15</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E64" s="25">
+        <v>73</v>
+      </c>
+      <c r="E64" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="20">
-        <v>1</v>
-      </c>
-      <c r="G64" s="20">
-        <v>1</v>
-      </c>
-      <c r="H64" s="20">
+      <c r="F64" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I64" s="21"/>
       <c r="J64" s="21"/>
       <c r="K64" s="21"/>
       <c r="L64" s="20"/>
-      <c r="M64" s="20">
+      <c r="M64" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N64" s="21"/>
     </row>
-    <row r="65" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="23" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C65" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="25" t="n">
         <v>2</v>
       </c>
       <c r="F65" s="20"/>
@@ -3088,12 +3191,12 @@
       <c r="J65" s="21"/>
       <c r="K65" s="21"/>
       <c r="L65" s="20"/>
-      <c r="M65" s="20">
+      <c r="M65" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N65" s="21"/>
     </row>
-    <row r="66" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="23" t="s">
         <v>9</v>
       </c>
@@ -3101,30 +3204,30 @@
         <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" s="25">
+        <v>73</v>
+      </c>
+      <c r="E66" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="20">
-        <v>1</v>
-      </c>
-      <c r="G66" s="20">
-        <v>1</v>
-      </c>
-      <c r="H66" s="20">
+      <c r="F66" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I66" s="21"/>
       <c r="J66" s="21"/>
       <c r="K66" s="21"/>
       <c r="L66" s="20"/>
-      <c r="M66" s="20">
+      <c r="M66" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N66" s="21"/>
     </row>
-    <row r="67" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="23" t="s">
         <v>9</v>
       </c>
@@ -3132,31 +3235,31 @@
         <v>12</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="22"/>
-      <c r="E67" s="19">
+      <c r="E67" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="F67" s="20">
-        <v>1</v>
-      </c>
-      <c r="G67" s="20">
-        <v>1</v>
-      </c>
-      <c r="H67" s="20">
+      <c r="F67" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="21"/>
       <c r="J67" s="21"/>
       <c r="K67" s="21"/>
       <c r="L67" s="20"/>
-      <c r="M67" s="20">
+      <c r="M67" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N67" s="21"/>
     </row>
-    <row r="68" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="23" t="s">
         <v>9</v>
       </c>
@@ -3164,44 +3267,44 @@
         <v>15</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D68" s="22"/>
-      <c r="E68" s="19">
+      <c r="E68" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="20">
-        <v>1</v>
-      </c>
-      <c r="G68" s="20">
-        <v>1</v>
-      </c>
-      <c r="H68" s="20">
+      <c r="F68" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I68" s="21"/>
       <c r="J68" s="21"/>
       <c r="K68" s="21"/>
       <c r="L68" s="20"/>
-      <c r="M68" s="20">
+      <c r="M68" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N68" s="21"/>
     </row>
-    <row r="69" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="23" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D69" s="22">
+        <v>84</v>
+      </c>
+      <c r="D69" s="22" t="n">
         <v>5.2</v>
       </c>
-      <c r="E69" s="19">
+      <c r="E69" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F69" s="20"/>
@@ -3211,12 +3314,12 @@
       <c r="J69" s="21"/>
       <c r="K69" s="21"/>
       <c r="L69" s="20"/>
-      <c r="M69" s="20">
+      <c r="M69" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N69" s="21"/>
     </row>
-    <row r="70" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="23" t="s">
         <v>10</v>
       </c>
@@ -3224,31 +3327,31 @@
         <v>11</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D70" s="22"/>
-      <c r="E70" s="19">
+      <c r="E70" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="20">
-        <v>1</v>
-      </c>
-      <c r="G70" s="20">
-        <v>1</v>
-      </c>
-      <c r="H70" s="20">
+      <c r="F70" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I70" s="21"/>
       <c r="J70" s="21"/>
       <c r="K70" s="21"/>
       <c r="L70" s="20"/>
-      <c r="M70" s="20">
+      <c r="M70" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N70" s="21"/>
     </row>
-    <row r="71" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="23" t="s">
         <v>10</v>
       </c>
@@ -3256,42 +3359,42 @@
         <v>13</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D71" s="22"/>
-      <c r="E71" s="19">
+      <c r="E71" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="20">
-        <v>1</v>
-      </c>
-      <c r="G71" s="20">
-        <v>1</v>
-      </c>
-      <c r="H71" s="20">
+      <c r="F71" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I71" s="21"/>
       <c r="J71" s="21"/>
       <c r="K71" s="21"/>
       <c r="L71" s="20"/>
-      <c r="M71" s="20">
+      <c r="M71" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N71" s="21"/>
     </row>
-    <row r="72" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D72" s="22"/>
-      <c r="E72" s="19">
+      <c r="E72" s="19" t="n">
         <v>3</v>
       </c>
       <c r="F72" s="20"/>
@@ -3301,23 +3404,23 @@
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
       <c r="L72" s="20"/>
-      <c r="M72" s="20">
+      <c r="M72" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N72" s="21"/>
     </row>
-    <row r="73" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C73" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D73" s="22"/>
-      <c r="E73" s="19">
+      <c r="E73" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F73" s="20"/>
@@ -3327,23 +3430,23 @@
       <c r="J73" s="21"/>
       <c r="K73" s="21"/>
       <c r="L73" s="20"/>
-      <c r="M73" s="20">
+      <c r="M73" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N73" s="21"/>
     </row>
-    <row r="74" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="s">
         <v>10</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D74" s="22"/>
-      <c r="E74" s="19">
+      <c r="E74" s="19" t="n">
         <v>5</v>
       </c>
       <c r="F74" s="20"/>
@@ -3353,58 +3456,55 @@
       <c r="J74" s="21"/>
       <c r="K74" s="21"/>
       <c r="L74" s="20"/>
-      <c r="M74" s="20">
+      <c r="M74" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N74" s="21"/>
     </row>
-    <row r="75" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" t="s">
-        <v>74</v>
-      </c>
-      <c r="D75"/>
-      <c r="E75" s="26">
+        <v>52</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="F75" s="20">
+      <c r="F75" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G75" s="20"/>
-      <c r="H75" s="20">
+      <c r="H75" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I75" s="21"/>
       <c r="J75" s="21"/>
       <c r="K75" s="21"/>
-      <c r="L75" s="20">
-        <v>1</v>
-      </c>
-      <c r="M75" s="20">
+      <c r="L75" s="20"/>
+      <c r="M75" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N75" s="21"/>
     </row>
-    <row r="76" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C76" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D76" s="22">
+        <v>74</v>
+      </c>
+      <c r="D76" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="E76" s="19">
-        <f>2*D76+2</f>
+      <c r="E76" s="19" t="n">
+        <f aca="false">2*D76+2</f>
         <v>102</v>
       </c>
       <c r="F76" s="20"/>
@@ -3414,25 +3514,25 @@
       <c r="J76" s="21"/>
       <c r="K76" s="21"/>
       <c r="L76" s="20"/>
-      <c r="M76" s="20">
+      <c r="M76" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N76" s="21"/>
     </row>
-    <row r="77" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D77" s="4">
+        <v>87</v>
+      </c>
+      <c r="D77" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E77" s="19">
+      <c r="E77" s="19" t="n">
         <v>7</v>
       </c>
       <c r="F77" s="20"/>
@@ -3442,26 +3542,26 @@
       <c r="J77" s="21"/>
       <c r="K77" s="21"/>
       <c r="L77" s="20"/>
-      <c r="M77" s="20">
+      <c r="M77" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N77" s="21"/>
     </row>
-    <row r="78" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D78" s="22">
+        <v>74</v>
+      </c>
+      <c r="D78" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="19">
-        <f>2*D78+2</f>
+      <c r="E78" s="19" t="n">
+        <f aca="false">2*D78+2</f>
         <v>6</v>
       </c>
       <c r="F78" s="20"/>
@@ -3471,26 +3571,26 @@
       <c r="J78" s="21"/>
       <c r="K78" s="21"/>
       <c r="L78" s="20"/>
-      <c r="M78" s="20">
+      <c r="M78" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N78" s="21"/>
     </row>
-    <row r="79" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D79" s="4">
+        <v>74</v>
+      </c>
+      <c r="D79" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E79" s="19">
-        <f>2*D79+2</f>
+      <c r="E79" s="19" t="n">
+        <f aca="false">2*D79+2</f>
         <v>16</v>
       </c>
       <c r="F79" s="20"/>
@@ -3500,17 +3600,17 @@
       <c r="J79" s="21"/>
       <c r="K79" s="21"/>
       <c r="L79" s="20"/>
-      <c r="M79" s="20">
+      <c r="M79" s="20" t="n">
         <v>1</v>
       </c>
       <c r="N79" s="21"/>
     </row>
-    <row r="80" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A80" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" s="42"/>
-      <c r="C80" s="27"/>
+    <row r="80" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="27"/>
+      <c r="C80" s="28"/>
       <c r="D80" s="21"/>
       <c r="E80" s="21"/>
       <c r="F80" s="21"/>
@@ -3523,30 +3623,30 @@
       <c r="M80" s="20"/>
       <c r="N80" s="21"/>
     </row>
-    <row r="81" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A81" s="43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="43"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="43"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="28"/>
-      <c r="H81" s="28"/>
-      <c r="I81" s="28"/>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
+      <c r="D81" s="29"/>
+      <c r="E81" s="29"/>
+      <c r="F81" s="29"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
       <c r="L81" s="20"/>
       <c r="M81" s="20"/>
       <c r="N81" s="21"/>
     </row>
-    <row r="82" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" s="44"/>
-      <c r="C82" s="29"/>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="31"/>
+      <c r="C82" s="32"/>
       <c r="D82" s="21"/>
       <c r="E82" s="21"/>
       <c r="F82" s="21"/>
@@ -3559,33 +3659,33 @@
       <c r="M82" s="20"/>
       <c r="N82" s="21"/>
     </row>
-    <row r="83" spans="1:14" ht="60" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C83" s="31" t="s">
+    <row r="83" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B83" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D83" s="32" t="s">
+      <c r="C83" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E83" s="32" t="s">
+      <c r="D83" s="35" t="s">
         <v>93</v>
       </c>
-      <c r="F83" s="32" t="s">
+      <c r="E83" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="G83" s="32" t="s">
+      <c r="F83" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="H83" s="32" t="s">
+      <c r="G83" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="I83" s="32" t="s">
+      <c r="H83" s="35" t="s">
         <v>97</v>
+      </c>
+      <c r="I83" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
@@ -3593,39 +3693,39 @@
       <c r="M83" s="20"/>
       <c r="N83" s="21"/>
     </row>
-    <row r="84" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="s">
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B84" s="4">
+      <c r="B84" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="D84" s="19">
-        <f t="shared" ref="D84:D95" si="0">B84+10*C84</f>
+      <c r="D84" s="19" t="n">
+        <f aca="false">B84+10*C84</f>
         <v>100</v>
       </c>
-      <c r="E84" s="19">
-        <f>SUM(E18:E25)</f>
+      <c r="E84" s="19" t="n">
+        <f aca="false">SUM(E18:E25)</f>
         <v>135</v>
       </c>
-      <c r="F84" s="19">
-        <f t="shared" ref="F84:F95" si="1">D84*E84</f>
+      <c r="F84" s="19" t="n">
+        <f aca="false">D84*E84</f>
         <v>13500</v>
       </c>
-      <c r="G84" s="34">
-        <f t="shared" ref="G84:I95" si="2">F84/1024</f>
+      <c r="G84" s="37" t="n">
+        <f aca="false">F84/1024</f>
         <v>13.18359375</v>
       </c>
-      <c r="H84" s="34">
-        <f t="shared" si="2"/>
-        <v>1.2874603271484375E-2</v>
-      </c>
-      <c r="I84" s="19">
-        <f t="shared" si="2"/>
-        <v>1.257285475730896E-5</v>
+      <c r="H84" s="37" t="n">
+        <f aca="false">G84/1024</f>
+        <v>0.0128746032714844</v>
+      </c>
+      <c r="I84" s="19" t="n">
+        <f aca="false">H84/1024</f>
+        <v>1.2572854757309E-005</v>
       </c>
       <c r="J84" s="21"/>
       <c r="K84" s="21"/>
@@ -3633,39 +3733,39 @@
       <c r="M84" s="20"/>
       <c r="N84" s="21"/>
     </row>
-    <row r="85" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A85" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B85" s="36">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="B85" s="39" t="n">
         <v>10000000</v>
       </c>
-      <c r="C85" s="36">
+      <c r="C85" s="39" t="n">
         <v>11000000</v>
       </c>
-      <c r="D85" s="19">
-        <f t="shared" si="0"/>
+      <c r="D85" s="19" t="n">
+        <f aca="false">B85+10*C85</f>
         <v>120000000</v>
       </c>
-      <c r="E85" s="19">
-        <f>SUM(E26:E29)</f>
+      <c r="E85" s="19" t="n">
+        <f aca="false">SUM(E26:E29)</f>
         <v>17</v>
       </c>
-      <c r="F85" s="19">
-        <f t="shared" si="1"/>
+      <c r="F85" s="19" t="n">
+        <f aca="false">D85*E85</f>
         <v>2040000000</v>
       </c>
-      <c r="G85" s="34">
-        <f t="shared" si="2"/>
+      <c r="G85" s="37" t="n">
+        <f aca="false">F85/1024</f>
         <v>1992187.5</v>
       </c>
-      <c r="H85" s="34">
-        <f t="shared" si="2"/>
+      <c r="H85" s="37" t="n">
+        <f aca="false">G85/1024</f>
         <v>1945.49560546875</v>
       </c>
-      <c r="I85" s="19">
-        <f t="shared" si="2"/>
-        <v>1.8998980522155762</v>
+      <c r="I85" s="19" t="n">
+        <f aca="false">H85/1024</f>
+        <v>1.89989805221558</v>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -3673,39 +3773,39 @@
       <c r="M85" s="20"/>
       <c r="N85" s="21"/>
     </row>
-    <row r="86" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A86" s="35" t="s">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B86" s="4">
+      <c r="B86" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="D86" s="19">
-        <f t="shared" si="0"/>
+      <c r="D86" s="19" t="n">
+        <f aca="false">B86+10*C86</f>
         <v>450</v>
       </c>
-      <c r="E86" s="19">
-        <f>SUM(E30:E31)</f>
+      <c r="E86" s="19" t="n">
+        <f aca="false">SUM(E30:E31)</f>
         <v>8</v>
       </c>
-      <c r="F86" s="19">
-        <f t="shared" si="1"/>
+      <c r="F86" s="19" t="n">
+        <f aca="false">D86*E86</f>
         <v>3600</v>
       </c>
-      <c r="G86" s="34">
-        <f t="shared" si="2"/>
+      <c r="G86" s="37" t="n">
+        <f aca="false">F86/1024</f>
         <v>3.515625</v>
       </c>
-      <c r="H86" s="34">
-        <f t="shared" si="2"/>
-        <v>3.4332275390625E-3</v>
-      </c>
-      <c r="I86" s="19">
-        <f t="shared" si="2"/>
-        <v>3.3527612686157227E-6</v>
+      <c r="H86" s="37" t="n">
+        <f aca="false">G86/1024</f>
+        <v>0.0034332275390625</v>
+      </c>
+      <c r="I86" s="19" t="n">
+        <f aca="false">H86/1024</f>
+        <v>3.35276126861572E-006</v>
       </c>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
@@ -3713,39 +3813,39 @@
       <c r="M86" s="20"/>
       <c r="N86" s="21"/>
     </row>
-    <row r="87" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A87" s="35" t="s">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B87" s="4">
+      <c r="B87" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="D87" s="19">
-        <f t="shared" si="0"/>
+      <c r="D87" s="19" t="n">
+        <f aca="false">B87+10*C87</f>
         <v>540</v>
       </c>
-      <c r="E87" s="19">
-        <f>SUM(E32:E41)</f>
+      <c r="E87" s="19" t="n">
+        <f aca="false">SUM(E32:E41)</f>
         <v>205</v>
       </c>
-      <c r="F87" s="19">
-        <f t="shared" si="1"/>
+      <c r="F87" s="19" t="n">
+        <f aca="false">D87*E87</f>
         <v>110700</v>
       </c>
-      <c r="G87" s="34">
-        <f t="shared" si="2"/>
+      <c r="G87" s="37" t="n">
+        <f aca="false">F87/1024</f>
         <v>108.10546875</v>
       </c>
-      <c r="H87" s="34">
-        <f t="shared" si="2"/>
-        <v>0.10557174682617188</v>
-      </c>
-      <c r="I87" s="19">
-        <f t="shared" si="2"/>
-        <v>1.0309740900993347E-4</v>
+      <c r="H87" s="37" t="n">
+        <f aca="false">G87/1024</f>
+        <v>0.105571746826172</v>
+      </c>
+      <c r="I87" s="19" t="n">
+        <f aca="false">H87/1024</f>
+        <v>0.000103097409009933</v>
       </c>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
@@ -3753,39 +3853,39 @@
       <c r="M87" s="20"/>
       <c r="N87" s="21"/>
     </row>
-    <row r="88" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A88" s="35" t="s">
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B88" s="21">
+      <c r="B88" s="21" t="n">
         <v>50</v>
       </c>
-      <c r="C88" s="21">
+      <c r="C88" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="D88" s="19">
-        <f t="shared" si="0"/>
+      <c r="D88" s="19" t="n">
+        <f aca="false">B88+10*C88</f>
         <v>100</v>
       </c>
-      <c r="E88" s="19">
-        <f>SUM(E42:E46)</f>
+      <c r="E88" s="19" t="n">
+        <f aca="false">SUM(E42:E46)</f>
         <v>120</v>
       </c>
-      <c r="F88" s="19">
-        <f t="shared" si="1"/>
+      <c r="F88" s="19" t="n">
+        <f aca="false">D88*E88</f>
         <v>12000</v>
       </c>
-      <c r="G88" s="34">
-        <f t="shared" si="2"/>
+      <c r="G88" s="37" t="n">
+        <f aca="false">F88/1024</f>
         <v>11.71875</v>
       </c>
-      <c r="H88" s="34">
-        <f t="shared" si="2"/>
-        <v>1.1444091796875E-2</v>
-      </c>
-      <c r="I88" s="19">
-        <f t="shared" si="2"/>
-        <v>1.1175870895385742E-5</v>
+      <c r="H88" s="37" t="n">
+        <f aca="false">G88/1024</f>
+        <v>0.011444091796875</v>
+      </c>
+      <c r="I88" s="19" t="n">
+        <f aca="false">H88/1024</f>
+        <v>1.11758708953857E-005</v>
       </c>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
@@ -3793,39 +3893,39 @@
       <c r="M88" s="20"/>
       <c r="N88" s="21"/>
     </row>
-    <row r="89" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A89" s="37" t="s">
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B89" s="4">
+      <c r="B89" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="19">
-        <f t="shared" si="0"/>
+      <c r="D89" s="19" t="n">
+        <f aca="false">B89+10*C89</f>
         <v>6</v>
       </c>
-      <c r="E89" s="19">
-        <f>SUM(E47:E48)</f>
+      <c r="E89" s="19" t="n">
+        <f aca="false">SUM(E47:E48)</f>
         <v>106</v>
       </c>
-      <c r="F89" s="19">
-        <f t="shared" si="1"/>
+      <c r="F89" s="19" t="n">
+        <f aca="false">D89*E89</f>
         <v>636</v>
       </c>
-      <c r="G89" s="34">
-        <f t="shared" si="2"/>
+      <c r="G89" s="37" t="n">
+        <f aca="false">F89/1024</f>
         <v>0.62109375</v>
       </c>
-      <c r="H89" s="34">
-        <f t="shared" si="2"/>
-        <v>6.06536865234375E-4</v>
-      </c>
-      <c r="I89" s="19">
-        <f t="shared" si="2"/>
-        <v>5.9232115745544434E-7</v>
+      <c r="H89" s="37" t="n">
+        <f aca="false">G89/1024</f>
+        <v>0.000606536865234375</v>
+      </c>
+      <c r="I89" s="19" t="n">
+        <f aca="false">H89/1024</f>
+        <v>5.92321157455444E-007</v>
       </c>
       <c r="J89" s="21"/>
       <c r="K89" s="21"/>
@@ -3833,39 +3933,39 @@
       <c r="M89" s="20"/>
       <c r="N89" s="21"/>
     </row>
-    <row r="90" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A90" s="37" t="s">
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B90" s="4">
+      <c r="B90" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="D90" s="19">
-        <f t="shared" si="0"/>
+      <c r="D90" s="19" t="n">
+        <f aca="false">B90+10*C90</f>
         <v>220</v>
       </c>
-      <c r="E90" s="19">
-        <f>SUM(E49:E55)</f>
+      <c r="E90" s="19" t="n">
+        <f aca="false">SUM(E49:E55)</f>
         <v>134</v>
       </c>
-      <c r="F90" s="19">
-        <f t="shared" si="1"/>
+      <c r="F90" s="19" t="n">
+        <f aca="false">D90*E90</f>
         <v>29480</v>
       </c>
-      <c r="G90" s="34">
-        <f t="shared" si="2"/>
+      <c r="G90" s="37" t="n">
+        <f aca="false">F90/1024</f>
         <v>28.7890625</v>
       </c>
-      <c r="H90" s="34">
-        <f t="shared" si="2"/>
-        <v>2.811431884765625E-2</v>
-      </c>
-      <c r="I90" s="19">
-        <f t="shared" si="2"/>
-        <v>2.7455389499664307E-5</v>
+      <c r="H90" s="37" t="n">
+        <f aca="false">G90/1024</f>
+        <v>0.0281143188476563</v>
+      </c>
+      <c r="I90" s="19" t="n">
+        <f aca="false">H90/1024</f>
+        <v>2.74553894996643E-005</v>
       </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
@@ -3873,39 +3973,39 @@
       <c r="M90" s="20"/>
       <c r="N90" s="21"/>
     </row>
-    <row r="91" spans="1:14" ht="23.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="37" t="s">
+    <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B91" s="4">
+      <c r="B91" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D91" s="19">
-        <f t="shared" si="0"/>
+      <c r="D91" s="19" t="n">
+        <f aca="false">B91+10*C91</f>
         <v>70</v>
       </c>
-      <c r="E91" s="19">
-        <f>SUM(E57:E61)</f>
+      <c r="E91" s="19" t="n">
+        <f aca="false">SUM(E57:E61)</f>
         <v>16</v>
       </c>
-      <c r="F91" s="19">
-        <f t="shared" si="1"/>
+      <c r="F91" s="19" t="n">
+        <f aca="false">D91*E91</f>
         <v>1120</v>
       </c>
-      <c r="G91" s="34">
-        <f t="shared" si="2"/>
+      <c r="G91" s="37" t="n">
+        <f aca="false">F91/1024</f>
         <v>1.09375</v>
       </c>
-      <c r="H91" s="34">
-        <f t="shared" si="2"/>
-        <v>1.068115234375E-3</v>
-      </c>
-      <c r="I91" s="19">
-        <f t="shared" si="2"/>
-        <v>1.0430812835693359E-6</v>
+      <c r="H91" s="37" t="n">
+        <f aca="false">G91/1024</f>
+        <v>0.001068115234375</v>
+      </c>
+      <c r="I91" s="19" t="n">
+        <f aca="false">H91/1024</f>
+        <v>1.04308128356934E-006</v>
       </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21"/>
@@ -3913,39 +4013,39 @@
       <c r="M91" s="20"/>
       <c r="N91" s="21"/>
     </row>
-    <row r="92" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A92" s="35" t="s">
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="D92" s="19">
-        <f t="shared" si="0"/>
+      <c r="D92" s="19" t="n">
+        <f aca="false">B92+10*C92</f>
         <v>500</v>
       </c>
-      <c r="E92" s="19">
-        <f>SUM(E62:E65)</f>
+      <c r="E92" s="19" t="n">
+        <f aca="false">SUM(E62:E65)</f>
         <v>12</v>
       </c>
-      <c r="F92" s="19">
-        <f t="shared" si="1"/>
+      <c r="F92" s="19" t="n">
+        <f aca="false">D92*E92</f>
         <v>6000</v>
       </c>
-      <c r="G92" s="34">
-        <f t="shared" si="2"/>
+      <c r="G92" s="37" t="n">
+        <f aca="false">F92/1024</f>
         <v>5.859375</v>
       </c>
-      <c r="H92" s="34">
-        <f t="shared" si="2"/>
-        <v>5.7220458984375E-3</v>
-      </c>
-      <c r="I92" s="19">
-        <f t="shared" si="2"/>
-        <v>5.5879354476928711E-6</v>
+      <c r="H92" s="37" t="n">
+        <f aca="false">G92/1024</f>
+        <v>0.0057220458984375</v>
+      </c>
+      <c r="I92" s="19" t="n">
+        <f aca="false">H92/1024</f>
+        <v>5.58793544769287E-006</v>
       </c>
       <c r="J92" s="21"/>
       <c r="K92" s="21"/>
@@ -3953,39 +4053,39 @@
       <c r="M92" s="20"/>
       <c r="N92" s="21"/>
     </row>
-    <row r="93" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A93" s="35" t="s">
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="38">
+      <c r="B93" s="41" t="n">
         <v>30000000</v>
       </c>
-      <c r="C93" s="38">
+      <c r="C93" s="41" t="n">
         <v>33000000</v>
       </c>
-      <c r="D93" s="19">
-        <f t="shared" si="0"/>
+      <c r="D93" s="19" t="n">
+        <f aca="false">B93+10*C93</f>
         <v>360000000</v>
       </c>
-      <c r="E93" s="19">
-        <f>SUM(E66:E69)</f>
+      <c r="E93" s="19" t="n">
+        <f aca="false">SUM(E66:E69)</f>
         <v>21</v>
       </c>
-      <c r="F93" s="19">
-        <f t="shared" si="1"/>
+      <c r="F93" s="19" t="n">
+        <f aca="false">D93*E93</f>
         <v>7560000000</v>
       </c>
-      <c r="G93" s="34">
-        <f t="shared" si="2"/>
+      <c r="G93" s="37" t="n">
+        <f aca="false">F93/1024</f>
         <v>7382812.5</v>
       </c>
-      <c r="H93" s="34">
-        <f t="shared" si="2"/>
+      <c r="H93" s="37" t="n">
+        <f aca="false">G93/1024</f>
         <v>7209.77783203125</v>
       </c>
-      <c r="I93" s="19">
-        <f t="shared" si="2"/>
-        <v>7.0407986640930176</v>
+      <c r="I93" s="19" t="n">
+        <f aca="false">H93/1024</f>
+        <v>7.04079866409302</v>
       </c>
       <c r="J93" s="21"/>
       <c r="K93" s="21"/>
@@ -3993,39 +4093,39 @@
       <c r="M93" s="20"/>
       <c r="N93" s="21"/>
     </row>
-    <row r="94" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A94" s="35" t="s">
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="18" t="n">
         <v>30000</v>
       </c>
-      <c r="C94" s="18">
+      <c r="C94" s="18" t="n">
         <v>36000</v>
       </c>
-      <c r="D94" s="19">
-        <f t="shared" si="0"/>
+      <c r="D94" s="19" t="n">
+        <f aca="false">B94+10*C94</f>
         <v>390000</v>
       </c>
-      <c r="E94" s="19">
-        <f>SUM(E70:E74)</f>
+      <c r="E94" s="19" t="n">
+        <f aca="false">SUM(E70:E74)</f>
         <v>21</v>
       </c>
-      <c r="F94" s="19">
-        <f t="shared" si="1"/>
+      <c r="F94" s="19" t="n">
+        <f aca="false">D94*E94</f>
         <v>8190000</v>
       </c>
-      <c r="G94" s="34">
-        <f t="shared" si="2"/>
+      <c r="G94" s="37" t="n">
+        <f aca="false">F94/1024</f>
         <v>7998.046875</v>
       </c>
-      <c r="H94" s="34">
-        <f t="shared" si="2"/>
-        <v>7.8105926513671875</v>
-      </c>
-      <c r="I94" s="19">
-        <f t="shared" si="2"/>
-        <v>7.627531886100769E-3</v>
+      <c r="H94" s="37" t="n">
+        <f aca="false">G94/1024</f>
+        <v>7.81059265136719</v>
+      </c>
+      <c r="I94" s="19" t="n">
+        <f aca="false">H94/1024</f>
+        <v>0.00762753188610077</v>
       </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -4033,39 +4133,39 @@
       <c r="M94" s="20"/>
       <c r="N94" s="21"/>
     </row>
-    <row r="95" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="18">
+        <v>23</v>
+      </c>
+      <c r="B95" s="18" t="n">
         <v>250</v>
       </c>
-      <c r="C95" s="18">
+      <c r="C95" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="D95" s="19">
-        <f t="shared" si="0"/>
+      <c r="D95" s="19" t="n">
+        <f aca="false">B95+10*C95</f>
         <v>640</v>
       </c>
-      <c r="E95" s="19">
-        <f>SUM(E75:E79)</f>
+      <c r="E95" s="19" t="n">
+        <f aca="false">SUM(E75:E79)</f>
         <v>135</v>
       </c>
-      <c r="F95" s="19">
-        <f t="shared" si="1"/>
+      <c r="F95" s="19" t="n">
+        <f aca="false">D95*E95</f>
         <v>86400</v>
       </c>
-      <c r="G95" s="34">
-        <f t="shared" si="2"/>
+      <c r="G95" s="37" t="n">
+        <f aca="false">F95/1024</f>
         <v>84.375</v>
       </c>
-      <c r="H95" s="34">
-        <f t="shared" si="2"/>
-        <v>8.23974609375E-2</v>
-      </c>
-      <c r="I95" s="19">
-        <f t="shared" si="2"/>
-        <v>8.0466270446777344E-5</v>
+      <c r="H95" s="37" t="n">
+        <f aca="false">G95/1024</f>
+        <v>0.0823974609375</v>
+      </c>
+      <c r="I95" s="19" t="n">
+        <f aca="false">H95/1024</f>
+        <v>8.04662704467773E-005</v>
       </c>
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
@@ -4073,44 +4173,36 @@
       <c r="M95" s="20"/>
       <c r="N95" s="21"/>
     </row>
-    <row r="96" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-      <c r="I96"/>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
       <c r="L96" s="20"/>
       <c r="M96" s="20"/>
       <c r="N96" s="21"/>
     </row>
-    <row r="97" spans="1:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="A97" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="B97" s="40"/>
-      <c r="C97" s="40"/>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" s="43"/>
+      <c r="C97" s="43"/>
       <c r="D97" s="21"/>
       <c r="E97" s="21"/>
-      <c r="F97" s="19">
-        <f>SUM(F84:F95)</f>
+      <c r="F97" s="19" t="n">
+        <f aca="false">SUM(F84:F95)</f>
         <v>9608453436</v>
       </c>
-      <c r="G97" s="19">
-        <f>SUM(G84:G95)</f>
+      <c r="G97" s="19" t="n">
+        <f aca="false">SUM(G84:G95)</f>
         <v>9383255.30859375</v>
       </c>
-      <c r="H97" s="19">
-        <f>SUM(H84:H95)</f>
-        <v>9163.335262298584</v>
-      </c>
-      <c r="I97" s="19">
-        <f>SUM(I84:I95)</f>
-        <v>8.9485695920884609</v>
+      <c r="H97" s="19" t="n">
+        <f aca="false">SUM(H84:H95)</f>
+        <v>9163.33526229858</v>
+      </c>
+      <c r="I97" s="19" t="n">
+        <f aca="false">SUM(I84:I95)</f>
+        <v>8.94856959208846</v>
       </c>
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
@@ -4118,7 +4210,7 @@
       <c r="M97" s="20"/>
       <c r="N97" s="21"/>
     </row>
-    <row r="98" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="21"/>
       <c r="B98" s="21"/>
       <c r="C98" s="21"/>
@@ -4127,38 +4219,40 @@
       <c r="F98" s="21"/>
       <c r="G98" s="21"/>
       <c r="H98" s="21"/>
-      <c r="I98" s="21"/>
+      <c r="I98" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
       <c r="L98" s="20"/>
       <c r="M98" s="20"/>
       <c r="N98" s="21"/>
     </row>
-    <row r="99" spans="1:14" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="41">
+    <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="45" t="n">
         <v>0.4</v>
       </c>
       <c r="E99" s="21"/>
-      <c r="F99" s="19">
-        <f>F97*1.4</f>
+      <c r="F99" s="19" t="n">
+        <f aca="false">F97*1.4</f>
         <v>13451834810.4</v>
       </c>
-      <c r="G99" s="19">
-        <f>G97*1.4</f>
-        <v>13136557.43203125</v>
-      </c>
-      <c r="H99" s="19">
-        <f>H97*1.4</f>
-        <v>12828.669367218017</v>
-      </c>
-      <c r="I99" s="19">
-        <f>I97*1.4</f>
-        <v>12.527997428923845</v>
+      <c r="G99" s="19" t="n">
+        <f aca="false">G97*1.4</f>
+        <v>13136557.4320313</v>
+      </c>
+      <c r="H99" s="19" t="n">
+        <f aca="false">H97*1.4</f>
+        <v>12828.669367218</v>
+      </c>
+      <c r="I99" s="19" t="n">
+        <f aca="false">I97*1.4</f>
+        <v>12.5279974289238</v>
       </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
@@ -4166,7 +4260,7 @@
       <c r="M99" s="20"/>
       <c r="N99" s="21"/>
     </row>
-    <row r="100" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="23"/>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
@@ -4182,7 +4276,7 @@
       <c r="M100" s="20"/>
       <c r="N100" s="21"/>
     </row>
-    <row r="101" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="23"/>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
@@ -4198,7 +4292,7 @@
       <c r="M101" s="20"/>
       <c r="N101" s="21"/>
     </row>
-    <row r="102" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="23"/>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
@@ -4214,28 +4308,28 @@
       <c r="M102" s="20"/>
       <c r="N102" s="21"/>
     </row>
-    <row r="103" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
       <c r="L103" s="20"/>
       <c r="M103" s="20"/>
       <c r="N103" s="21"/>
     </row>
-    <row r="104" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J104" s="21"/>
       <c r="K104" s="21"/>
       <c r="L104" s="20"/>
       <c r="M104" s="20"/>
       <c r="N104" s="21"/>
     </row>
-    <row r="105" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J105" s="21"/>
       <c r="K105" s="21"/>
       <c r="L105" s="20"/>
       <c r="M105" s="20"/>
       <c r="N105" s="21"/>
     </row>
-    <row r="106" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="23"/>
       <c r="B106" s="18"/>
       <c r="C106" s="18"/>
@@ -4251,7 +4345,7 @@
       <c r="M106" s="20"/>
       <c r="N106" s="21"/>
     </row>
-    <row r="107" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="23"/>
       <c r="B107" s="18"/>
       <c r="C107" s="18"/>
@@ -4267,7 +4361,7 @@
       <c r="M107" s="20"/>
       <c r="N107" s="21"/>
     </row>
-    <row r="108" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="23"/>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
@@ -4283,7 +4377,7 @@
       <c r="M108" s="20"/>
       <c r="N108" s="21"/>
     </row>
-    <row r="109" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="23"/>
       <c r="B109" s="18"/>
       <c r="C109" s="18"/>
@@ -4299,7 +4393,7 @@
       <c r="M109" s="20"/>
       <c r="N109" s="21"/>
     </row>
-    <row r="110" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="23"/>
       <c r="B110" s="18"/>
       <c r="C110" s="18"/>
@@ -4315,7 +4409,7 @@
       <c r="M110" s="20"/>
       <c r="N110" s="21"/>
     </row>
-    <row r="111" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="23"/>
       <c r="B111" s="18"/>
       <c r="C111" s="18"/>
@@ -4331,7 +4425,7 @@
       <c r="M111" s="20"/>
       <c r="N111" s="21"/>
     </row>
-    <row r="112" spans="1:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="23"/>
       <c r="B112" s="18"/>
       <c r="C112" s="18"/>
@@ -4347,91 +4441,91 @@
       <c r="M112" s="20"/>
       <c r="N112" s="21"/>
     </row>
-    <row r="113" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
       <c r="L113" s="20"/>
       <c r="M113" s="20"/>
       <c r="N113" s="21"/>
     </row>
-    <row r="114" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J114" s="21"/>
       <c r="K114" s="21"/>
       <c r="L114" s="20"/>
       <c r="M114" s="20"/>
       <c r="N114" s="21"/>
     </row>
-    <row r="115" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J115" s="21"/>
       <c r="K115" s="21"/>
       <c r="L115" s="20"/>
       <c r="M115" s="20"/>
       <c r="N115" s="21"/>
     </row>
-    <row r="116" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
       <c r="L116" s="20"/>
       <c r="M116" s="20"/>
       <c r="N116" s="21"/>
     </row>
-    <row r="117" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J117" s="21"/>
       <c r="K117" s="21"/>
       <c r="L117" s="20"/>
       <c r="M117" s="20"/>
       <c r="N117" s="21"/>
     </row>
-    <row r="118" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
       <c r="L118" s="20"/>
       <c r="M118" s="20"/>
       <c r="N118" s="21"/>
     </row>
-    <row r="119" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
       <c r="L119" s="20"/>
       <c r="M119" s="20"/>
       <c r="N119" s="21"/>
     </row>
-    <row r="120" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J120" s="21"/>
       <c r="K120" s="21"/>
       <c r="L120" s="20"/>
       <c r="M120" s="20"/>
       <c r="N120" s="21"/>
     </row>
-    <row r="121" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J121" s="21"/>
       <c r="K121" s="21"/>
       <c r="L121" s="20"/>
       <c r="M121" s="20"/>
       <c r="N121" s="21"/>
     </row>
-    <row r="122" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J122" s="21"/>
       <c r="K122" s="21"/>
       <c r="L122" s="20"/>
       <c r="M122" s="20"/>
       <c r="N122" s="21"/>
     </row>
-    <row r="123" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J123" s="21"/>
       <c r="K123" s="21"/>
       <c r="L123" s="20"/>
       <c r="M123" s="20"/>
       <c r="N123" s="21"/>
     </row>
-    <row r="124" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J124" s="21"/>
       <c r="K124" s="21"/>
       <c r="L124" s="20"/>
       <c r="M124" s="20"/>
       <c r="N124" s="21"/>
     </row>
-    <row r="125" spans="10:14" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J125" s="21"/>
       <c r="K125" s="21"/>
       <c r="L125" s="20"/>
@@ -4445,9 +4539,10 @@
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A99:C99"/>
   </mergeCells>
-  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;12Page &amp;P</oddFooter>
   </headerFooter>

--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="3.NF" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="103">
   <si>
     <t xml:space="preserve">Filiale</t>
   </si>
@@ -77,6 +77,9 @@
     <t xml:space="preserve">ZutatID</t>
   </si>
   <si>
+    <t xml:space="preserve">SchichtID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Filialname</t>
   </si>
   <si>
@@ -110,52 +113,52 @@
     <t xml:space="preserve">Allergen</t>
   </si>
   <si>
+    <t xml:space="preserve">Stromkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stunden/Woche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProduktName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gültig_bis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreisProkg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menge</t>
+  </si>
+  <si>
     <t xml:space="preserve">Datum</t>
   </si>
   <si>
-    <t xml:space="preserve">Stromkosten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stunden/Woche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProduktName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gültig_bis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PreisProkg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menge</t>
+    <t xml:space="preserve">Heizkosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kündigungsdatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gültig_ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezeichnung</t>
   </si>
   <si>
     <t xml:space="preserve">Schichtende</t>
   </si>
   <si>
-    <t xml:space="preserve">Heizkosten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kündigungsdatum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gültig_ab</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bezeichnung</t>
+    <t xml:space="preserve">Kaltmiete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehalt/Stunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backzeit</t>
   </si>
   <si>
     <t xml:space="preserve">Schichtbeginn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltmiete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gehalt/Stunde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backzeit</t>
   </si>
   <si>
     <t xml:space="preserve">sonstNebenkosten</t>
@@ -583,6 +586,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -613,10 +620,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1010,65 +1013,65 @@
       <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>11</v>
+      <c r="K2" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
+      <c r="A3" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
         <v>28</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -1076,152 +1079,155 @@
       <c r="J4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
+      <c r="K4" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -1257,8 +1263,8 @@
       <c r="K19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="7" t="s">
-        <v>23</v>
+      <c r="L19" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1292,71 +1298,71 @@
       <c r="J20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>11</v>
+      <c r="K20" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="L20" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
+      <c r="A21" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>19</v>
+      <c r="E21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="H21" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
         <v>28</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>15</v>
@@ -1364,167 +1370,170 @@
       <c r="J22" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>54</v>
+      <c r="K22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4" t="s">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>55</v>
+      <c r="L23" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4" t="s">
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>56</v>
+      <c r="L24" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4" t="s">
+      <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="4" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4" t="s">
+      <c r="A27" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="6" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="10"/>
+      <c r="D31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D32" s="4"/>
+      <c r="D32" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1542,19 +1551,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N125"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="17.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="18.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="17.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="6.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="6.1"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="18.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="17.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="6.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="12.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1591,8 +1601,8 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
-        <v>23</v>
+      <c r="L1" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1626,70 +1636,70 @@
       <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>52</v>
+      <c r="K2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>18</v>
+      <c r="A3" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>19</v>
+      <c r="E3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="H3" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
         <v>28</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>15</v>
@@ -1697,166 +1707,169 @@
       <c r="J4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>54</v>
+      <c r="K4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="A9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="4"/>
+      <c r="F9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="J10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1867,7 +1880,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E18" s="19" t="n">
         <v>4</v>
@@ -1892,11 +1905,11 @@
       <c r="A19" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>18</v>
+      <c r="B19" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D19" s="22" t="n">
         <v>50</v>
@@ -1922,11 +1935,11 @@
       <c r="A20" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>52</v>
+      <c r="B20" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D20" s="22"/>
       <c r="E20" s="19" t="n">
@@ -1936,9 +1949,7 @@
       <c r="G20" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="H20" s="20"/>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
       <c r="K20" s="21"/>
@@ -1950,11 +1961,11 @@
       <c r="A21" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" s="22" t="n">
         <v>7.2</v>
@@ -1978,11 +1989,11 @@
       <c r="A22" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="22" t="n">
         <v>7.2</v>
@@ -2006,11 +2017,11 @@
       <c r="A23" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D23" s="22" t="n">
         <v>7.2</v>
@@ -2033,11 +2044,11 @@
       <c r="A24" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>45</v>
+      <c r="B24" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D24" s="22" t="n">
         <v>7.2</v>
@@ -2061,13 +2072,13 @@
       <c r="A25" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>58</v>
+      <c r="B25" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>7.2</v>
       </c>
       <c r="E25" s="19" t="n">
@@ -2093,7 +2104,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" s="19" t="n">
         <v>8</v>
@@ -2122,7 +2133,7 @@
         <v>11</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E27" s="24" t="n">
         <v>4</v>
@@ -2149,13 +2160,13 @@
       <c r="A28" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>24</v>
+      <c r="B28" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="D28" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="D28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="19" t="n">
@@ -2177,11 +2188,11 @@
       <c r="A29" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E29" s="25" t="n">
         <v>4</v>
@@ -2189,7 +2200,7 @@
       <c r="G29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="21"/>
@@ -2209,7 +2220,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E30" s="24" t="n">
         <v>4</v>
@@ -2234,11 +2245,11 @@
       <c r="A31" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E31" s="25" t="n">
         <v>4</v>
@@ -2265,7 +2276,7 @@
         <v>14</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E32" s="24" t="n">
         <v>4</v>
@@ -2289,11 +2300,11 @@
       <c r="A33" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>19</v>
+      <c r="B33" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D33" s="22" t="n">
         <v>50</v>
@@ -2317,11 +2328,11 @@
       <c r="A34" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>25</v>
+      <c r="B34" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D34" s="22" t="n">
         <v>1</v>
@@ -2342,13 +2353,13 @@
       <c r="A35" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>78</v>
+      <c r="B35" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D35" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="E35" s="19" t="n">
@@ -2369,11 +2380,11 @@
       <c r="A36" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E36" s="19" t="n">
         <v>8</v>
@@ -2391,13 +2402,13 @@
       <c r="A37" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="E37" s="19" t="n">
@@ -2418,11 +2429,11 @@
       <c r="A38" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>46</v>
+      <c r="B38" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E38" s="19" t="n">
         <v>8</v>
@@ -2442,13 +2453,13 @@
       <c r="A39" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>49</v>
+      <c r="B39" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="D39" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E39" s="19" t="n">
@@ -2470,11 +2481,11 @@
       <c r="A40" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>52</v>
+      <c r="B40" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D40" s="22"/>
       <c r="E40" s="19" t="n">
@@ -2497,11 +2508,11 @@
       <c r="A41" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>51</v>
+      <c r="B41" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D41" s="22" t="n">
         <v>20</v>
@@ -2529,7 +2540,7 @@
         <v>15</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E42" s="24" t="n">
         <v>4</v>
@@ -2544,20 +2555,22 @@
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
       <c r="K42" s="21"/>
-      <c r="M42" s="20"/>
+      <c r="M42" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>20</v>
+      <c r="B43" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D43" s="5" t="n">
         <v>4.2</v>
       </c>
       <c r="E43" s="19" t="n">
@@ -2578,11 +2591,11 @@
       <c r="A44" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>26</v>
+      <c r="B44" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>4.2</v>
@@ -2606,11 +2619,11 @@
       <c r="A45" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45" s="22" t="n">
         <v>50</v>
@@ -2637,11 +2650,11 @@
       <c r="A46" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E46" s="25" t="n">
         <v>4</v>
@@ -2670,7 +2683,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E47" s="25" t="n">
         <v>4</v>
@@ -2695,11 +2708,11 @@
       <c r="A48" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>19</v>
+      <c r="B48" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D48" s="22" t="n">
         <v>50</v>
@@ -2730,7 +2743,7 @@
         <v>15</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E49" s="25" t="n">
         <v>4</v>
@@ -2758,10 +2771,10 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D50" s="22"/>
       <c r="E50" s="19" t="n">
@@ -2787,11 +2800,11 @@
       <c r="A51" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>27</v>
+      <c r="B51" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D51" s="22" t="n">
         <v>4.2</v>
@@ -2815,11 +2828,11 @@
       <c r="A52" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D52" s="22"/>
       <c r="E52" s="19" t="n">
@@ -2839,11 +2852,11 @@
       <c r="A53" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D53" s="22"/>
       <c r="E53" s="19" t="n">
@@ -2863,11 +2876,11 @@
       <c r="A54" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D54" s="22" t="n">
         <v>4.2</v>
@@ -2891,11 +2904,11 @@
       <c r="A55" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="4" t="s">
-        <v>47</v>
+      <c r="B55" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>50</v>
@@ -2920,11 +2933,11 @@
       <c r="A56" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B56" s="4" t="s">
-        <v>50</v>
+      <c r="B56" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D56" s="22"/>
       <c r="E56" s="19" t="n">
@@ -2948,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E57" s="25" t="n">
         <v>4</v>
@@ -2973,11 +2986,11 @@
       <c r="A58" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B58" s="4" t="s">
-        <v>22</v>
+      <c r="B58" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D58" s="22" t="n">
         <v>4.2</v>
@@ -3001,11 +3014,11 @@
       <c r="A59" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="4" t="s">
-        <v>28</v>
+      <c r="B59" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D59" s="22"/>
       <c r="E59" s="19"/>
@@ -3023,11 +3036,11 @@
       <c r="A60" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>57</v>
+      <c r="B60" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D60" s="22" t="n">
         <v>7.2</v>
@@ -3051,17 +3064,17 @@
       <c r="A61" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D61" s="22" t="n">
         <v>50</v>
       </c>
       <c r="E61" s="19" t="n">
-        <f aca="false">2*D642+2</f>
+        <f aca="false">2*D643+2</f>
         <v>2</v>
       </c>
       <c r="F61" s="20"/>
@@ -3086,7 +3099,7 @@
         <v>17</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E62" s="25" t="n">
         <v>4</v>
@@ -3114,10 +3127,10 @@
         <v>8</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E63" s="25" t="n">
         <v>2</v>
@@ -3148,7 +3161,7 @@
         <v>15</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E64" s="25" t="n">
         <v>4</v>
@@ -3175,11 +3188,11 @@
       <c r="A65" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E65" s="25" t="n">
         <v>2</v>
@@ -3204,7 +3217,7 @@
         <v>11</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E66" s="25" t="n">
         <v>4</v>
@@ -3235,7 +3248,7 @@
         <v>12</v>
       </c>
       <c r="C67" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D67" s="22"/>
       <c r="E67" s="19" t="n">
@@ -3267,7 +3280,7 @@
         <v>15</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D68" s="22"/>
       <c r="E68" s="19" t="n">
@@ -3295,11 +3308,11 @@
       <c r="A69" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C69" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D69" s="22" t="n">
         <v>5.2</v>
@@ -3323,11 +3336,11 @@
       <c r="A70" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>11</v>
+      <c r="B70" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D70" s="22"/>
       <c r="E70" s="19" t="n">
@@ -3336,9 +3349,7 @@
       <c r="F70" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G70" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="G70" s="20"/>
       <c r="H70" s="20" t="n">
         <v>1</v>
       </c>
@@ -3355,25 +3366,21 @@
       <c r="A71" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>13</v>
+      <c r="B71" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C71" s="18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D71" s="22"/>
       <c r="E71" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="F71" s="20"/>
       <c r="G71" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="H71" s="20"/>
       <c r="I71" s="21"/>
       <c r="J71" s="21"/>
       <c r="K71" s="21"/>
@@ -3387,18 +3394,20 @@
       <c r="A72" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4" t="s">
-        <v>29</v>
+      <c r="B72" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D72" s="22"/>
       <c r="E72" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+      <c r="G72" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="H72" s="20"/>
       <c r="I72" s="21"/>
       <c r="J72" s="21"/>
@@ -3413,7 +3422,7 @@
       <c r="A73" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C73" s="18" t="s">
@@ -3421,7 +3430,7 @@
       </c>
       <c r="D73" s="22"/>
       <c r="E73" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F73" s="20"/>
       <c r="G73" s="20"/>
@@ -3439,11 +3448,11 @@
       <c r="A74" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D74" s="22"/>
       <c r="E74" s="19" t="n">
@@ -3463,24 +3472,21 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E75" s="26" t="n">
-        <v>4</v>
-      </c>
-      <c r="F75" s="20" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D75" s="22"/>
+      <c r="E75" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F75" s="20"/>
       <c r="G75" s="20"/>
-      <c r="H75" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="H75" s="20"/>
       <c r="I75" s="21"/>
       <c r="J75" s="21"/>
       <c r="K75" s="21"/>
@@ -3492,24 +3498,24 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B76" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="C76" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D76" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="E76" s="19" t="n">
-        <f aca="false">2*D76+2</f>
-        <v>102</v>
-      </c>
-      <c r="F76" s="20"/>
+      <c r="E76" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
+      <c r="H76" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="I76" s="21"/>
       <c r="J76" s="21"/>
       <c r="K76" s="21"/>
@@ -3521,19 +3527,20 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B77" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B77" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C77" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D77" s="4" t="n">
-        <v>5</v>
+        <v>75</v>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>50</v>
       </c>
       <c r="E77" s="19" t="n">
-        <v>7</v>
+        <f aca="false">2*D77+2</f>
+        <v>102</v>
       </c>
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
@@ -3549,20 +3556,19 @@
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B78" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B78" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D78" s="22" t="n">
-        <v>2</v>
+        <v>88</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="E78" s="19" t="n">
-        <f aca="false">2*D78+2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F78" s="20"/>
       <c r="G78" s="20"/>
@@ -3578,20 +3584,20 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C79" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>7</v>
+        <v>75</v>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="E79" s="19" t="n">
         <f aca="false">2*D79+2</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F79" s="20"/>
       <c r="G79" s="20"/>
@@ -3605,36 +3611,47 @@
       </c>
       <c r="N79" s="21"/>
     </row>
-    <row r="80" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="27"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="21"/>
-      <c r="G80" s="21"/>
-      <c r="H80" s="21"/>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" s="19" t="n">
+        <f aca="false">2*D80+2</f>
+        <v>16</v>
+      </c>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
       <c r="I80" s="21"/>
       <c r="J80" s="21"/>
       <c r="K80" s="21"/>
       <c r="L80" s="20"/>
-      <c r="M80" s="20"/>
+      <c r="M80" s="20" t="n">
+        <v>1</v>
+      </c>
       <c r="N80" s="21"/>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="29" t="s">
+    <row r="81" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="29"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="30"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="28"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
       <c r="L81" s="20"/>
@@ -3642,90 +3659,68 @@
       <c r="N81" s="21"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="31" t="s">
+      <c r="A82" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="31"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="21"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="21"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
+      <c r="D82" s="29"/>
+      <c r="E82" s="29"/>
+      <c r="F82" s="29"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
       <c r="J82" s="21"/>
       <c r="K82" s="21"/>
       <c r="L82" s="20"/>
       <c r="M82" s="20"/>
       <c r="N82" s="21"/>
     </row>
-    <row r="83" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B83" s="34" t="s">
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C83" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="D83" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="E83" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F83" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="G83" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="H83" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="I83" s="35" t="s">
-        <v>98</v>
-      </c>
+      <c r="B83" s="31"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="21"/>
+      <c r="H83" s="21"/>
+      <c r="I83" s="21"/>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
       <c r="L83" s="20"/>
       <c r="M83" s="20"/>
       <c r="N83" s="21"/>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C84" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D84" s="19" t="n">
-        <f aca="false">B84+10*C84</f>
-        <v>100</v>
-      </c>
-      <c r="E84" s="19" t="n">
-        <f aca="false">SUM(E18:E25)</f>
-        <v>135</v>
-      </c>
-      <c r="F84" s="19" t="n">
-        <f aca="false">D84*E84</f>
-        <v>13500</v>
-      </c>
-      <c r="G84" s="37" t="n">
-        <f aca="false">F84/1024</f>
-        <v>13.18359375</v>
-      </c>
-      <c r="H84" s="37" t="n">
-        <f aca="false">G84/1024</f>
-        <v>0.0128746032714844</v>
-      </c>
-      <c r="I84" s="19" t="n">
-        <f aca="false">H84/1024</f>
-        <v>1.2572854757309E-005</v>
+    <row r="84" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B84" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D84" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E84" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="G84" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="H84" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="I84" s="35" t="s">
+        <v>99</v>
       </c>
       <c r="J84" s="21"/>
       <c r="K84" s="21"/>
@@ -3734,38 +3729,38 @@
       <c r="N84" s="21"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B85" s="39" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="C85" s="39" t="n">
-        <v>11000000</v>
+      <c r="A85" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="D85" s="19" t="n">
         <f aca="false">B85+10*C85</f>
-        <v>120000000</v>
+        <v>100</v>
       </c>
       <c r="E85" s="19" t="n">
-        <f aca="false">SUM(E26:E29)</f>
-        <v>17</v>
+        <f aca="false">SUM(E18:E25)</f>
+        <v>135</v>
       </c>
       <c r="F85" s="19" t="n">
         <f aca="false">D85*E85</f>
-        <v>2040000000</v>
+        <v>13500</v>
       </c>
       <c r="G85" s="37" t="n">
         <f aca="false">F85/1024</f>
-        <v>1992187.5</v>
+        <v>13.18359375</v>
       </c>
       <c r="H85" s="37" t="n">
         <f aca="false">G85/1024</f>
-        <v>1945.49560546875</v>
+        <v>0.0128746032714844</v>
       </c>
       <c r="I85" s="19" t="n">
         <f aca="false">H85/1024</f>
-        <v>1.89989805221558</v>
+        <v>1.2572854757309E-005</v>
       </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
@@ -3775,37 +3770,37 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="C86" s="4" t="n">
-        <v>30</v>
+        <v>1</v>
+      </c>
+      <c r="B86" s="39" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C86" s="39" t="n">
+        <v>11000000</v>
       </c>
       <c r="D86" s="19" t="n">
         <f aca="false">B86+10*C86</f>
-        <v>450</v>
+        <v>120000000</v>
       </c>
       <c r="E86" s="19" t="n">
-        <f aca="false">SUM(E30:E31)</f>
-        <v>8</v>
+        <f aca="false">SUM(E26:E29)</f>
+        <v>17</v>
       </c>
       <c r="F86" s="19" t="n">
         <f aca="false">D86*E86</f>
-        <v>3600</v>
+        <v>2040000000</v>
       </c>
       <c r="G86" s="37" t="n">
         <f aca="false">F86/1024</f>
-        <v>3.515625</v>
+        <v>1992187.5</v>
       </c>
       <c r="H86" s="37" t="n">
         <f aca="false">G86/1024</f>
-        <v>0.0034332275390625</v>
+        <v>1945.49560546875</v>
       </c>
       <c r="I86" s="19" t="n">
         <f aca="false">H86/1024</f>
-        <v>3.35276126861572E-006</v>
+        <v>1.89989805221558</v>
       </c>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
@@ -3815,37 +3810,37 @@
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="C87" s="4" t="n">
-        <v>34</v>
+        <v>2</v>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="D87" s="19" t="n">
         <f aca="false">B87+10*C87</f>
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="E87" s="19" t="n">
-        <f aca="false">SUM(E32:E41)</f>
-        <v>205</v>
+        <f aca="false">SUM(E30:E31)</f>
+        <v>8</v>
       </c>
       <c r="F87" s="19" t="n">
         <f aca="false">D87*E87</f>
-        <v>110700</v>
+        <v>3600</v>
       </c>
       <c r="G87" s="37" t="n">
         <f aca="false">F87/1024</f>
-        <v>108.10546875</v>
+        <v>3.515625</v>
       </c>
       <c r="H87" s="37" t="n">
         <f aca="false">G87/1024</f>
-        <v>0.105571746826172</v>
+        <v>0.0034332275390625</v>
       </c>
       <c r="I87" s="19" t="n">
         <f aca="false">H87/1024</f>
-        <v>0.000103097409009933</v>
+        <v>3.35276126861572E-006</v>
       </c>
       <c r="J87" s="21"/>
       <c r="K87" s="21"/>
@@ -3855,37 +3850,37 @@
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="B88" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="C88" s="21" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>34</v>
       </c>
       <c r="D88" s="19" t="n">
         <f aca="false">B88+10*C88</f>
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="E88" s="19" t="n">
-        <f aca="false">SUM(E42:E46)</f>
-        <v>120</v>
+        <f aca="false">SUM(E32:E41)</f>
+        <v>205</v>
       </c>
       <c r="F88" s="19" t="n">
         <f aca="false">D88*E88</f>
-        <v>12000</v>
+        <v>110700</v>
       </c>
       <c r="G88" s="37" t="n">
         <f aca="false">F88/1024</f>
-        <v>11.71875</v>
+        <v>108.10546875</v>
       </c>
       <c r="H88" s="37" t="n">
         <f aca="false">G88/1024</f>
-        <v>0.011444091796875</v>
+        <v>0.105571746826172</v>
       </c>
       <c r="I88" s="19" t="n">
         <f aca="false">H88/1024</f>
-        <v>1.11758708953857E-005</v>
+        <v>0.000103097409009933</v>
       </c>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
@@ -3894,38 +3889,38 @@
       <c r="N88" s="21"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="40" t="s">
+      <c r="A89" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B89" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C89" s="21" t="n">
         <v>5</v>
-      </c>
-      <c r="B89" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="D89" s="19" t="n">
         <f aca="false">B89+10*C89</f>
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E89" s="19" t="n">
-        <f aca="false">SUM(E47:E48)</f>
-        <v>106</v>
+        <f aca="false">SUM(E42:E46)</f>
+        <v>120</v>
       </c>
       <c r="F89" s="19" t="n">
         <f aca="false">D89*E89</f>
-        <v>636</v>
+        <v>12000</v>
       </c>
       <c r="G89" s="37" t="n">
         <f aca="false">F89/1024</f>
-        <v>0.62109375</v>
+        <v>11.71875</v>
       </c>
       <c r="H89" s="37" t="n">
         <f aca="false">G89/1024</f>
-        <v>0.000606536865234375</v>
+        <v>0.011444091796875</v>
       </c>
       <c r="I89" s="19" t="n">
         <f aca="false">H89/1024</f>
-        <v>5.92321157455444E-007</v>
+        <v>1.11758708953857E-005</v>
       </c>
       <c r="J89" s="21"/>
       <c r="K89" s="21"/>
@@ -3935,37 +3930,37 @@
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B90" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B90" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C90" s="4" t="n">
-        <v>15</v>
+      <c r="C90" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="D90" s="19" t="n">
         <f aca="false">B90+10*C90</f>
-        <v>220</v>
+        <v>6</v>
       </c>
       <c r="E90" s="19" t="n">
-        <f aca="false">SUM(E49:E55)</f>
-        <v>134</v>
+        <f aca="false">SUM(E47:E48)</f>
+        <v>106</v>
       </c>
       <c r="F90" s="19" t="n">
         <f aca="false">D90*E90</f>
-        <v>29480</v>
+        <v>636</v>
       </c>
       <c r="G90" s="37" t="n">
         <f aca="false">F90/1024</f>
-        <v>28.7890625</v>
+        <v>0.62109375</v>
       </c>
       <c r="H90" s="37" t="n">
         <f aca="false">G90/1024</f>
-        <v>0.0281143188476563</v>
+        <v>0.000606536865234375</v>
       </c>
       <c r="I90" s="19" t="n">
         <f aca="false">H90/1024</f>
-        <v>2.74553894996643E-005</v>
+        <v>5.92321157455444E-007</v>
       </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
@@ -3973,39 +3968,39 @@
       <c r="M90" s="20"/>
       <c r="N90" s="21"/>
     </row>
-    <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C91" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="B91" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>15</v>
       </c>
       <c r="D91" s="19" t="n">
         <f aca="false">B91+10*C91</f>
-        <v>70</v>
+        <v>220</v>
       </c>
       <c r="E91" s="19" t="n">
-        <f aca="false">SUM(E57:E61)</f>
-        <v>16</v>
+        <f aca="false">SUM(E49:E55)</f>
+        <v>134</v>
       </c>
       <c r="F91" s="19" t="n">
         <f aca="false">D91*E91</f>
-        <v>1120</v>
+        <v>29480</v>
       </c>
       <c r="G91" s="37" t="n">
         <f aca="false">F91/1024</f>
-        <v>1.09375</v>
+        <v>28.7890625</v>
       </c>
       <c r="H91" s="37" t="n">
         <f aca="false">G91/1024</f>
-        <v>0.001068115234375</v>
+        <v>0.0281143188476563</v>
       </c>
       <c r="I91" s="19" t="n">
         <f aca="false">H91/1024</f>
-        <v>1.04308128356934E-006</v>
+        <v>2.74553894996643E-005</v>
       </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21"/>
@@ -4013,39 +4008,39 @@
       <c r="M91" s="20"/>
       <c r="N91" s="21"/>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="B92" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="C92" s="18" t="n">
-        <v>25</v>
+    <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D92" s="19" t="n">
         <f aca="false">B92+10*C92</f>
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="E92" s="19" t="n">
-        <f aca="false">SUM(E62:E65)</f>
-        <v>12</v>
+        <f aca="false">SUM(E57:E61)</f>
+        <v>16</v>
       </c>
       <c r="F92" s="19" t="n">
         <f aca="false">D92*E92</f>
-        <v>6000</v>
+        <v>1120</v>
       </c>
       <c r="G92" s="37" t="n">
         <f aca="false">F92/1024</f>
-        <v>5.859375</v>
+        <v>1.09375</v>
       </c>
       <c r="H92" s="37" t="n">
         <f aca="false">G92/1024</f>
-        <v>0.0057220458984375</v>
+        <v>0.001068115234375</v>
       </c>
       <c r="I92" s="19" t="n">
         <f aca="false">H92/1024</f>
-        <v>5.58793544769287E-006</v>
+        <v>1.04308128356934E-006</v>
       </c>
       <c r="J92" s="21"/>
       <c r="K92" s="21"/>
@@ -4055,37 +4050,37 @@
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B93" s="41" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="C93" s="41" t="n">
-        <v>33000000</v>
+        <v>8</v>
+      </c>
+      <c r="B93" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="C93" s="18" t="n">
+        <v>25</v>
       </c>
       <c r="D93" s="19" t="n">
         <f aca="false">B93+10*C93</f>
-        <v>360000000</v>
+        <v>500</v>
       </c>
       <c r="E93" s="19" t="n">
-        <f aca="false">SUM(E66:E69)</f>
-        <v>21</v>
+        <f aca="false">SUM(E62:E65)</f>
+        <v>12</v>
       </c>
       <c r="F93" s="19" t="n">
         <f aca="false">D93*E93</f>
-        <v>7560000000</v>
+        <v>6000</v>
       </c>
       <c r="G93" s="37" t="n">
         <f aca="false">F93/1024</f>
-        <v>7382812.5</v>
+        <v>5.859375</v>
       </c>
       <c r="H93" s="37" t="n">
         <f aca="false">G93/1024</f>
-        <v>7209.77783203125</v>
+        <v>0.0057220458984375</v>
       </c>
       <c r="I93" s="19" t="n">
         <f aca="false">H93/1024</f>
-        <v>7.04079866409302</v>
+        <v>5.58793544769287E-006</v>
       </c>
       <c r="J93" s="21"/>
       <c r="K93" s="21"/>
@@ -4095,37 +4090,37 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="B94" s="18" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C94" s="18" t="n">
-        <v>36000</v>
+        <v>9</v>
+      </c>
+      <c r="B94" s="41" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C94" s="41" t="n">
+        <v>33000000</v>
       </c>
       <c r="D94" s="19" t="n">
         <f aca="false">B94+10*C94</f>
-        <v>390000</v>
+        <v>360000000</v>
       </c>
       <c r="E94" s="19" t="n">
-        <f aca="false">SUM(E70:E74)</f>
+        <f aca="false">SUM(E66:E69)</f>
         <v>21</v>
       </c>
       <c r="F94" s="19" t="n">
         <f aca="false">D94*E94</f>
-        <v>8190000</v>
+        <v>7560000000</v>
       </c>
       <c r="G94" s="37" t="n">
         <f aca="false">F94/1024</f>
-        <v>7998.046875</v>
+        <v>7382812.5</v>
       </c>
       <c r="H94" s="37" t="n">
         <f aca="false">G94/1024</f>
-        <v>7.81059265136719</v>
+        <v>7209.77783203125</v>
       </c>
       <c r="I94" s="19" t="n">
         <f aca="false">H94/1024</f>
-        <v>0.00762753188610077</v>
+        <v>7.04079866409302</v>
       </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -4134,38 +4129,38 @@
       <c r="N94" s="21"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="23" t="s">
-        <v>23</v>
+      <c r="A95" s="38" t="s">
+        <v>10</v>
       </c>
       <c r="B95" s="18" t="n">
-        <v>250</v>
+        <v>30000</v>
       </c>
       <c r="C95" s="18" t="n">
-        <v>39</v>
+        <v>36000</v>
       </c>
       <c r="D95" s="19" t="n">
         <f aca="false">B95+10*C95</f>
-        <v>640</v>
+        <v>390000</v>
       </c>
       <c r="E95" s="19" t="n">
-        <f aca="false">SUM(E75:E79)</f>
-        <v>135</v>
+        <f aca="false">SUM(E71:E75)</f>
+        <v>21</v>
       </c>
       <c r="F95" s="19" t="n">
         <f aca="false">D95*E95</f>
-        <v>86400</v>
+        <v>8190000</v>
       </c>
       <c r="G95" s="37" t="n">
         <f aca="false">F95/1024</f>
-        <v>84.375</v>
+        <v>7998.046875</v>
       </c>
       <c r="H95" s="37" t="n">
         <f aca="false">G95/1024</f>
-        <v>0.0823974609375</v>
+        <v>7.81059265136719</v>
       </c>
       <c r="I95" s="19" t="n">
         <f aca="false">H95/1024</f>
-        <v>8.04662704467773E-005</v>
+        <v>0.00762753188610077</v>
       </c>
       <c r="J95" s="21"/>
       <c r="K95" s="21"/>
@@ -4174,6 +4169,39 @@
       <c r="N95" s="21"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="C96" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="D96" s="19" t="n">
+        <f aca="false">B96+10*C96</f>
+        <v>640</v>
+      </c>
+      <c r="E96" s="19" t="n">
+        <f aca="false">SUM(E76:E80)</f>
+        <v>135</v>
+      </c>
+      <c r="F96" s="19" t="n">
+        <f aca="false">D96*E96</f>
+        <v>86400</v>
+      </c>
+      <c r="G96" s="37" t="n">
+        <f aca="false">F96/1024</f>
+        <v>84.375</v>
+      </c>
+      <c r="H96" s="37" t="n">
+        <f aca="false">G96/1024</f>
+        <v>0.0823974609375</v>
+      </c>
+      <c r="I96" s="19" t="n">
+        <f aca="false">H96/1024</f>
+        <v>8.04662704467773E-005</v>
+      </c>
       <c r="J96" s="21"/>
       <c r="K96" s="21"/>
       <c r="L96" s="20"/>
@@ -4181,46 +4209,35 @@
       <c r="N96" s="21"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" s="43"/>
-      <c r="C97" s="43"/>
-      <c r="D97" s="21"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="19" t="n">
-        <f aca="false">SUM(F84:F95)</f>
-        <v>9608453436</v>
-      </c>
-      <c r="G97" s="19" t="n">
-        <f aca="false">SUM(G84:G95)</f>
-        <v>9383255.30859375</v>
-      </c>
-      <c r="H97" s="19" t="n">
-        <f aca="false">SUM(H84:H95)</f>
-        <v>9163.33526229858</v>
-      </c>
-      <c r="I97" s="19" t="n">
-        <f aca="false">SUM(I84:I95)</f>
-        <v>8.94856959208846</v>
-      </c>
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
       <c r="L97" s="20"/>
       <c r="M97" s="20"/>
       <c r="N97" s="21"/>
     </row>
-    <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="21"/>
-      <c r="B98" s="21"/>
-      <c r="C98" s="21"/>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" s="43"/>
+      <c r="C98" s="43"/>
       <c r="D98" s="21"/>
       <c r="E98" s="21"/>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="21" t="s">
-        <v>100</v>
+      <c r="F98" s="19" t="n">
+        <f aca="false">SUM(F85:F96)</f>
+        <v>9608453436</v>
+      </c>
+      <c r="G98" s="19" t="n">
+        <f aca="false">SUM(G85:G96)</f>
+        <v>9383255.30859375</v>
+      </c>
+      <c r="H98" s="19" t="n">
+        <f aca="false">SUM(H85:H96)</f>
+        <v>9163.33526229858</v>
+      </c>
+      <c r="I98" s="19" t="n">
+        <f aca="false">SUM(I85:I96)</f>
+        <v>8.94856959208846</v>
       </c>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
@@ -4229,30 +4246,16 @@
       <c r="N98" s="21"/>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="44" t="s">
+      <c r="A99" s="21"/>
+      <c r="B99" s="21"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21" t="s">
         <v>101</v>
-      </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="44"/>
-      <c r="D99" s="45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E99" s="21"/>
-      <c r="F99" s="19" t="n">
-        <f aca="false">F97*1.4</f>
-        <v>13451834810.4</v>
-      </c>
-      <c r="G99" s="19" t="n">
-        <f aca="false">G97*1.4</f>
-        <v>13136557.4320313</v>
-      </c>
-      <c r="H99" s="19" t="n">
-        <f aca="false">H97*1.4</f>
-        <v>12828.669367218</v>
-      </c>
-      <c r="I99" s="19" t="n">
-        <f aca="false">I97*1.4</f>
-        <v>12.5279974289238</v>
       </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
@@ -4260,16 +4263,32 @@
       <c r="M99" s="20"/>
       <c r="N99" s="21"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="23"/>
-      <c r="B100" s="18"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="22"/>
+    <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="44"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="45" t="n">
+        <v>0.4</v>
+      </c>
       <c r="E100" s="21"/>
-      <c r="F100" s="20"/>
-      <c r="G100" s="20"/>
-      <c r="H100" s="20"/>
-      <c r="I100" s="21"/>
+      <c r="F100" s="19" t="n">
+        <f aca="false">F98*1.4</f>
+        <v>13451834810.4</v>
+      </c>
+      <c r="G100" s="19" t="n">
+        <f aca="false">G98*1.4</f>
+        <v>13136557.4320313</v>
+      </c>
+      <c r="H100" s="19" t="n">
+        <f aca="false">H98*1.4</f>
+        <v>12828.669367218</v>
+      </c>
+      <c r="I100" s="19" t="n">
+        <f aca="false">I98*1.4</f>
+        <v>12.5279974289238</v>
+      </c>
       <c r="J100" s="21"/>
       <c r="K100" s="21"/>
       <c r="L100" s="20"/>
@@ -4309,6 +4328,15 @@
       <c r="N102" s="21"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="23"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="18"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="20"/>
+      <c r="G103" s="20"/>
+      <c r="H103" s="20"/>
+      <c r="I103" s="21"/>
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
       <c r="L103" s="20"/>
@@ -4330,15 +4358,6 @@
       <c r="N105" s="21"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="23"/>
-      <c r="B106" s="18"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="22"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="20"/>
-      <c r="G106" s="20"/>
-      <c r="H106" s="20"/>
-      <c r="I106" s="21"/>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
       <c r="L106" s="20"/>
@@ -4442,6 +4461,15 @@
       <c r="N112" s="21"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="23"/>
+      <c r="B113" s="18"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="22"/>
+      <c r="E113" s="21"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="20"/>
+      <c r="H113" s="20"/>
+      <c r="I113" s="21"/>
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
       <c r="L113" s="20"/>
@@ -4532,12 +4560,19 @@
       <c r="M125" s="20"/>
       <c r="N125" s="21"/>
     </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J126" s="21"/>
+      <c r="K126" s="21"/>
+      <c r="L126" s="20"/>
+      <c r="M126" s="20"/>
+      <c r="N126" s="21"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A100:C100"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="3.NF" sheetId="1" state="visible" r:id="rId3"/>
@@ -569,8 +569,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -586,10 +590,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -602,20 +602,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -672,10 +664,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -940,80 +928,80 @@
   <dimension ref="A1:L32"/>
   <sheetFormatPr defaultColWidth="12.71484375" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1021,7 +1009,7 @@
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1036,19 +1024,19 @@
       <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1073,13 +1061,13 @@
       <c r="H4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1230,78 +1218,78 @@
       <c r="I12" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="K19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L20" s="0" t="s">
+      <c r="L20" s="1" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1309,7 +1297,7 @@
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -1324,19 +1312,19 @@
       <c r="F21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="J21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="4" t="s">
         <v>11</v>
       </c>
       <c r="L21" s="7" t="s">
@@ -1364,13 +1352,13 @@
       <c r="H22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="7" t="s">
@@ -1470,7 +1458,7 @@
         <v>47</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="9"/>
+      <c r="F26" s="8"/>
       <c r="G26" s="5" t="s">
         <v>48</v>
       </c>
@@ -1517,20 +1505,16 @@
       </c>
       <c r="E29" s="5"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="10"/>
+      <c r="H29" s="9"/>
       <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="11"/>
       <c r="E30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="5"/>
@@ -1562,84 +1546,84 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="5" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="5" width="6.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="8.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="8.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="12" style="9" width="12.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1647,7 +1631,7 @@
       <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1662,22 +1646,22 @@
       <c r="F3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="1" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1701,16 +1685,16 @@
       <c r="H4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="1" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1743,7 +1727,7 @@
       <c r="K5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="1" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1768,7 +1752,7 @@
       <c r="K6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1829,1907 +1813,1907 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="27" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="H17" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="I17" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="13" t="s">
+      <c r="J17" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="M17" s="13" t="s">
+      <c r="M17" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="N17" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E18" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="21"/>
+      <c r="F18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E19" s="19" t="n">
+      <c r="E19" s="17" t="n">
         <v>102</v>
       </c>
-      <c r="F19" s="20"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="21"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="19" t="n">
+      <c r="D20" s="20"/>
+      <c r="E20" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="21"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E21" s="19" t="n">
+      <c r="E21" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="21"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E23" s="19" t="n">
+      <c r="E23" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="21"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E24" s="19" t="n">
+      <c r="E24" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" s="21"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>76</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>7.2</v>
       </c>
-      <c r="E25" s="19" t="n">
+      <c r="E25" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="21"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="21"/>
+      <c r="F26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="E27" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" s="21"/>
+      <c r="F27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="16" t="s">
         <v>78</v>
       </c>
       <c r="D28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" s="21"/>
+      <c r="E28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" s="21"/>
+      <c r="G29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="24" t="n">
+      <c r="E30" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="21"/>
+      <c r="F30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="21" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" s="21"/>
+      <c r="G31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="M32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" s="21"/>
+      <c r="F32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="M32" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E33" s="19" t="n">
+      <c r="E33" s="17" t="n">
         <f aca="false">2*D33+2</f>
         <v>102</v>
       </c>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="M33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" s="21"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="M33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="21"/>
+      <c r="D34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="16" t="s">
         <v>80</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="E35" s="19" t="n">
+      <c r="E35" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
-      <c r="M35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" s="21"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="M35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="21"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="21"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="16" t="s">
         <v>80</v>
       </c>
       <c r="D37" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21"/>
-      <c r="K37" s="21"/>
-      <c r="M37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="21"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="M37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21"/>
-      <c r="K38" s="21"/>
-      <c r="M38" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" s="21"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="M38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="16" t="s">
         <v>75</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="17" t="n">
         <f aca="false">2*D39+2</f>
         <v>26</v>
       </c>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="21"/>
-      <c r="M39" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" s="21"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="M39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="19" t="n">
+      <c r="D40" s="20"/>
+      <c r="E40" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="20"/>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21"/>
-      <c r="K40" s="21"/>
-      <c r="M40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" s="21"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="M40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="s">
+      <c r="A41" s="21" t="s">
         <v>3</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="22" t="n">
+      <c r="D41" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="E41" s="19" t="n">
+      <c r="E41" s="17" t="n">
         <f aca="false">2*D41+2</f>
         <v>42</v>
       </c>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
-      <c r="M41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="M41" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23" t="s">
+      <c r="A42" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="24" t="n">
+      <c r="E42" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="M42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" s="21"/>
+      <c r="F42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="M42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
+      <c r="A43" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="16" t="s">
         <v>80</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>4.2</v>
       </c>
-      <c r="E43" s="19" t="n">
+      <c r="E43" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21"/>
-      <c r="K43" s="21"/>
-      <c r="M43" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" s="21"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="M43" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" s="19"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D44" s="22" t="n">
+      <c r="D44" s="20" t="n">
         <v>4.2</v>
       </c>
-      <c r="E44" s="19" t="n">
+      <c r="E44" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="21"/>
-      <c r="J44" s="21"/>
-      <c r="K44" s="21"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N44" s="21"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" s="19"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="23" t="s">
+      <c r="A45" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="22" t="n">
+      <c r="D45" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E45" s="19" t="n">
+      <c r="E45" s="17" t="n">
         <f aca="false">2*D45+2</f>
         <v>102</v>
       </c>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N45" s="21"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" s="19"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="21" t="s">
         <v>4</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="25" t="n">
+      <c r="E46" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="21"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" s="21"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="19"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="25" t="n">
+      <c r="E47" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="21"/>
+      <c r="F47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="19"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="23" t="s">
+      <c r="A48" s="21" t="s">
         <v>5</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D48" s="22" t="n">
+      <c r="D48" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E48" s="19" t="n">
+      <c r="E48" s="17" t="n">
         <f aca="false">2*D48+2</f>
         <v>102</v>
       </c>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21"/>
-      <c r="K48" s="21"/>
-      <c r="L48" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N48" s="21"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="19"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="23" t="s">
+      <c r="A49" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E49" s="25" t="n">
+      <c r="E49" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
-      <c r="K49" s="21"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="21"/>
+      <c r="F49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="23" t="s">
+      <c r="A50" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="19" t="n">
+      <c r="D50" s="20"/>
+      <c r="E50" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="20"/>
-      <c r="H50" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="21"/>
+      <c r="F50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D51" s="22" t="n">
+      <c r="D51" s="20" t="n">
         <v>4.2</v>
       </c>
-      <c r="E51" s="19" t="n">
+      <c r="E51" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="20"/>
-      <c r="G51" s="20"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="21"/>
-      <c r="J51" s="21"/>
-      <c r="K51" s="21"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="21"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="19"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="23" t="s">
+      <c r="A52" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="22"/>
-      <c r="E52" s="19" t="n">
+      <c r="D52" s="20"/>
+      <c r="E52" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21"/>
-      <c r="K52" s="21"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="21"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="18"/>
+      <c r="M52" s="18"/>
+      <c r="N52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="23" t="s">
+      <c r="A53" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D53" s="22"/>
-      <c r="E53" s="19" t="n">
+      <c r="D53" s="20"/>
+      <c r="E53" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="21"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="23" t="s">
+      <c r="A54" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="22" t="n">
+      <c r="D54" s="20" t="n">
         <v>4.2</v>
       </c>
-      <c r="E54" s="19" t="n">
+      <c r="E54" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
-      <c r="K54" s="21"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" s="21"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="22" t="n">
+      <c r="D55" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E55" s="19" t="n">
+      <c r="E55" s="17" t="n">
         <f aca="false">2*D55+2</f>
         <v>102</v>
       </c>
-      <c r="F55" s="20"/>
-      <c r="G55" s="20"/>
-      <c r="H55" s="20"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" s="21"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="19"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="21" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D56" s="22"/>
-      <c r="E56" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21"/>
-      <c r="K56" s="21"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="21"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
+      <c r="N56" s="19"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E57" s="25" t="n">
+      <c r="E57" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21"/>
-      <c r="K57" s="21"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" s="21"/>
+      <c r="F57" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="19"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D58" s="22" t="n">
+      <c r="D58" s="20" t="n">
         <v>4.2</v>
       </c>
-      <c r="E58" s="19" t="n">
+      <c r="E58" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" s="21"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" s="19"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="23" t="s">
+      <c r="A59" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="22"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="21"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="19"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="23" t="s">
+      <c r="A60" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D60" s="22" t="n">
+      <c r="D60" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E60" s="19" t="n">
+      <c r="E60" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="19"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="22" t="n">
+      <c r="D61" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E61" s="19" t="n">
+      <c r="E61" s="17" t="n">
         <f aca="false">2*D643+2</f>
         <v>2</v>
       </c>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="21"/>
-      <c r="J61" s="21"/>
-      <c r="K61" s="21"/>
-      <c r="L61" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" s="21"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="18"/>
+      <c r="H61" s="18"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" s="19"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="23" t="s">
+      <c r="A62" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="25" t="n">
+      <c r="E62" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N62" s="21"/>
+      <c r="F62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N62" s="19"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="23" t="s">
+      <c r="A63" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E63" s="25" t="n">
+      <c r="E63" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="21"/>
+      <c r="F63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" s="19"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="23" t="s">
+      <c r="A64" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E64" s="25" t="n">
+      <c r="E64" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" s="21"/>
+      <c r="F64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" s="19"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="23" t="s">
+      <c r="A65" s="21" t="s">
         <v>8</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E65" s="25" t="n">
+      <c r="E65" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" s="21"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="19"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="23" t="s">
+      <c r="A66" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="E66" s="25" t="n">
+      <c r="E66" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="F66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="20"/>
-      <c r="M66" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="21"/>
+      <c r="F66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="19"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="23" t="s">
+      <c r="A67" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D67" s="22"/>
-      <c r="E67" s="19" t="n">
+      <c r="D67" s="20"/>
+      <c r="E67" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="F67" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21"/>
-      <c r="K67" s="21"/>
-      <c r="L67" s="20"/>
-      <c r="M67" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N67" s="21"/>
+      <c r="F67" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="18"/>
+      <c r="M67" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" s="19"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="23" t="s">
+      <c r="A68" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D68" s="22"/>
-      <c r="E68" s="19" t="n">
+      <c r="D68" s="20"/>
+      <c r="E68" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="20"/>
-      <c r="M68" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N68" s="21"/>
+      <c r="F68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" s="19"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="21" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D69" s="22" t="n">
+      <c r="D69" s="20" t="n">
         <v>5.2</v>
       </c>
-      <c r="E69" s="19" t="n">
+      <c r="E69" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="20"/>
-      <c r="M69" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" s="21"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" s="19"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D70" s="22"/>
-      <c r="E70" s="19" t="n">
+      <c r="D70" s="20"/>
+      <c r="E70" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F70" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="20"/>
-      <c r="M70" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" s="21"/>
+      <c r="F70" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="19"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="23" t="s">
+      <c r="A71" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D71" s="22"/>
-      <c r="E71" s="19" t="n">
+      <c r="D71" s="20"/>
+      <c r="E71" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="20"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="20"/>
-      <c r="M71" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N71" s="21"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="18"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="19"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="23" t="s">
+      <c r="A72" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D72" s="22"/>
-      <c r="E72" s="19" t="n">
+      <c r="D72" s="20"/>
+      <c r="E72" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="20"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="20"/>
-      <c r="M72" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" s="21"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="18"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" s="19"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="23" t="s">
+      <c r="A73" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="19" t="n">
+      <c r="D73" s="20"/>
+      <c r="E73" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="20"/>
-      <c r="M73" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N73" s="21"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="19"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="23" t="s">
+      <c r="A74" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D74" s="22"/>
-      <c r="E74" s="19" t="n">
+      <c r="D74" s="20"/>
+      <c r="E74" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="20"/>
-      <c r="M74" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="21"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" s="19"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="21" t="s">
         <v>10</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D75" s="22"/>
-      <c r="E75" s="19" t="n">
+      <c r="D75" s="20"/>
+      <c r="E75" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="20"/>
-      <c r="M75" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N75" s="21"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" s="19"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="23" t="s">
+      <c r="A76" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E76" s="26" t="n">
+      <c r="E76" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="F76" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="20"/>
-      <c r="M76" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" s="21"/>
+      <c r="F76" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" s="19"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="23" t="s">
+      <c r="A77" s="21" t="s">
         <v>24</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D77" s="22" t="n">
+      <c r="D77" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="E77" s="19" t="n">
+      <c r="E77" s="17" t="n">
         <f aca="false">2*D77+2</f>
         <v>102</v>
       </c>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" s="21"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N77" s="19"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="23" t="s">
+      <c r="A78" s="21" t="s">
         <v>24</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="16" t="s">
         <v>88</v>
       </c>
       <c r="D78" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="19" t="n">
+      <c r="E78" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="F78" s="20"/>
-      <c r="G78" s="20"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="20"/>
-      <c r="M78" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" s="21"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
+      <c r="K78" s="19"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="19"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="23" t="s">
+      <c r="A79" s="21" t="s">
         <v>24</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D79" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" s="19" t="n">
+      <c r="D79" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" s="17" t="n">
         <f aca="false">2*D79+2</f>
-        <v>6</v>
-      </c>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" s="21"/>
+        <v>42</v>
+      </c>
+      <c r="F79" s="18"/>
+      <c r="G79" s="18"/>
+      <c r="H79" s="18"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="18"/>
+      <c r="M79" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N79" s="19"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="23" t="s">
+      <c r="A80" s="21" t="s">
         <v>24</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="16" t="s">
         <v>75</v>
       </c>
       <c r="D80" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E80" s="19" t="n">
+      <c r="E80" s="17" t="n">
         <f aca="false">2*D80+2</f>
         <v>16</v>
       </c>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="21"/>
-      <c r="J80" s="21"/>
-      <c r="K80" s="21"/>
-      <c r="L80" s="20"/>
-      <c r="M80" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N80" s="21"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="18"/>
+      <c r="M80" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" s="19"/>
     </row>
     <row r="81" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="27" t="s">
+      <c r="A81" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B81" s="27"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21"/>
-      <c r="H81" s="21"/>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21"/>
-      <c r="K81" s="21"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="20"/>
-      <c r="N81" s="21"/>
+      <c r="B81" s="24"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="18"/>
+      <c r="M81" s="18"/>
+      <c r="N81" s="19"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="29" t="s">
+      <c r="A82" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
-      <c r="F82" s="29"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="30"/>
-      <c r="J82" s="21"/>
-      <c r="K82" s="21"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="20"/>
-      <c r="N82" s="21"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
+      <c r="N82" s="19"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="31" t="s">
+      <c r="A83" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="31"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="21"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21"/>
-      <c r="K83" s="21"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="20"/>
-      <c r="N83" s="21"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="29"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="18"/>
+      <c r="M83" s="18"/>
+      <c r="N83" s="19"/>
     </row>
     <row r="84" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="33" t="s">
+      <c r="A84" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="B84" s="34" t="s">
+      <c r="B84" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C84" s="34" t="s">
+      <c r="C84" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="D84" s="35" t="s">
+      <c r="D84" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="E84" s="35" t="s">
+      <c r="E84" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="F84" s="35" t="s">
+      <c r="F84" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="G84" s="35" t="s">
+      <c r="G84" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="H84" s="35" t="s">
+      <c r="H84" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="I84" s="35" t="s">
+      <c r="I84" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="J84" s="21"/>
-      <c r="K84" s="21"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20"/>
-      <c r="N84" s="21"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="18"/>
+      <c r="M84" s="18"/>
+      <c r="N84" s="19"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="36" t="s">
+      <c r="A85" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B85" s="5" t="n">
@@ -3738,78 +3722,78 @@
       <c r="C85" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D85" s="19" t="n">
+      <c r="D85" s="17" t="n">
         <f aca="false">B85+10*C85</f>
         <v>100</v>
       </c>
-      <c r="E85" s="19" t="n">
+      <c r="E85" s="17" t="n">
         <f aca="false">SUM(E18:E25)</f>
         <v>135</v>
       </c>
-      <c r="F85" s="19" t="n">
+      <c r="F85" s="17" t="n">
         <f aca="false">D85*E85</f>
         <v>13500</v>
       </c>
-      <c r="G85" s="37" t="n">
+      <c r="G85" s="34" t="n">
         <f aca="false">F85/1024</f>
         <v>13.18359375</v>
       </c>
-      <c r="H85" s="37" t="n">
+      <c r="H85" s="34" t="n">
         <f aca="false">G85/1024</f>
         <v>0.0128746032714844</v>
       </c>
-      <c r="I85" s="19" t="n">
+      <c r="I85" s="17" t="n">
         <f aca="false">H85/1024</f>
         <v>1.2572854757309E-005</v>
       </c>
-      <c r="J85" s="21"/>
-      <c r="K85" s="21"/>
-      <c r="L85" s="20"/>
-      <c r="M85" s="20"/>
-      <c r="N85" s="21"/>
+      <c r="J85" s="19"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="18"/>
+      <c r="M85" s="18"/>
+      <c r="N85" s="19"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" s="39" t="n">
+      <c r="A86" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B86" s="36" t="n">
         <v>10000000</v>
       </c>
-      <c r="C86" s="39" t="n">
+      <c r="C86" s="36" t="n">
         <v>11000000</v>
       </c>
-      <c r="D86" s="19" t="n">
+      <c r="D86" s="17" t="n">
         <f aca="false">B86+10*C86</f>
         <v>120000000</v>
       </c>
-      <c r="E86" s="19" t="n">
+      <c r="E86" s="17" t="n">
         <f aca="false">SUM(E26:E29)</f>
         <v>17</v>
       </c>
-      <c r="F86" s="19" t="n">
+      <c r="F86" s="17" t="n">
         <f aca="false">D86*E86</f>
         <v>2040000000</v>
       </c>
-      <c r="G86" s="37" t="n">
+      <c r="G86" s="34" t="n">
         <f aca="false">F86/1024</f>
         <v>1992187.5</v>
       </c>
-      <c r="H86" s="37" t="n">
+      <c r="H86" s="34" t="n">
         <f aca="false">G86/1024</f>
         <v>1945.49560546875</v>
       </c>
-      <c r="I86" s="19" t="n">
+      <c r="I86" s="17" t="n">
         <f aca="false">H86/1024</f>
         <v>1.89989805221558</v>
       </c>
-      <c r="J86" s="21"/>
-      <c r="K86" s="21"/>
-      <c r="L86" s="20"/>
-      <c r="M86" s="20"/>
-      <c r="N86" s="21"/>
+      <c r="J86" s="19"/>
+      <c r="K86" s="19"/>
+      <c r="L86" s="18"/>
+      <c r="M86" s="18"/>
+      <c r="N86" s="19"/>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="38" t="s">
+      <c r="A87" s="35" t="s">
         <v>2</v>
       </c>
       <c r="B87" s="5" t="n">
@@ -3818,38 +3802,38 @@
       <c r="C87" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D87" s="19" t="n">
+      <c r="D87" s="17" t="n">
         <f aca="false">B87+10*C87</f>
         <v>450</v>
       </c>
-      <c r="E87" s="19" t="n">
+      <c r="E87" s="17" t="n">
         <f aca="false">SUM(E30:E31)</f>
         <v>8</v>
       </c>
-      <c r="F87" s="19" t="n">
+      <c r="F87" s="17" t="n">
         <f aca="false">D87*E87</f>
         <v>3600</v>
       </c>
-      <c r="G87" s="37" t="n">
+      <c r="G87" s="34" t="n">
         <f aca="false">F87/1024</f>
         <v>3.515625</v>
       </c>
-      <c r="H87" s="37" t="n">
+      <c r="H87" s="34" t="n">
         <f aca="false">G87/1024</f>
         <v>0.0034332275390625</v>
       </c>
-      <c r="I87" s="19" t="n">
+      <c r="I87" s="17" t="n">
         <f aca="false">H87/1024</f>
         <v>3.35276126861572E-006</v>
       </c>
-      <c r="J87" s="21"/>
-      <c r="K87" s="21"/>
-      <c r="L87" s="20"/>
-      <c r="M87" s="20"/>
-      <c r="N87" s="21"/>
+      <c r="J87" s="19"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="18"/>
+      <c r="M87" s="18"/>
+      <c r="N87" s="19"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="38" t="s">
+      <c r="A88" s="35" t="s">
         <v>3</v>
       </c>
       <c r="B88" s="5" t="n">
@@ -3858,78 +3842,78 @@
       <c r="C88" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="D88" s="19" t="n">
+      <c r="D88" s="17" t="n">
         <f aca="false">B88+10*C88</f>
         <v>540</v>
       </c>
-      <c r="E88" s="19" t="n">
+      <c r="E88" s="17" t="n">
         <f aca="false">SUM(E32:E41)</f>
         <v>205</v>
       </c>
-      <c r="F88" s="19" t="n">
+      <c r="F88" s="17" t="n">
         <f aca="false">D88*E88</f>
         <v>110700</v>
       </c>
-      <c r="G88" s="37" t="n">
+      <c r="G88" s="34" t="n">
         <f aca="false">F88/1024</f>
         <v>108.10546875</v>
       </c>
-      <c r="H88" s="37" t="n">
+      <c r="H88" s="34" t="n">
         <f aca="false">G88/1024</f>
         <v>0.105571746826172</v>
       </c>
-      <c r="I88" s="19" t="n">
+      <c r="I88" s="17" t="n">
         <f aca="false">H88/1024</f>
         <v>0.000103097409009933</v>
       </c>
-      <c r="J88" s="21"/>
-      <c r="K88" s="21"/>
-      <c r="L88" s="20"/>
-      <c r="M88" s="20"/>
-      <c r="N88" s="21"/>
+      <c r="J88" s="19"/>
+      <c r="K88" s="19"/>
+      <c r="L88" s="18"/>
+      <c r="M88" s="18"/>
+      <c r="N88" s="19"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="38" t="s">
+      <c r="A89" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B89" s="21" t="n">
+      <c r="B89" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="C89" s="21" t="n">
+      <c r="C89" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D89" s="19" t="n">
+      <c r="D89" s="17" t="n">
         <f aca="false">B89+10*C89</f>
         <v>100</v>
       </c>
-      <c r="E89" s="19" t="n">
+      <c r="E89" s="17" t="n">
         <f aca="false">SUM(E42:E46)</f>
         <v>120</v>
       </c>
-      <c r="F89" s="19" t="n">
+      <c r="F89" s="17" t="n">
         <f aca="false">D89*E89</f>
         <v>12000</v>
       </c>
-      <c r="G89" s="37" t="n">
+      <c r="G89" s="34" t="n">
         <f aca="false">F89/1024</f>
         <v>11.71875</v>
       </c>
-      <c r="H89" s="37" t="n">
+      <c r="H89" s="34" t="n">
         <f aca="false">G89/1024</f>
         <v>0.011444091796875</v>
       </c>
-      <c r="I89" s="19" t="n">
+      <c r="I89" s="17" t="n">
         <f aca="false">H89/1024</f>
         <v>1.11758708953857E-005</v>
       </c>
-      <c r="J89" s="21"/>
-      <c r="K89" s="21"/>
-      <c r="L89" s="20"/>
-      <c r="M89" s="20"/>
-      <c r="N89" s="21"/>
+      <c r="J89" s="19"/>
+      <c r="K89" s="19"/>
+      <c r="L89" s="18"/>
+      <c r="M89" s="18"/>
+      <c r="N89" s="19"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="40" t="s">
+      <c r="A90" s="37" t="s">
         <v>5</v>
       </c>
       <c r="B90" s="5" t="n">
@@ -3938,38 +3922,38 @@
       <c r="C90" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D90" s="19" t="n">
+      <c r="D90" s="17" t="n">
         <f aca="false">B90+10*C90</f>
         <v>6</v>
       </c>
-      <c r="E90" s="19" t="n">
+      <c r="E90" s="17" t="n">
         <f aca="false">SUM(E47:E48)</f>
         <v>106</v>
       </c>
-      <c r="F90" s="19" t="n">
+      <c r="F90" s="17" t="n">
         <f aca="false">D90*E90</f>
         <v>636</v>
       </c>
-      <c r="G90" s="37" t="n">
+      <c r="G90" s="34" t="n">
         <f aca="false">F90/1024</f>
         <v>0.62109375</v>
       </c>
-      <c r="H90" s="37" t="n">
+      <c r="H90" s="34" t="n">
         <f aca="false">G90/1024</f>
         <v>0.000606536865234375</v>
       </c>
-      <c r="I90" s="19" t="n">
+      <c r="I90" s="17" t="n">
         <f aca="false">H90/1024</f>
         <v>5.92321157455444E-007</v>
       </c>
-      <c r="J90" s="21"/>
-      <c r="K90" s="21"/>
-      <c r="L90" s="20"/>
-      <c r="M90" s="20"/>
-      <c r="N90" s="21"/>
+      <c r="J90" s="19"/>
+      <c r="K90" s="19"/>
+      <c r="L90" s="18"/>
+      <c r="M90" s="18"/>
+      <c r="N90" s="19"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="40" t="s">
+      <c r="A91" s="37" t="s">
         <v>6</v>
       </c>
       <c r="B91" s="5" t="n">
@@ -3978,38 +3962,38 @@
       <c r="C91" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="D91" s="19" t="n">
+      <c r="D91" s="17" t="n">
         <f aca="false">B91+10*C91</f>
         <v>220</v>
       </c>
-      <c r="E91" s="19" t="n">
+      <c r="E91" s="17" t="n">
         <f aca="false">SUM(E49:E55)</f>
         <v>134</v>
       </c>
-      <c r="F91" s="19" t="n">
+      <c r="F91" s="17" t="n">
         <f aca="false">D91*E91</f>
         <v>29480</v>
       </c>
-      <c r="G91" s="37" t="n">
+      <c r="G91" s="34" t="n">
         <f aca="false">F91/1024</f>
         <v>28.7890625</v>
       </c>
-      <c r="H91" s="37" t="n">
+      <c r="H91" s="34" t="n">
         <f aca="false">G91/1024</f>
         <v>0.0281143188476563</v>
       </c>
-      <c r="I91" s="19" t="n">
+      <c r="I91" s="17" t="n">
         <f aca="false">H91/1024</f>
         <v>2.74553894996643E-005</v>
       </c>
-      <c r="J91" s="21"/>
-      <c r="K91" s="21"/>
-      <c r="L91" s="20"/>
-      <c r="M91" s="20"/>
-      <c r="N91" s="21"/>
+      <c r="J91" s="19"/>
+      <c r="K91" s="19"/>
+      <c r="L91" s="18"/>
+      <c r="M91" s="18"/>
+      <c r="N91" s="19"/>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="37" t="s">
         <v>7</v>
       </c>
       <c r="B92" s="5" t="n">
@@ -4018,554 +4002,554 @@
       <c r="C92" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D92" s="19" t="n">
+      <c r="D92" s="17" t="n">
         <f aca="false">B92+10*C92</f>
         <v>70</v>
       </c>
-      <c r="E92" s="19" t="n">
+      <c r="E92" s="17" t="n">
         <f aca="false">SUM(E57:E61)</f>
         <v>16</v>
       </c>
-      <c r="F92" s="19" t="n">
+      <c r="F92" s="17" t="n">
         <f aca="false">D92*E92</f>
         <v>1120</v>
       </c>
-      <c r="G92" s="37" t="n">
+      <c r="G92" s="34" t="n">
         <f aca="false">F92/1024</f>
         <v>1.09375</v>
       </c>
-      <c r="H92" s="37" t="n">
+      <c r="H92" s="34" t="n">
         <f aca="false">G92/1024</f>
         <v>0.001068115234375</v>
       </c>
-      <c r="I92" s="19" t="n">
+      <c r="I92" s="17" t="n">
         <f aca="false">H92/1024</f>
         <v>1.04308128356934E-006</v>
       </c>
-      <c r="J92" s="21"/>
-      <c r="K92" s="21"/>
-      <c r="L92" s="20"/>
-      <c r="M92" s="20"/>
-      <c r="N92" s="21"/>
+      <c r="J92" s="19"/>
+      <c r="K92" s="19"/>
+      <c r="L92" s="18"/>
+      <c r="M92" s="18"/>
+      <c r="N92" s="19"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="38" t="s">
+      <c r="A93" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B93" s="18" t="n">
+      <c r="B93" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="C93" s="18" t="n">
+      <c r="C93" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="D93" s="19" t="n">
+      <c r="D93" s="17" t="n">
         <f aca="false">B93+10*C93</f>
         <v>500</v>
       </c>
-      <c r="E93" s="19" t="n">
+      <c r="E93" s="17" t="n">
         <f aca="false">SUM(E62:E65)</f>
         <v>12</v>
       </c>
-      <c r="F93" s="19" t="n">
+      <c r="F93" s="17" t="n">
         <f aca="false">D93*E93</f>
         <v>6000</v>
       </c>
-      <c r="G93" s="37" t="n">
+      <c r="G93" s="34" t="n">
         <f aca="false">F93/1024</f>
         <v>5.859375</v>
       </c>
-      <c r="H93" s="37" t="n">
+      <c r="H93" s="34" t="n">
         <f aca="false">G93/1024</f>
         <v>0.0057220458984375</v>
       </c>
-      <c r="I93" s="19" t="n">
+      <c r="I93" s="17" t="n">
         <f aca="false">H93/1024</f>
         <v>5.58793544769287E-006</v>
       </c>
-      <c r="J93" s="21"/>
-      <c r="K93" s="21"/>
-      <c r="L93" s="20"/>
-      <c r="M93" s="20"/>
-      <c r="N93" s="21"/>
+      <c r="J93" s="19"/>
+      <c r="K93" s="19"/>
+      <c r="L93" s="18"/>
+      <c r="M93" s="18"/>
+      <c r="N93" s="19"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="38" t="s">
+      <c r="A94" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="41" t="n">
+      <c r="B94" s="38" t="n">
         <v>30000000</v>
       </c>
-      <c r="C94" s="41" t="n">
+      <c r="C94" s="38" t="n">
         <v>33000000</v>
       </c>
-      <c r="D94" s="19" t="n">
+      <c r="D94" s="17" t="n">
         <f aca="false">B94+10*C94</f>
         <v>360000000</v>
       </c>
-      <c r="E94" s="19" t="n">
+      <c r="E94" s="17" t="n">
         <f aca="false">SUM(E66:E69)</f>
         <v>21</v>
       </c>
-      <c r="F94" s="19" t="n">
+      <c r="F94" s="17" t="n">
         <f aca="false">D94*E94</f>
         <v>7560000000</v>
       </c>
-      <c r="G94" s="37" t="n">
+      <c r="G94" s="34" t="n">
         <f aca="false">F94/1024</f>
         <v>7382812.5</v>
       </c>
-      <c r="H94" s="37" t="n">
+      <c r="H94" s="34" t="n">
         <f aca="false">G94/1024</f>
         <v>7209.77783203125</v>
       </c>
-      <c r="I94" s="19" t="n">
+      <c r="I94" s="17" t="n">
         <f aca="false">H94/1024</f>
         <v>7.04079866409302</v>
       </c>
-      <c r="J94" s="21"/>
-      <c r="K94" s="21"/>
-      <c r="L94" s="20"/>
-      <c r="M94" s="20"/>
-      <c r="N94" s="21"/>
+      <c r="J94" s="19"/>
+      <c r="K94" s="19"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
+      <c r="N94" s="19"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="38" t="s">
+      <c r="A95" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B95" s="18" t="n">
+      <c r="B95" s="16" t="n">
         <v>30000</v>
       </c>
-      <c r="C95" s="18" t="n">
+      <c r="C95" s="16" t="n">
         <v>36000</v>
       </c>
-      <c r="D95" s="19" t="n">
+      <c r="D95" s="17" t="n">
         <f aca="false">B95+10*C95</f>
         <v>390000</v>
       </c>
-      <c r="E95" s="19" t="n">
+      <c r="E95" s="17" t="n">
         <f aca="false">SUM(E71:E75)</f>
         <v>21</v>
       </c>
-      <c r="F95" s="19" t="n">
+      <c r="F95" s="17" t="n">
         <f aca="false">D95*E95</f>
         <v>8190000</v>
       </c>
-      <c r="G95" s="37" t="n">
+      <c r="G95" s="34" t="n">
         <f aca="false">F95/1024</f>
         <v>7998.046875</v>
       </c>
-      <c r="H95" s="37" t="n">
+      <c r="H95" s="34" t="n">
         <f aca="false">G95/1024</f>
         <v>7.81059265136719</v>
       </c>
-      <c r="I95" s="19" t="n">
+      <c r="I95" s="17" t="n">
         <f aca="false">H95/1024</f>
         <v>0.00762753188610077</v>
       </c>
-      <c r="J95" s="21"/>
-      <c r="K95" s="21"/>
-      <c r="L95" s="20"/>
-      <c r="M95" s="20"/>
-      <c r="N95" s="21"/>
+      <c r="J95" s="19"/>
+      <c r="K95" s="19"/>
+      <c r="L95" s="18"/>
+      <c r="M95" s="18"/>
+      <c r="N95" s="19"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="23" t="s">
+      <c r="A96" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B96" s="18" t="n">
+      <c r="B96" s="16" t="n">
         <v>250</v>
       </c>
-      <c r="C96" s="18" t="n">
+      <c r="C96" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="D96" s="19" t="n">
+      <c r="D96" s="17" t="n">
         <f aca="false">B96+10*C96</f>
         <v>640</v>
       </c>
-      <c r="E96" s="19" t="n">
+      <c r="E96" s="17" t="n">
         <f aca="false">SUM(E76:E80)</f>
-        <v>135</v>
-      </c>
-      <c r="F96" s="19" t="n">
+        <v>171</v>
+      </c>
+      <c r="F96" s="17" t="n">
         <f aca="false">D96*E96</f>
-        <v>86400</v>
-      </c>
-      <c r="G96" s="37" t="n">
+        <v>109440</v>
+      </c>
+      <c r="G96" s="34" t="n">
         <f aca="false">F96/1024</f>
-        <v>84.375</v>
-      </c>
-      <c r="H96" s="37" t="n">
+        <v>106.875</v>
+      </c>
+      <c r="H96" s="34" t="n">
         <f aca="false">G96/1024</f>
-        <v>0.0823974609375</v>
-      </c>
-      <c r="I96" s="19" t="n">
+        <v>0.1043701171875</v>
+      </c>
+      <c r="I96" s="17" t="n">
         <f aca="false">H96/1024</f>
-        <v>8.04662704467773E-005</v>
-      </c>
-      <c r="J96" s="21"/>
-      <c r="K96" s="21"/>
-      <c r="L96" s="20"/>
-      <c r="M96" s="20"/>
-      <c r="N96" s="21"/>
+        <v>0.000101923942565918</v>
+      </c>
+      <c r="J96" s="19"/>
+      <c r="K96" s="19"/>
+      <c r="L96" s="18"/>
+      <c r="M96" s="18"/>
+      <c r="N96" s="19"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J97" s="21"/>
-      <c r="K97" s="21"/>
-      <c r="L97" s="20"/>
-      <c r="M97" s="20"/>
-      <c r="N97" s="21"/>
+      <c r="J97" s="19"/>
+      <c r="K97" s="19"/>
+      <c r="L97" s="18"/>
+      <c r="M97" s="18"/>
+      <c r="N97" s="19"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="42" t="s">
+      <c r="A98" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="43"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="21"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="19" t="n">
+      <c r="B98" s="40"/>
+      <c r="C98" s="40"/>
+      <c r="D98" s="19"/>
+      <c r="E98" s="19"/>
+      <c r="F98" s="17" t="n">
         <f aca="false">SUM(F85:F96)</f>
-        <v>9608453436</v>
-      </c>
-      <c r="G98" s="19" t="n">
+        <v>9608476476</v>
+      </c>
+      <c r="G98" s="17" t="n">
         <f aca="false">SUM(G85:G96)</f>
-        <v>9383255.30859375</v>
-      </c>
-      <c r="H98" s="19" t="n">
+        <v>9383277.80859375</v>
+      </c>
+      <c r="H98" s="17" t="n">
         <f aca="false">SUM(H85:H96)</f>
-        <v>9163.33526229858</v>
-      </c>
-      <c r="I98" s="19" t="n">
+        <v>9163.35723495483</v>
+      </c>
+      <c r="I98" s="17" t="n">
         <f aca="false">SUM(I85:I96)</f>
-        <v>8.94856959208846</v>
-      </c>
-      <c r="J98" s="21"/>
-      <c r="K98" s="21"/>
-      <c r="L98" s="20"/>
-      <c r="M98" s="20"/>
-      <c r="N98" s="21"/>
+        <v>8.94859104976059</v>
+      </c>
+      <c r="J98" s="19"/>
+      <c r="K98" s="19"/>
+      <c r="L98" s="18"/>
+      <c r="M98" s="18"/>
+      <c r="N98" s="19"/>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="21"/>
-      <c r="B99" s="21"/>
-      <c r="C99" s="21"/>
-      <c r="D99" s="21"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="21"/>
-      <c r="G99" s="21"/>
-      <c r="H99" s="21"/>
-      <c r="I99" s="21" t="s">
+      <c r="A99" s="19"/>
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="19"/>
+      <c r="E99" s="19"/>
+      <c r="F99" s="19"/>
+      <c r="G99" s="19"/>
+      <c r="H99" s="19"/>
+      <c r="I99" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="J99" s="21"/>
-      <c r="K99" s="21"/>
-      <c r="L99" s="20"/>
-      <c r="M99" s="20"/>
-      <c r="N99" s="21"/>
+      <c r="J99" s="19"/>
+      <c r="K99" s="19"/>
+      <c r="L99" s="18"/>
+      <c r="M99" s="18"/>
+      <c r="N99" s="19"/>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="44" t="s">
+      <c r="A100" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B100" s="44"/>
-      <c r="C100" s="44"/>
-      <c r="D100" s="45" t="n">
+      <c r="B100" s="41"/>
+      <c r="C100" s="41"/>
+      <c r="D100" s="42" t="n">
         <v>0.4</v>
       </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="19" t="n">
+      <c r="E100" s="19"/>
+      <c r="F100" s="17" t="n">
         <f aca="false">F98*1.4</f>
-        <v>13451834810.4</v>
-      </c>
-      <c r="G100" s="19" t="n">
+        <v>13451867066.4</v>
+      </c>
+      <c r="G100" s="17" t="n">
         <f aca="false">G98*1.4</f>
-        <v>13136557.4320313</v>
-      </c>
-      <c r="H100" s="19" t="n">
+        <v>13136588.9320313</v>
+      </c>
+      <c r="H100" s="17" t="n">
         <f aca="false">H98*1.4</f>
-        <v>12828.669367218</v>
-      </c>
-      <c r="I100" s="19" t="n">
+        <v>12828.7001289368</v>
+      </c>
+      <c r="I100" s="17" t="n">
         <f aca="false">I98*1.4</f>
-        <v>12.5279974289238</v>
-      </c>
-      <c r="J100" s="21"/>
-      <c r="K100" s="21"/>
-      <c r="L100" s="20"/>
-      <c r="M100" s="20"/>
-      <c r="N100" s="21"/>
+        <v>12.5280274696648</v>
+      </c>
+      <c r="J100" s="19"/>
+      <c r="K100" s="19"/>
+      <c r="L100" s="18"/>
+      <c r="M100" s="18"/>
+      <c r="N100" s="19"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="23"/>
-      <c r="B101" s="18"/>
-      <c r="C101" s="18"/>
-      <c r="D101" s="22"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="20"/>
-      <c r="G101" s="20"/>
-      <c r="H101" s="20"/>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21"/>
-      <c r="K101" s="21"/>
-      <c r="L101" s="20"/>
-      <c r="M101" s="20"/>
-      <c r="N101" s="21"/>
+      <c r="A101" s="21"/>
+      <c r="B101" s="16"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="18"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="19"/>
+      <c r="K101" s="19"/>
+      <c r="L101" s="18"/>
+      <c r="M101" s="18"/>
+      <c r="N101" s="19"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="23"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="20"/>
-      <c r="G102" s="20"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21"/>
-      <c r="K102" s="21"/>
-      <c r="L102" s="20"/>
-      <c r="M102" s="20"/>
-      <c r="N102" s="21"/>
+      <c r="A102" s="21"/>
+      <c r="B102" s="16"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="19"/>
+      <c r="F102" s="18"/>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="19"/>
+      <c r="K102" s="19"/>
+      <c r="L102" s="18"/>
+      <c r="M102" s="18"/>
+      <c r="N102" s="19"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="23"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="22"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="20"/>
-      <c r="G103" s="20"/>
-      <c r="H103" s="20"/>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21"/>
-      <c r="K103" s="21"/>
-      <c r="L103" s="20"/>
-      <c r="M103" s="20"/>
-      <c r="N103" s="21"/>
+      <c r="A103" s="21"/>
+      <c r="B103" s="16"/>
+      <c r="C103" s="16"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="19"/>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19"/>
+      <c r="K103" s="19"/>
+      <c r="L103" s="18"/>
+      <c r="M103" s="18"/>
+      <c r="N103" s="19"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J104" s="21"/>
-      <c r="K104" s="21"/>
-      <c r="L104" s="20"/>
-      <c r="M104" s="20"/>
-      <c r="N104" s="21"/>
+      <c r="J104" s="19"/>
+      <c r="K104" s="19"/>
+      <c r="L104" s="18"/>
+      <c r="M104" s="18"/>
+      <c r="N104" s="19"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J105" s="21"/>
-      <c r="K105" s="21"/>
-      <c r="L105" s="20"/>
-      <c r="M105" s="20"/>
-      <c r="N105" s="21"/>
+      <c r="J105" s="19"/>
+      <c r="K105" s="19"/>
+      <c r="L105" s="18"/>
+      <c r="M105" s="18"/>
+      <c r="N105" s="19"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J106" s="21"/>
-      <c r="K106" s="21"/>
-      <c r="L106" s="20"/>
-      <c r="M106" s="20"/>
-      <c r="N106" s="21"/>
+      <c r="J106" s="19"/>
+      <c r="K106" s="19"/>
+      <c r="L106" s="18"/>
+      <c r="M106" s="18"/>
+      <c r="N106" s="19"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="23"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="18"/>
-      <c r="D107" s="22"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="20"/>
-      <c r="G107" s="20"/>
-      <c r="H107" s="20"/>
-      <c r="I107" s="21"/>
-      <c r="J107" s="21"/>
-      <c r="K107" s="21"/>
-      <c r="L107" s="20"/>
-      <c r="M107" s="20"/>
-      <c r="N107" s="21"/>
+      <c r="A107" s="21"/>
+      <c r="B107" s="16"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="19"/>
+      <c r="F107" s="18"/>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18"/>
+      <c r="I107" s="19"/>
+      <c r="J107" s="19"/>
+      <c r="K107" s="19"/>
+      <c r="L107" s="18"/>
+      <c r="M107" s="18"/>
+      <c r="N107" s="19"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="23"/>
-      <c r="B108" s="18"/>
-      <c r="C108" s="18"/>
-      <c r="D108" s="22"/>
-      <c r="E108" s="21"/>
-      <c r="F108" s="20"/>
-      <c r="G108" s="20"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="21"/>
-      <c r="J108" s="21"/>
-      <c r="K108" s="21"/>
-      <c r="L108" s="20"/>
-      <c r="M108" s="20"/>
-      <c r="N108" s="21"/>
+      <c r="A108" s="21"/>
+      <c r="B108" s="16"/>
+      <c r="C108" s="16"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="18"/>
+      <c r="M108" s="18"/>
+      <c r="N108" s="19"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="23"/>
-      <c r="B109" s="18"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="22"/>
-      <c r="E109" s="21"/>
-      <c r="F109" s="20"/>
-      <c r="G109" s="20"/>
-      <c r="H109" s="20"/>
-      <c r="I109" s="21"/>
-      <c r="J109" s="21"/>
-      <c r="K109" s="21"/>
-      <c r="L109" s="20"/>
-      <c r="M109" s="20"/>
-      <c r="N109" s="21"/>
+      <c r="A109" s="21"/>
+      <c r="B109" s="16"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="18"/>
+      <c r="M109" s="18"/>
+      <c r="N109" s="19"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="23"/>
-      <c r="B110" s="18"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="22"/>
-      <c r="E110" s="21"/>
-      <c r="F110" s="20"/>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
-      <c r="I110" s="21"/>
-      <c r="J110" s="21"/>
-      <c r="K110" s="21"/>
-      <c r="L110" s="20"/>
-      <c r="M110" s="20"/>
-      <c r="N110" s="21"/>
+      <c r="A110" s="21"/>
+      <c r="B110" s="16"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="20"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="18"/>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="18"/>
+      <c r="M110" s="18"/>
+      <c r="N110" s="19"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="23"/>
-      <c r="B111" s="18"/>
-      <c r="C111" s="18"/>
-      <c r="D111" s="22"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="20"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="21"/>
-      <c r="J111" s="21"/>
-      <c r="K111" s="21"/>
-      <c r="L111" s="20"/>
-      <c r="M111" s="20"/>
-      <c r="N111" s="21"/>
+      <c r="A111" s="21"/>
+      <c r="B111" s="16"/>
+      <c r="C111" s="16"/>
+      <c r="D111" s="20"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="18"/>
+      <c r="G111" s="18"/>
+      <c r="H111" s="18"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="19"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="18"/>
+      <c r="M111" s="18"/>
+      <c r="N111" s="19"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="23"/>
-      <c r="B112" s="18"/>
-      <c r="C112" s="18"/>
-      <c r="D112" s="22"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21"/>
-      <c r="K112" s="21"/>
-      <c r="L112" s="20"/>
-      <c r="M112" s="20"/>
-      <c r="N112" s="21"/>
+      <c r="A112" s="21"/>
+      <c r="B112" s="16"/>
+      <c r="C112" s="16"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="18"/>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="18"/>
+      <c r="M112" s="18"/>
+      <c r="N112" s="19"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="23"/>
-      <c r="B113" s="18"/>
-      <c r="C113" s="18"/>
-      <c r="D113" s="22"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21"/>
-      <c r="K113" s="21"/>
-      <c r="L113" s="20"/>
-      <c r="M113" s="20"/>
-      <c r="N113" s="21"/>
+      <c r="A113" s="21"/>
+      <c r="B113" s="16"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="18"/>
+      <c r="M113" s="18"/>
+      <c r="N113" s="19"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J114" s="21"/>
-      <c r="K114" s="21"/>
-      <c r="L114" s="20"/>
-      <c r="M114" s="20"/>
-      <c r="N114" s="21"/>
+      <c r="J114" s="19"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="18"/>
+      <c r="M114" s="18"/>
+      <c r="N114" s="19"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J115" s="21"/>
-      <c r="K115" s="21"/>
-      <c r="L115" s="20"/>
-      <c r="M115" s="20"/>
-      <c r="N115" s="21"/>
+      <c r="J115" s="19"/>
+      <c r="K115" s="19"/>
+      <c r="L115" s="18"/>
+      <c r="M115" s="18"/>
+      <c r="N115" s="19"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J116" s="21"/>
-      <c r="K116" s="21"/>
-      <c r="L116" s="20"/>
-      <c r="M116" s="20"/>
-      <c r="N116" s="21"/>
+      <c r="J116" s="19"/>
+      <c r="K116" s="19"/>
+      <c r="L116" s="18"/>
+      <c r="M116" s="18"/>
+      <c r="N116" s="19"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J117" s="21"/>
-      <c r="K117" s="21"/>
-      <c r="L117" s="20"/>
-      <c r="M117" s="20"/>
-      <c r="N117" s="21"/>
+      <c r="J117" s="19"/>
+      <c r="K117" s="19"/>
+      <c r="L117" s="18"/>
+      <c r="M117" s="18"/>
+      <c r="N117" s="19"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J118" s="21"/>
-      <c r="K118" s="21"/>
-      <c r="L118" s="20"/>
-      <c r="M118" s="20"/>
-      <c r="N118" s="21"/>
+      <c r="J118" s="19"/>
+      <c r="K118" s="19"/>
+      <c r="L118" s="18"/>
+      <c r="M118" s="18"/>
+      <c r="N118" s="19"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J119" s="21"/>
-      <c r="K119" s="21"/>
-      <c r="L119" s="20"/>
-      <c r="M119" s="20"/>
-      <c r="N119" s="21"/>
+      <c r="J119" s="19"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="18"/>
+      <c r="M119" s="18"/>
+      <c r="N119" s="19"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J120" s="21"/>
-      <c r="K120" s="21"/>
-      <c r="L120" s="20"/>
-      <c r="M120" s="20"/>
-      <c r="N120" s="21"/>
+      <c r="J120" s="19"/>
+      <c r="K120" s="19"/>
+      <c r="L120" s="18"/>
+      <c r="M120" s="18"/>
+      <c r="N120" s="19"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J121" s="21"/>
-      <c r="K121" s="21"/>
-      <c r="L121" s="20"/>
-      <c r="M121" s="20"/>
-      <c r="N121" s="21"/>
+      <c r="J121" s="19"/>
+      <c r="K121" s="19"/>
+      <c r="L121" s="18"/>
+      <c r="M121" s="18"/>
+      <c r="N121" s="19"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J122" s="21"/>
-      <c r="K122" s="21"/>
-      <c r="L122" s="20"/>
-      <c r="M122" s="20"/>
-      <c r="N122" s="21"/>
+      <c r="J122" s="19"/>
+      <c r="K122" s="19"/>
+      <c r="L122" s="18"/>
+      <c r="M122" s="18"/>
+      <c r="N122" s="19"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J123" s="21"/>
-      <c r="K123" s="21"/>
-      <c r="L123" s="20"/>
-      <c r="M123" s="20"/>
-      <c r="N123" s="21"/>
+      <c r="J123" s="19"/>
+      <c r="K123" s="19"/>
+      <c r="L123" s="18"/>
+      <c r="M123" s="18"/>
+      <c r="N123" s="19"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J124" s="21"/>
-      <c r="K124" s="21"/>
-      <c r="L124" s="20"/>
-      <c r="M124" s="20"/>
-      <c r="N124" s="21"/>
+      <c r="J124" s="19"/>
+      <c r="K124" s="19"/>
+      <c r="L124" s="18"/>
+      <c r="M124" s="18"/>
+      <c r="N124" s="19"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J125" s="21"/>
-      <c r="K125" s="21"/>
-      <c r="L125" s="20"/>
-      <c r="M125" s="20"/>
-      <c r="N125" s="21"/>
+      <c r="J125" s="19"/>
+      <c r="K125" s="19"/>
+      <c r="L125" s="18"/>
+      <c r="M125" s="18"/>
+      <c r="N125" s="19"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J126" s="21"/>
-      <c r="K126" s="21"/>
-      <c r="L126" s="20"/>
-      <c r="M126" s="20"/>
-      <c r="N126" s="21"/>
+      <c r="J126" s="19"/>
+      <c r="K126" s="19"/>
+      <c r="L126" s="18"/>
+      <c r="M126" s="18"/>
+      <c r="N126" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Speicherplatzberechnung_Bäckereikette.xlsx
+++ b/Speicherplatzberechnung_Bäckereikette.xlsx
@@ -4127,24 +4127,24 @@
         <v>390000</v>
       </c>
       <c r="E95" s="17" t="n">
-        <f aca="false">SUM(E71:E75)</f>
-        <v>21</v>
+        <f aca="false">SUM(E70:E74)</f>
+        <v>20</v>
       </c>
       <c r="F95" s="17" t="n">
         <f aca="false">D95*E95</f>
-        <v>8190000</v>
+        <v>7800000</v>
       </c>
       <c r="G95" s="34" t="n">
         <f aca="false">F95/1024</f>
-        <v>7998.046875</v>
+        <v>7617.1875</v>
       </c>
       <c r="H95" s="34" t="n">
         <f aca="false">G95/1024</f>
-        <v>7.81059265136719</v>
+        <v>7.43865966796875</v>
       </c>
       <c r="I95" s="17" t="n">
         <f aca="false">H95/1024</f>
-        <v>0.00762753188610077</v>
+        <v>0.00726431608200073</v>
       </c>
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
@@ -4209,19 +4209,19 @@
       <c r="E98" s="19"/>
       <c r="F98" s="17" t="n">
         <f aca="false">SUM(F85:F96)</f>
-        <v>9608476476</v>
+        <v>9608086476</v>
       </c>
       <c r="G98" s="17" t="n">
         <f aca="false">SUM(G85:G96)</f>
-        <v>9383277.80859375</v>
+        <v>9382896.94921875</v>
       </c>
       <c r="H98" s="17" t="n">
         <f aca="false">SUM(H85:H96)</f>
-        <v>9163.35723495483</v>
+        <v>9162.98530197144</v>
       </c>
       <c r="I98" s="17" t="n">
         <f aca="false">SUM(I85:I96)</f>
-        <v>8.94859104976059</v>
+        <v>8.94822783395649</v>
       </c>
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
@@ -4259,19 +4259,19 @@
       <c r="E100" s="19"/>
       <c r="F100" s="17" t="n">
         <f aca="false">F98*1.4</f>
-        <v>13451867066.4</v>
+        <v>13451321066.4</v>
       </c>
       <c r="G100" s="17" t="n">
         <f aca="false">G98*1.4</f>
-        <v>13136588.9320313</v>
+        <v>13136055.7289063</v>
       </c>
       <c r="H100" s="17" t="n">
         <f aca="false">H98*1.4</f>
-        <v>12828.7001289368</v>
+        <v>12828.17942276</v>
       </c>
       <c r="I100" s="17" t="n">
         <f aca="false">I98*1.4</f>
-        <v>12.5280274696648</v>
+        <v>12.5275189675391</v>
       </c>
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
